--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE97F19-3299-4AA7-A272-9E976627C0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B1B50A-1926-45C7-AE34-96CBAD6C4EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="1428">
   <si>
     <t>artist</t>
   </si>
@@ -4804,6 +4804,12 @@
   </si>
   <si>
     <t>Jondy</t>
+  </si>
+  <si>
+    <t>Tanweer Studios</t>
+  </si>
+  <si>
+    <t>Tanweer's Preparation Workshop</t>
   </si>
 </sst>
 </file>
@@ -17046,7 +17052,9 @@
       <c r="I341" s="6"/>
       <c r="J341" s="8"/>
       <c r="K341" s="7"/>
-      <c r="L341" s="7"/>
+      <c r="L341" s="7" t="s">
+        <v>1426</v>
+      </c>
       <c r="M341" s="7"/>
       <c r="N341" s="7"/>
       <c r="O341" s="7"/>
@@ -17073,7 +17081,9 @@
       <c r="I342" s="6"/>
       <c r="J342" s="8"/>
       <c r="K342" s="7"/>
-      <c r="L342" s="7"/>
+      <c r="L342" s="7" t="s">
+        <v>1427</v>
+      </c>
       <c r="M342" s="7"/>
       <c r="N342" s="7"/>
       <c r="O342" s="7"/>
@@ -17085,9 +17095,7 @@
       <c r="S342" s="7"/>
       <c r="T342" s="6"/>
       <c r="U342" s="6"/>
-      <c r="V342" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="V342" s="7"/>
       <c r="W342" s="7"/>
       <c r="X342" s="6"/>
       <c r="Y342" s="6"/>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B1B50A-1926-45C7-AE34-96CBAD6C4EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1B7B74-B581-443E-AB99-28D78C3E9B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="1496">
   <si>
     <t>artist</t>
   </si>
@@ -4810,6 +4810,210 @@
   </si>
   <si>
     <t>Tanweer's Preparation Workshop</t>
+  </si>
+  <si>
+    <t>corisa-lee</t>
+  </si>
+  <si>
+    <t>judy-chen</t>
+  </si>
+  <si>
+    <t>karen-wang</t>
+  </si>
+  <si>
+    <t>jiang-xian-cheng</t>
+  </si>
+  <si>
+    <t>xie-wen-de</t>
+  </si>
+  <si>
+    <t>sun-de-cheng</t>
+  </si>
+  <si>
+    <t>yang-shao-wen</t>
+  </si>
+  <si>
+    <t>xu-jian-chun</t>
+  </si>
+  <si>
+    <t>shen-guang-ping</t>
+  </si>
+  <si>
+    <t>tong-shao-zong</t>
+  </si>
+  <si>
+    <t>hong-ming</t>
+  </si>
+  <si>
+    <t>bernard-lau</t>
+  </si>
+  <si>
+    <t>hong-zi-jing</t>
+  </si>
+  <si>
+    <t>karen-wangs-studio</t>
+  </si>
+  <si>
+    <t>house-of-music-group</t>
+  </si>
+  <si>
+    <t>Corisa Lee</t>
+  </si>
+  <si>
+    <t>Judy Chen</t>
+  </si>
+  <si>
+    <t>Karen Wang</t>
+  </si>
+  <si>
+    <t>Hóng Míng</t>
+  </si>
+  <si>
+    <t>洪明</t>
+  </si>
+  <si>
+    <t>Bernard Lau</t>
+  </si>
+  <si>
+    <t>Lǐ</t>
+  </si>
+  <si>
+    <t>Chén</t>
+  </si>
+  <si>
+    <t>Wáng</t>
+  </si>
+  <si>
+    <t>Jiāng</t>
+  </si>
+  <si>
+    <t>Xiè</t>
+  </si>
+  <si>
+    <t>Sūn</t>
+  </si>
+  <si>
+    <t>Yáng</t>
+  </si>
+  <si>
+    <t>Xú</t>
+  </si>
+  <si>
+    <t>Shěn</t>
+  </si>
+  <si>
+    <t>Tóng</t>
+  </si>
+  <si>
+    <t>Zhāng</t>
+  </si>
+  <si>
+    <t>Lóu</t>
+  </si>
+  <si>
+    <t>Hóng</t>
+  </si>
+  <si>
+    <t>Wén-Dé</t>
+  </si>
+  <si>
+    <t>Dé-Chéng</t>
+  </si>
+  <si>
+    <t>Shǎo-Wén</t>
+  </si>
+  <si>
+    <t>Jiàn-Chūn</t>
+  </si>
+  <si>
+    <t>Guāng-Píng</t>
+  </si>
+  <si>
+    <t>Shào-Zōng</t>
+  </si>
+  <si>
+    <t>Hóng-Míng</t>
+  </si>
+  <si>
+    <t>Ēn-Qí</t>
+  </si>
+  <si>
+    <t>Zǐ-Jīng</t>
+  </si>
+  <si>
+    <t>Zhí-píng</t>
+  </si>
+  <si>
+    <t>Xiù-zhū</t>
+  </si>
+  <si>
+    <t>Jǐng-píng</t>
+  </si>
+  <si>
+    <t>Xiān-chéng</t>
+  </si>
+  <si>
+    <t>李直平</t>
+  </si>
+  <si>
+    <t>陳秀珠</t>
+  </si>
+  <si>
+    <t>王景平</t>
+  </si>
+  <si>
+    <t>姜先誠</t>
+  </si>
+  <si>
+    <t>謝文德</t>
+  </si>
+  <si>
+    <t>孫德成</t>
+  </si>
+  <si>
+    <t>楊少文</t>
+  </si>
+  <si>
+    <t>徐健春</t>
+  </si>
+  <si>
+    <t>沈光平</t>
+  </si>
+  <si>
+    <t>佟紹宗</t>
+  </si>
+  <si>
+    <t>張鴻明</t>
+  </si>
+  <si>
+    <t>樓恩奇</t>
+  </si>
+  <si>
+    <t>洪紫晶</t>
+  </si>
+  <si>
+    <t>Karen Wang's Studio Co., LTD (景平工作室)</t>
+  </si>
+  <si>
+    <t>"HMG" House of Music Group (音樂世家)</t>
+  </si>
+  <si>
+    <t>chinese-traditional</t>
+  </si>
+  <si>
+    <t>Corisa_Lee.png</t>
+  </si>
+  <si>
+    <t>Judy_Chen.png</t>
+  </si>
+  <si>
+    <t>Karen_Wang.png</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>1953-11-15</t>
   </si>
 </sst>
 </file>
@@ -17139,24 +17343,42 @@
       <c r="Y343" s="6"/>
     </row>
     <row r="344" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A344" s="7"/>
-      <c r="B344" s="7"/>
+      <c r="A344" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>1443</v>
+      </c>
       <c r="C344" s="7"/>
-      <c r="D344" s="7"/>
+      <c r="D344" s="7" t="s">
+        <v>1449</v>
+      </c>
       <c r="E344" s="7"/>
-      <c r="F344" s="7"/>
-      <c r="G344" s="7"/>
-      <c r="H344" s="7"/>
+      <c r="F344" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G344" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I344" s="6"/>
       <c r="J344" s="8"/>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
       <c r="N344" s="7"/>
-      <c r="O344" s="7"/>
-      <c r="P344" s="7"/>
+      <c r="O344" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="P344" t="s">
+        <v>1491</v>
+      </c>
       <c r="Q344" s="6"/>
-      <c r="R344" s="7"/>
+      <c r="R344" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S344" s="7"/>
       <c r="T344" s="6"/>
       <c r="U344" s="6"/>
@@ -17166,24 +17388,42 @@
       <c r="Y344" s="6"/>
     </row>
     <row r="345" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A345" s="7"/>
-      <c r="B345" s="7"/>
+      <c r="A345" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>1444</v>
+      </c>
       <c r="C345" s="7"/>
-      <c r="D345" s="7"/>
+      <c r="D345" s="7" t="s">
+        <v>1450</v>
+      </c>
       <c r="E345" s="7"/>
-      <c r="F345" s="7"/>
-      <c r="G345" s="7"/>
-      <c r="H345" s="7"/>
+      <c r="F345" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G345" s="7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H345" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I345" s="6"/>
       <c r="J345" s="8"/>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c r="M345" s="7"/>
       <c r="N345" s="7"/>
-      <c r="O345" s="7"/>
-      <c r="P345" s="7"/>
+      <c r="O345" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="P345" t="s">
+        <v>1492</v>
+      </c>
       <c r="Q345" s="6"/>
-      <c r="R345" s="7"/>
+      <c r="R345" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S345" s="7"/>
       <c r="T345" s="6"/>
       <c r="U345" s="6"/>
@@ -17193,26 +17433,46 @@
       <c r="Y345" s="6"/>
     </row>
     <row r="346" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A346" s="7"/>
-      <c r="B346" s="7"/>
+      <c r="A346" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>1445</v>
+      </c>
       <c r="C346" s="7"/>
-      <c r="D346" s="7"/>
+      <c r="D346" s="7" t="s">
+        <v>1451</v>
+      </c>
       <c r="E346" s="7"/>
-      <c r="F346" s="7"/>
-      <c r="G346" s="7"/>
-      <c r="H346" s="7"/>
+      <c r="F346" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G346" s="7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H346" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I346" s="6"/>
       <c r="J346" s="8"/>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c r="M346" s="7"/>
       <c r="N346" s="7"/>
-      <c r="O346" s="7"/>
-      <c r="P346" s="7"/>
+      <c r="O346" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="P346" t="s">
+        <v>1493</v>
+      </c>
       <c r="Q346" s="6"/>
-      <c r="R346" s="7"/>
+      <c r="R346" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S346" s="7"/>
-      <c r="T346" s="6"/>
+      <c r="T346" s="6" t="s">
+        <v>1495</v>
+      </c>
       <c r="U346" s="6"/>
       <c r="V346" s="7"/>
       <c r="W346" s="7"/>
@@ -17220,24 +17480,38 @@
       <c r="Y346" s="6"/>
     </row>
     <row r="347" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A347" s="7"/>
+      <c r="A347" s="7" t="s">
+        <v>1431</v>
+      </c>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
-      <c r="D347" s="7"/>
+      <c r="D347" s="7" t="s">
+        <v>1452</v>
+      </c>
       <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
-      <c r="G347" s="7"/>
-      <c r="H347" s="7"/>
+      <c r="F347" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G347" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H347" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I347" s="6"/>
       <c r="J347" s="8"/>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
       <c r="N347" s="7"/>
-      <c r="O347" s="7"/>
+      <c r="O347" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P347" s="7"/>
       <c r="Q347" s="6"/>
-      <c r="R347" s="7"/>
+      <c r="R347" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S347" s="7"/>
       <c r="T347" s="6"/>
       <c r="U347" s="6"/>
@@ -17247,24 +17521,38 @@
       <c r="Y347" s="6"/>
     </row>
     <row r="348" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A348" s="7"/>
+      <c r="A348" s="7" t="s">
+        <v>1432</v>
+      </c>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
-      <c r="D348" s="7"/>
+      <c r="D348" s="7" t="s">
+        <v>1453</v>
+      </c>
       <c r="E348" s="7"/>
-      <c r="F348" s="7"/>
-      <c r="G348" s="7"/>
-      <c r="H348" s="7"/>
+      <c r="F348" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G348" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I348" s="6"/>
       <c r="J348" s="8"/>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
       <c r="N348" s="7"/>
-      <c r="O348" s="7"/>
+      <c r="O348" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P348" s="7"/>
       <c r="Q348" s="6"/>
-      <c r="R348" s="7"/>
+      <c r="R348" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S348" s="7"/>
       <c r="T348" s="6"/>
       <c r="U348" s="6"/>
@@ -17274,24 +17562,38 @@
       <c r="Y348" s="6"/>
     </row>
     <row r="349" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A349" s="7"/>
+      <c r="A349" s="7" t="s">
+        <v>1433</v>
+      </c>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
-      <c r="D349" s="7"/>
+      <c r="D349" s="7" t="s">
+        <v>1454</v>
+      </c>
       <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
-      <c r="G349" s="7"/>
-      <c r="H349" s="7"/>
+      <c r="F349" s="7" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G349" s="7" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H349" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I349" s="6"/>
       <c r="J349" s="8"/>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c r="M349" s="7"/>
       <c r="N349" s="7"/>
-      <c r="O349" s="7"/>
+      <c r="O349" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P349" s="7"/>
       <c r="Q349" s="6"/>
-      <c r="R349" s="7"/>
+      <c r="R349" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S349" s="7"/>
       <c r="T349" s="6"/>
       <c r="U349" s="6"/>
@@ -17301,24 +17603,38 @@
       <c r="Y349" s="6"/>
     </row>
     <row r="350" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A350" s="7"/>
+      <c r="A350" s="7" t="s">
+        <v>1434</v>
+      </c>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
-      <c r="D350" s="7"/>
+      <c r="D350" s="7" t="s">
+        <v>1455</v>
+      </c>
       <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
-      <c r="G350" s="7"/>
-      <c r="H350" s="7"/>
+      <c r="F350" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G350" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H350" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I350" s="6"/>
       <c r="J350" s="8"/>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c r="M350" s="7"/>
       <c r="N350" s="7"/>
-      <c r="O350" s="7"/>
+      <c r="O350" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P350" s="7"/>
       <c r="Q350" s="6"/>
-      <c r="R350" s="7"/>
+      <c r="R350" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S350" s="7"/>
       <c r="T350" s="6"/>
       <c r="U350" s="6"/>
@@ -17328,24 +17644,38 @@
       <c r="Y350" s="6"/>
     </row>
     <row r="351" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A351" s="7"/>
+      <c r="A351" s="7" t="s">
+        <v>1435</v>
+      </c>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
-      <c r="D351" s="7"/>
+      <c r="D351" s="7" t="s">
+        <v>1456</v>
+      </c>
       <c r="E351" s="7"/>
-      <c r="F351" s="7"/>
-      <c r="G351" s="7"/>
-      <c r="H351" s="7"/>
+      <c r="F351" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G351" s="7" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I351" s="6"/>
       <c r="J351" s="8"/>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
       <c r="N351" s="7"/>
-      <c r="O351" s="7"/>
+      <c r="O351" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P351" s="7"/>
       <c r="Q351" s="6"/>
-      <c r="R351" s="7"/>
+      <c r="R351" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S351" s="7"/>
       <c r="T351" s="6"/>
       <c r="U351" s="6"/>
@@ -17355,24 +17685,38 @@
       <c r="Y351" s="6"/>
     </row>
     <row r="352" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A352" s="7"/>
+      <c r="A352" s="7" t="s">
+        <v>1436</v>
+      </c>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
-      <c r="D352" s="7"/>
+      <c r="D352" s="7" t="s">
+        <v>1457</v>
+      </c>
       <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
-      <c r="G352" s="7"/>
-      <c r="H352" s="7"/>
+      <c r="F352" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G352" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I352" s="6"/>
       <c r="J352" s="8"/>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
       <c r="N352" s="7"/>
-      <c r="O352" s="7"/>
+      <c r="O352" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P352" s="7"/>
       <c r="Q352" s="6"/>
-      <c r="R352" s="7"/>
+      <c r="R352" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S352" s="7"/>
       <c r="T352" s="6"/>
       <c r="U352" s="6"/>
@@ -17382,24 +17726,38 @@
       <c r="Y352" s="6"/>
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A353" s="7"/>
+      <c r="A353" s="7" t="s">
+        <v>1437</v>
+      </c>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
-      <c r="D353" s="7"/>
+      <c r="D353" s="7" t="s">
+        <v>1458</v>
+      </c>
       <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
-      <c r="G353" s="7"/>
-      <c r="H353" s="7"/>
+      <c r="F353" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G353" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I353" s="6"/>
       <c r="J353" s="8"/>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
       <c r="N353" s="7"/>
-      <c r="O353" s="7"/>
+      <c r="O353" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P353" s="7"/>
       <c r="Q353" s="6"/>
-      <c r="R353" s="7"/>
+      <c r="R353" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S353" s="7"/>
       <c r="T353" s="6"/>
       <c r="U353" s="6"/>
@@ -17409,24 +17767,42 @@
       <c r="Y353" s="6"/>
     </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A354" s="7"/>
-      <c r="B354" s="7"/>
-      <c r="C354" s="7"/>
-      <c r="D354" s="7"/>
+      <c r="A354" s="7" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D354" s="7" t="s">
+        <v>1459</v>
+      </c>
       <c r="E354" s="7"/>
-      <c r="F354" s="7"/>
-      <c r="G354" s="7"/>
-      <c r="H354" s="7"/>
+      <c r="F354" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G354" s="7" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I354" s="6"/>
       <c r="J354" s="8"/>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c r="M354" s="7"/>
       <c r="N354" s="7"/>
-      <c r="O354" s="7"/>
+      <c r="O354" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P354" s="7"/>
       <c r="Q354" s="6"/>
-      <c r="R354" s="7"/>
+      <c r="R354" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S354" s="7"/>
       <c r="T354" s="6"/>
       <c r="U354" s="6"/>
@@ -17436,24 +17812,40 @@
       <c r="Y354" s="6"/>
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A355" s="7"/>
-      <c r="B355" s="7"/>
+      <c r="A355" s="7" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>1448</v>
+      </c>
       <c r="C355" s="7"/>
-      <c r="D355" s="7"/>
+      <c r="D355" s="7" t="s">
+        <v>1460</v>
+      </c>
       <c r="E355" s="7"/>
-      <c r="F355" s="7"/>
-      <c r="G355" s="7"/>
-      <c r="H355" s="7"/>
+      <c r="F355" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G355" s="7" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I355" s="6"/>
       <c r="J355" s="8"/>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
       <c r="N355" s="7"/>
-      <c r="O355" s="7"/>
+      <c r="O355" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P355" s="7"/>
       <c r="Q355" s="6"/>
-      <c r="R355" s="7"/>
+      <c r="R355" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S355" s="7"/>
       <c r="T355" s="6"/>
       <c r="U355" s="6"/>
@@ -17463,24 +17855,38 @@
       <c r="Y355" s="6"/>
     </row>
     <row r="356" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A356" s="7"/>
+      <c r="A356" s="7" t="s">
+        <v>1440</v>
+      </c>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
-      <c r="D356" s="7"/>
+      <c r="D356" s="7" t="s">
+        <v>1461</v>
+      </c>
       <c r="E356" s="7"/>
-      <c r="F356" s="7"/>
-      <c r="G356" s="7"/>
-      <c r="H356" s="7"/>
+      <c r="F356" s="7" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G356" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H356" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="I356" s="6"/>
       <c r="J356" s="8"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
       <c r="N356" s="7"/>
-      <c r="O356" s="7"/>
+      <c r="O356" s="7" t="s">
+        <v>1490</v>
+      </c>
       <c r="P356" s="7"/>
       <c r="Q356" s="6"/>
-      <c r="R356" s="7"/>
+      <c r="R356" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S356" s="7"/>
       <c r="T356" s="6"/>
       <c r="U356" s="6"/>
@@ -17490,7 +17896,9 @@
       <c r="Y356" s="6"/>
     </row>
     <row r="357" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A357" s="7"/>
+      <c r="A357" s="7" t="s">
+        <v>1441</v>
+      </c>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -17501,23 +17909,31 @@
       <c r="I357" s="6"/>
       <c r="J357" s="8"/>
       <c r="K357" s="7"/>
-      <c r="L357" s="7"/>
+      <c r="L357" s="7" t="s">
+        <v>1488</v>
+      </c>
       <c r="M357" s="7"/>
       <c r="N357" s="7"/>
       <c r="O357" s="7"/>
       <c r="P357" s="7"/>
       <c r="Q357" s="6"/>
-      <c r="R357" s="7"/>
+      <c r="R357" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S357" s="7"/>
       <c r="T357" s="6"/>
       <c r="U357" s="6"/>
-      <c r="V357" s="7"/>
+      <c r="V357" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="W357" s="7"/>
       <c r="X357" s="6"/>
       <c r="Y357" s="6"/>
     </row>
     <row r="358" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A358" s="7"/>
+      <c r="A358" s="7" t="s">
+        <v>1442</v>
+      </c>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -17528,17 +17944,23 @@
       <c r="I358" s="6"/>
       <c r="J358" s="8"/>
       <c r="K358" s="7"/>
-      <c r="L358" s="7"/>
+      <c r="L358" s="7" t="s">
+        <v>1489</v>
+      </c>
       <c r="M358" s="7"/>
       <c r="N358" s="7"/>
       <c r="O358" s="7"/>
       <c r="P358" s="7"/>
       <c r="Q358" s="6"/>
-      <c r="R358" s="7"/>
+      <c r="R358" s="7" t="s">
+        <v>1494</v>
+      </c>
       <c r="S358" s="7"/>
       <c r="T358" s="6"/>
       <c r="U358" s="6"/>
-      <c r="V358" s="7"/>
+      <c r="V358" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="W358" s="7"/>
       <c r="X358" s="6"/>
       <c r="Y358" s="6"/>
@@ -34856,7 +35278,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H239:H999 H2:H166" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H166 H239:H999" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"family"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -35277,18 +35277,21 @@
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H166 H239:H999" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H1001" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"family"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="V239:V999 V2:V166" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="V2:V1001" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"studio"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="W239:W999 W2:W166" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="W2:W1001" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"cover"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="0" sqref="O2:O1001" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>"arabic,armenian,bengali,cantonese,chinese-simplified,chinese-traditional,cyrillic,georgian,greek,hebrew,hindi,marathi,japanese,kannada,korean,malayalam,tamil,telugu,thai"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1B7B74-B581-443E-AB99-28D78C3E9B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B2214E-64A3-4DEB-8A87-6986F6D442C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Artistes" sheetId="1" r:id="rId1"/>
@@ -4914,33 +4914,6 @@
     <t>Hóng</t>
   </si>
   <si>
-    <t>Wén-Dé</t>
-  </si>
-  <si>
-    <t>Dé-Chéng</t>
-  </si>
-  <si>
-    <t>Shǎo-Wén</t>
-  </si>
-  <si>
-    <t>Jiàn-Chūn</t>
-  </si>
-  <si>
-    <t>Guāng-Píng</t>
-  </si>
-  <si>
-    <t>Shào-Zōng</t>
-  </si>
-  <si>
-    <t>Hóng-Míng</t>
-  </si>
-  <si>
-    <t>Ēn-Qí</t>
-  </si>
-  <si>
-    <t>Zǐ-Jīng</t>
-  </si>
-  <si>
     <t>Zhí-píng</t>
   </si>
   <si>
@@ -5014,6 +4987,33 @@
   </si>
   <si>
     <t>1953-11-15</t>
+  </si>
+  <si>
+    <t>Dé-chéng</t>
+  </si>
+  <si>
+    <t>Wén-dé</t>
+  </si>
+  <si>
+    <t>Shǎo-wén</t>
+  </si>
+  <si>
+    <t>Jiàn-chūn</t>
+  </si>
+  <si>
+    <t>Guāng-píng</t>
+  </si>
+  <si>
+    <t>Shào-zōng</t>
+  </si>
+  <si>
+    <t>Hóng-míng</t>
+  </si>
+  <si>
+    <t>Ēn-qí</t>
+  </si>
+  <si>
+    <t>Zǐ-jīng</t>
   </si>
 </sst>
 </file>
@@ -17355,10 +17355,10 @@
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7" t="s">
-        <v>1471</v>
+        <v>1462</v>
       </c>
       <c r="G344" s="7" t="s">
-        <v>1475</v>
+        <v>1466</v>
       </c>
       <c r="H344" s="7" t="s">
         <v>31</v>
@@ -17370,14 +17370,14 @@
       <c r="M344" s="7"/>
       <c r="N344" s="7"/>
       <c r="O344" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P344" t="s">
-        <v>1491</v>
+        <v>1482</v>
       </c>
       <c r="Q344" s="6"/>
       <c r="R344" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S344" s="7"/>
       <c r="T344" s="6"/>
@@ -17400,10 +17400,10 @@
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7" t="s">
-        <v>1472</v>
+        <v>1463</v>
       </c>
       <c r="G345" s="7" t="s">
-        <v>1476</v>
+        <v>1467</v>
       </c>
       <c r="H345" s="7" t="s">
         <v>31</v>
@@ -17415,14 +17415,14 @@
       <c r="M345" s="7"/>
       <c r="N345" s="7"/>
       <c r="O345" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P345" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="Q345" s="6"/>
       <c r="R345" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S345" s="7"/>
       <c r="T345" s="6"/>
@@ -17445,10 +17445,10 @@
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7" t="s">
-        <v>1473</v>
+        <v>1464</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="H346" s="7" t="s">
         <v>31</v>
@@ -17460,18 +17460,18 @@
       <c r="M346" s="7"/>
       <c r="N346" s="7"/>
       <c r="O346" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P346" t="s">
-        <v>1493</v>
+        <v>1484</v>
       </c>
       <c r="Q346" s="6"/>
       <c r="R346" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S346" s="7"/>
       <c r="T346" s="6" t="s">
-        <v>1495</v>
+        <v>1486</v>
       </c>
       <c r="U346" s="6"/>
       <c r="V346" s="7"/>
@@ -17490,10 +17490,10 @@
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7" t="s">
-        <v>1474</v>
+        <v>1465</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>1478</v>
+        <v>1469</v>
       </c>
       <c r="H347" s="7" t="s">
         <v>31</v>
@@ -17505,12 +17505,12 @@
       <c r="M347" s="7"/>
       <c r="N347" s="7"/>
       <c r="O347" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P347" s="7"/>
       <c r="Q347" s="6"/>
       <c r="R347" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S347" s="7"/>
       <c r="T347" s="6"/>
@@ -17531,10 +17531,10 @@
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7" t="s">
-        <v>1462</v>
+        <v>1488</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>1479</v>
+        <v>1470</v>
       </c>
       <c r="H348" s="7" t="s">
         <v>31</v>
@@ -17546,12 +17546,12 @@
       <c r="M348" s="7"/>
       <c r="N348" s="7"/>
       <c r="O348" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P348" s="7"/>
       <c r="Q348" s="6"/>
       <c r="R348" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S348" s="7"/>
       <c r="T348" s="6"/>
@@ -17572,10 +17572,10 @@
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7" t="s">
-        <v>1463</v>
+        <v>1487</v>
       </c>
       <c r="G349" s="7" t="s">
-        <v>1480</v>
+        <v>1471</v>
       </c>
       <c r="H349" s="7" t="s">
         <v>31</v>
@@ -17587,12 +17587,12 @@
       <c r="M349" s="7"/>
       <c r="N349" s="7"/>
       <c r="O349" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P349" s="7"/>
       <c r="Q349" s="6"/>
       <c r="R349" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S349" s="7"/>
       <c r="T349" s="6"/>
@@ -17613,10 +17613,10 @@
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7" t="s">
-        <v>1464</v>
+        <v>1489</v>
       </c>
       <c r="G350" s="7" t="s">
-        <v>1481</v>
+        <v>1472</v>
       </c>
       <c r="H350" s="7" t="s">
         <v>31</v>
@@ -17628,12 +17628,12 @@
       <c r="M350" s="7"/>
       <c r="N350" s="7"/>
       <c r="O350" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P350" s="7"/>
       <c r="Q350" s="6"/>
       <c r="R350" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S350" s="7"/>
       <c r="T350" s="6"/>
@@ -17654,10 +17654,10 @@
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7" t="s">
-        <v>1465</v>
+        <v>1490</v>
       </c>
       <c r="G351" s="7" t="s">
-        <v>1482</v>
+        <v>1473</v>
       </c>
       <c r="H351" s="7" t="s">
         <v>31</v>
@@ -17669,12 +17669,12 @@
       <c r="M351" s="7"/>
       <c r="N351" s="7"/>
       <c r="O351" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P351" s="7"/>
       <c r="Q351" s="6"/>
       <c r="R351" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S351" s="7"/>
       <c r="T351" s="6"/>
@@ -17695,10 +17695,10 @@
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7" t="s">
-        <v>1466</v>
+        <v>1491</v>
       </c>
       <c r="G352" s="7" t="s">
-        <v>1483</v>
+        <v>1474</v>
       </c>
       <c r="H352" s="7" t="s">
         <v>31</v>
@@ -17710,12 +17710,12 @@
       <c r="M352" s="7"/>
       <c r="N352" s="7"/>
       <c r="O352" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P352" s="7"/>
       <c r="Q352" s="6"/>
       <c r="R352" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S352" s="7"/>
       <c r="T352" s="6"/>
@@ -17736,10 +17736,10 @@
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7" t="s">
-        <v>1467</v>
+        <v>1492</v>
       </c>
       <c r="G353" s="7" t="s">
-        <v>1484</v>
+        <v>1475</v>
       </c>
       <c r="H353" s="7" t="s">
         <v>31</v>
@@ -17751,12 +17751,12 @@
       <c r="M353" s="7"/>
       <c r="N353" s="7"/>
       <c r="O353" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P353" s="7"/>
       <c r="Q353" s="6"/>
       <c r="R353" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S353" s="7"/>
       <c r="T353" s="6"/>
@@ -17781,10 +17781,10 @@
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7" t="s">
-        <v>1468</v>
+        <v>1493</v>
       </c>
       <c r="G354" s="7" t="s">
-        <v>1485</v>
+        <v>1476</v>
       </c>
       <c r="H354" s="7" t="s">
         <v>31</v>
@@ -17796,12 +17796,12 @@
       <c r="M354" s="7"/>
       <c r="N354" s="7"/>
       <c r="O354" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P354" s="7"/>
       <c r="Q354" s="6"/>
       <c r="R354" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S354" s="7"/>
       <c r="T354" s="6"/>
@@ -17824,10 +17824,10 @@
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7" t="s">
-        <v>1469</v>
+        <v>1494</v>
       </c>
       <c r="G355" s="7" t="s">
-        <v>1486</v>
+        <v>1477</v>
       </c>
       <c r="H355" s="7" t="s">
         <v>31</v>
@@ -17839,12 +17839,12 @@
       <c r="M355" s="7"/>
       <c r="N355" s="7"/>
       <c r="O355" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P355" s="7"/>
       <c r="Q355" s="6"/>
       <c r="R355" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S355" s="7"/>
       <c r="T355" s="6"/>
@@ -17865,10 +17865,10 @@
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7" t="s">
-        <v>1470</v>
+        <v>1495</v>
       </c>
       <c r="G356" s="7" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
       <c r="H356" s="7" t="s">
         <v>31</v>
@@ -17880,12 +17880,12 @@
       <c r="M356" s="7"/>
       <c r="N356" s="7"/>
       <c r="O356" s="7" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="P356" s="7"/>
       <c r="Q356" s="6"/>
       <c r="R356" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S356" s="7"/>
       <c r="T356" s="6"/>
@@ -17910,7 +17910,7 @@
       <c r="J357" s="8"/>
       <c r="K357" s="7"/>
       <c r="L357" s="7" t="s">
-        <v>1488</v>
+        <v>1479</v>
       </c>
       <c r="M357" s="7"/>
       <c r="N357" s="7"/>
@@ -17918,7 +17918,7 @@
       <c r="P357" s="7"/>
       <c r="Q357" s="6"/>
       <c r="R357" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S357" s="7"/>
       <c r="T357" s="6"/>
@@ -17945,7 +17945,7 @@
       <c r="J358" s="8"/>
       <c r="K358" s="7"/>
       <c r="L358" s="7" t="s">
-        <v>1489</v>
+        <v>1480</v>
       </c>
       <c r="M358" s="7"/>
       <c r="N358" s="7"/>
@@ -17953,7 +17953,7 @@
       <c r="P358" s="7"/>
       <c r="Q358" s="6"/>
       <c r="R358" s="7" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="S358" s="7"/>
       <c r="T358" s="6"/>
@@ -35290,7 +35290,7 @@
       <formula1>"cover"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" sqref="O2:O1001" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="O2:O1001" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"arabic,armenian,bengali,cantonese,chinese-simplified,chinese-traditional,cyrillic,georgian,greek,hebrew,hindi,marathi,japanese,kannada,korean,malayalam,tamil,telugu,thai"</formula1>
     </dataValidation>
   </dataValidations>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B2214E-64A3-4DEB-8A87-6986F6D442C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A2D949-8430-4F4F-8DE1-AA0833C98B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="1625">
   <si>
     <t>artist</t>
   </si>
@@ -5014,6 +5014,393 @@
   </si>
   <si>
     <t>Zǐ-jīng</t>
+  </si>
+  <si>
+    <t>annika-herlitz</t>
+  </si>
+  <si>
+    <t>Herlitz</t>
+  </si>
+  <si>
+    <t>Annika</t>
+  </si>
+  <si>
+    <t>lucas-kruger</t>
+  </si>
+  <si>
+    <t>Krüger</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>david-alvefjord</t>
+  </si>
+  <si>
+    <t>Alvefjord</t>
+  </si>
+  <si>
+    <t>linda-ulvaeus</t>
+  </si>
+  <si>
+    <t>Ulvaeus</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>viva-ostervall-lyngbrant</t>
+  </si>
+  <si>
+    <t>Viva</t>
+  </si>
+  <si>
+    <t>adrian-maceus</t>
+  </si>
+  <si>
+    <t>Macéus</t>
+  </si>
+  <si>
+    <t>Adrian</t>
+  </si>
+  <si>
+    <t>valdemar-molino-sanchez</t>
+  </si>
+  <si>
+    <t>Valdemar</t>
+  </si>
+  <si>
+    <t>mia-benson</t>
+  </si>
+  <si>
+    <t>Benson</t>
+  </si>
+  <si>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>kajsa-reingardt</t>
+  </si>
+  <si>
+    <t>Reingardt</t>
+  </si>
+  <si>
+    <t>Kajsa</t>
+  </si>
+  <si>
+    <t>rolf-christianson</t>
+  </si>
+  <si>
+    <t>Christianson</t>
+  </si>
+  <si>
+    <t>Rolf</t>
+  </si>
+  <si>
+    <t>andreas-rothlin-svensson</t>
+  </si>
+  <si>
+    <t>Andreas</t>
+  </si>
+  <si>
+    <t>joachim-bergstrom</t>
+  </si>
+  <si>
+    <t>Bergström</t>
+  </si>
+  <si>
+    <t>Joachim</t>
+  </si>
+  <si>
+    <t>gustav-levin</t>
+  </si>
+  <si>
+    <t>Levin</t>
+  </si>
+  <si>
+    <t>Gustav</t>
+  </si>
+  <si>
+    <t>annica-risberg</t>
+  </si>
+  <si>
+    <t>Risberg</t>
+  </si>
+  <si>
+    <t>Annica</t>
+  </si>
+  <si>
+    <t>johan-hedenberg</t>
+  </si>
+  <si>
+    <t>Hedenberg</t>
+  </si>
+  <si>
+    <t>Johan</t>
+  </si>
+  <si>
+    <t>magnus-loftsson</t>
+  </si>
+  <si>
+    <t>Loftsson</t>
+  </si>
+  <si>
+    <t>Magnus</t>
+  </si>
+  <si>
+    <t>jennie-jahns</t>
+  </si>
+  <si>
+    <t>Jahns</t>
+  </si>
+  <si>
+    <t>Jennie</t>
+  </si>
+  <si>
+    <t>johan-karlsson</t>
+  </si>
+  <si>
+    <t>Karlsson</t>
+  </si>
+  <si>
+    <t>dick-eriksson</t>
+  </si>
+  <si>
+    <t>Eriksson</t>
+  </si>
+  <si>
+    <t>Dick</t>
+  </si>
+  <si>
+    <t>karolin-funke</t>
+  </si>
+  <si>
+    <t>Funke</t>
+  </si>
+  <si>
+    <t>Karolin</t>
+  </si>
+  <si>
+    <t>anette-belander</t>
+  </si>
+  <si>
+    <t>Belander</t>
+  </si>
+  <si>
+    <t>Anette</t>
+  </si>
+  <si>
+    <t>klara-nilsson</t>
+  </si>
+  <si>
+    <t>Nilsson</t>
+  </si>
+  <si>
+    <t>Klara</t>
+  </si>
+  <si>
+    <t>annica-edstam</t>
+  </si>
+  <si>
+    <t>Edstam</t>
+  </si>
+  <si>
+    <t>kristin-lidstrom</t>
+  </si>
+  <si>
+    <t>Lidström</t>
+  </si>
+  <si>
+    <t>Kristin</t>
+  </si>
+  <si>
+    <t>bengt-skogholt</t>
+  </si>
+  <si>
+    <t>Skogholt</t>
+  </si>
+  <si>
+    <t>Bengt</t>
+  </si>
+  <si>
+    <t>linus-eklund-adolphson</t>
+  </si>
+  <si>
+    <t>Linus</t>
+  </si>
+  <si>
+    <t>charlotte-ardai-jennefors</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>oskar-nilsson</t>
+  </si>
+  <si>
+    <t>Oskar</t>
+  </si>
+  <si>
+    <t>christian-fex</t>
+  </si>
+  <si>
+    <t>Fex</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>rikard-bjork</t>
+  </si>
+  <si>
+    <t>Björk</t>
+  </si>
+  <si>
+    <t>Rikard</t>
+  </si>
+  <si>
+    <t>christopher-wollter</t>
+  </si>
+  <si>
+    <t>Wollter</t>
+  </si>
+  <si>
+    <t>Christopher</t>
+  </si>
+  <si>
+    <t>therese-andersson-lewis</t>
+  </si>
+  <si>
+    <t>Thérèse</t>
+  </si>
+  <si>
+    <t>joakim-jennefors</t>
+  </si>
+  <si>
+    <t>Jennefors</t>
+  </si>
+  <si>
+    <t>Joakim</t>
+  </si>
+  <si>
+    <t>robert-cronholt</t>
+  </si>
+  <si>
+    <t>Cronholt</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>adam-vassee</t>
+  </si>
+  <si>
+    <t>Vassée</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>enny-ronnback</t>
+  </si>
+  <si>
+    <t>Rönnbäck</t>
+  </si>
+  <si>
+    <t>Enny</t>
+  </si>
+  <si>
+    <t>maria-hellstrom</t>
+  </si>
+  <si>
+    <t>Hellström</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>michael-rudolph</t>
+  </si>
+  <si>
+    <t>Rudolph</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>eric-broberg</t>
+  </si>
+  <si>
+    <t>Broberg</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>sdi-media-sweden</t>
+  </si>
+  <si>
+    <t>walt-disney-studios-motion-pictures-sweden-ab</t>
+  </si>
+  <si>
+    <t>Ardai</t>
+  </si>
+  <si>
+    <t>Andersson</t>
+  </si>
+  <si>
+    <t>Eklund</t>
+  </si>
+  <si>
+    <t>Adolphson</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>Lyngbrant</t>
+  </si>
+  <si>
+    <t>Östervall</t>
+  </si>
+  <si>
+    <t>Molino</t>
+  </si>
+  <si>
+    <t>Rothlin</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>Svensson</t>
+  </si>
+  <si>
+    <t>SDI Media Sweden</t>
+  </si>
+  <si>
+    <t>Walt Disney Studios Motion Pictures Sweden AB</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>David_Alvefjord.png</t>
+  </si>
+  <si>
+    <t>Lucas_Kruger.png</t>
+  </si>
+  <si>
+    <t>Annika_Herlitz.png</t>
+  </si>
+  <si>
+    <t>1984-09-22</t>
+  </si>
+  <si>
+    <t>1989-05-17</t>
+  </si>
+  <si>
+    <t>1986-03-07</t>
   </si>
 </sst>
 </file>
@@ -5501,8 +5888,8 @@
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -17914,7 +18301,9 @@
       </c>
       <c r="M357" s="7"/>
       <c r="N357" s="7"/>
-      <c r="O357" s="7"/>
+      <c r="O357" s="7" t="s">
+        <v>1481</v>
+      </c>
       <c r="P357" s="7"/>
       <c r="Q357" s="6"/>
       <c r="R357" s="7" t="s">
@@ -17949,7 +18338,9 @@
       </c>
       <c r="M358" s="7"/>
       <c r="N358" s="7"/>
-      <c r="O358" s="7"/>
+      <c r="O358" s="7" t="s">
+        <v>1481</v>
+      </c>
       <c r="P358" s="7"/>
       <c r="Q358" s="6"/>
       <c r="R358" s="7" t="s">
@@ -17966,12 +18357,18 @@
       <c r="Y358" s="6"/>
     </row>
     <row r="359" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A359" s="7"/>
+      <c r="A359" s="7" t="s">
+        <v>1496</v>
+      </c>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
-      <c r="D359" s="7"/>
+      <c r="D359" s="7" t="s">
+        <v>1497</v>
+      </c>
       <c r="E359" s="7"/>
-      <c r="F359" s="7"/>
+      <c r="F359" s="7" t="s">
+        <v>1498</v>
+      </c>
       <c r="G359" s="7"/>
       <c r="H359" s="7"/>
       <c r="I359" s="6"/>
@@ -17981,11 +18378,17 @@
       <c r="M359" s="7"/>
       <c r="N359" s="7"/>
       <c r="O359" s="7"/>
-      <c r="P359" s="7"/>
+      <c r="P359" s="7" t="s">
+        <v>1621</v>
+      </c>
       <c r="Q359" s="6"/>
-      <c r="R359" s="7"/>
+      <c r="R359" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S359" s="7"/>
-      <c r="T359" s="6"/>
+      <c r="T359" s="6" t="s">
+        <v>1622</v>
+      </c>
       <c r="U359" s="6"/>
       <c r="V359" s="7"/>
       <c r="W359" s="7"/>
@@ -17993,12 +18396,18 @@
       <c r="Y359" s="6"/>
     </row>
     <row r="360" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A360" s="7"/>
+      <c r="A360" s="7" t="s">
+        <v>1499</v>
+      </c>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
-      <c r="D360" s="7"/>
+      <c r="D360" s="7" t="s">
+        <v>1500</v>
+      </c>
       <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
+      <c r="F360" s="7" t="s">
+        <v>1501</v>
+      </c>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
       <c r="I360" s="6"/>
@@ -18008,11 +18417,17 @@
       <c r="M360" s="7"/>
       <c r="N360" s="7"/>
       <c r="O360" s="7"/>
-      <c r="P360" s="7"/>
+      <c r="P360" s="7" t="s">
+        <v>1620</v>
+      </c>
       <c r="Q360" s="6"/>
-      <c r="R360" s="7"/>
+      <c r="R360" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S360" s="7"/>
-      <c r="T360" s="6"/>
+      <c r="T360" s="6" t="s">
+        <v>1623</v>
+      </c>
       <c r="U360" s="6"/>
       <c r="V360" s="7"/>
       <c r="W360" s="7"/>
@@ -18020,12 +18435,18 @@
       <c r="Y360" s="6"/>
     </row>
     <row r="361" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A361" s="7"/>
+      <c r="A361" s="7" t="s">
+        <v>1502</v>
+      </c>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
-      <c r="D361" s="7"/>
+      <c r="D361" s="7" t="s">
+        <v>1503</v>
+      </c>
       <c r="E361" s="7"/>
-      <c r="F361" s="7"/>
+      <c r="F361" s="7" t="s">
+        <v>193</v>
+      </c>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
       <c r="I361" s="6"/>
@@ -18035,11 +18456,17 @@
       <c r="M361" s="7"/>
       <c r="N361" s="7"/>
       <c r="O361" s="7"/>
-      <c r="P361" s="7"/>
+      <c r="P361" s="7" t="s">
+        <v>1619</v>
+      </c>
       <c r="Q361" s="6"/>
-      <c r="R361" s="7"/>
+      <c r="R361" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S361" s="7"/>
-      <c r="T361" s="6"/>
+      <c r="T361" s="6" t="s">
+        <v>1624</v>
+      </c>
       <c r="U361" s="6"/>
       <c r="V361" s="7"/>
       <c r="W361" s="7"/>
@@ -18047,12 +18474,18 @@
       <c r="Y361" s="6"/>
     </row>
     <row r="362" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A362" s="7"/>
+      <c r="A362" s="7" t="s">
+        <v>1504</v>
+      </c>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
-      <c r="D362" s="7"/>
+      <c r="D362" s="7" t="s">
+        <v>1505</v>
+      </c>
       <c r="E362" s="7"/>
-      <c r="F362" s="7"/>
+      <c r="F362" s="7" t="s">
+        <v>1506</v>
+      </c>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
       <c r="I362" s="6"/>
@@ -18064,7 +18497,9 @@
       <c r="O362" s="7"/>
       <c r="P362" s="7"/>
       <c r="Q362" s="6"/>
-      <c r="R362" s="7"/>
+      <c r="R362" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S362" s="7"/>
       <c r="T362" s="6"/>
       <c r="U362" s="6"/>
@@ -18074,12 +18509,20 @@
       <c r="Y362" s="6"/>
     </row>
     <row r="363" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A363" s="7"/>
+      <c r="A363" s="7" t="s">
+        <v>1507</v>
+      </c>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
-      <c r="D363" s="7"/>
-      <c r="E363" s="7"/>
-      <c r="F363" s="7"/>
+      <c r="D363" s="7" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E363" s="7" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>1508</v>
+      </c>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
       <c r="I363" s="6"/>
@@ -18091,7 +18534,9 @@
       <c r="O363" s="7"/>
       <c r="P363" s="7"/>
       <c r="Q363" s="6"/>
-      <c r="R363" s="7"/>
+      <c r="R363" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S363" s="7"/>
       <c r="T363" s="6"/>
       <c r="U363" s="6"/>
@@ -18101,12 +18546,18 @@
       <c r="Y363" s="6"/>
     </row>
     <row r="364" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A364" s="7"/>
+      <c r="A364" s="7" t="s">
+        <v>1509</v>
+      </c>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
-      <c r="D364" s="7"/>
+      <c r="D364" s="7" t="s">
+        <v>1510</v>
+      </c>
       <c r="E364" s="7"/>
-      <c r="F364" s="7"/>
+      <c r="F364" s="7" t="s">
+        <v>1511</v>
+      </c>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
       <c r="I364" s="6"/>
@@ -18118,7 +18569,9 @@
       <c r="O364" s="7"/>
       <c r="P364" s="7"/>
       <c r="Q364" s="6"/>
-      <c r="R364" s="7"/>
+      <c r="R364" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S364" s="7"/>
       <c r="T364" s="6"/>
       <c r="U364" s="6"/>
@@ -18128,12 +18581,20 @@
       <c r="Y364" s="6"/>
     </row>
     <row r="365" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A365" s="7"/>
+      <c r="A365" s="7" t="s">
+        <v>1512</v>
+      </c>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
-      <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
-      <c r="F365" s="7"/>
+      <c r="D365" s="7" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>1513</v>
+      </c>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
       <c r="I365" s="6"/>
@@ -18145,7 +18606,9 @@
       <c r="O365" s="7"/>
       <c r="P365" s="7"/>
       <c r="Q365" s="6"/>
-      <c r="R365" s="7"/>
+      <c r="R365" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S365" s="7"/>
       <c r="T365" s="6"/>
       <c r="U365" s="6"/>
@@ -18155,12 +18618,18 @@
       <c r="Y365" s="6"/>
     </row>
     <row r="366" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A366" s="7"/>
+      <c r="A366" s="7" t="s">
+        <v>1514</v>
+      </c>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
-      <c r="D366" s="7"/>
+      <c r="D366" s="7" t="s">
+        <v>1515</v>
+      </c>
       <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
+      <c r="F366" s="7" t="s">
+        <v>1516</v>
+      </c>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
       <c r="I366" s="6"/>
@@ -18172,7 +18641,9 @@
       <c r="O366" s="7"/>
       <c r="P366" s="7"/>
       <c r="Q366" s="6"/>
-      <c r="R366" s="7"/>
+      <c r="R366" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S366" s="7"/>
       <c r="T366" s="6"/>
       <c r="U366" s="6"/>
@@ -18182,12 +18653,18 @@
       <c r="Y366" s="6"/>
     </row>
     <row r="367" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A367" s="7"/>
+      <c r="A367" s="7" t="s">
+        <v>1517</v>
+      </c>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
-      <c r="D367" s="7"/>
+      <c r="D367" s="7" t="s">
+        <v>1518</v>
+      </c>
       <c r="E367" s="7"/>
-      <c r="F367" s="7"/>
+      <c r="F367" s="7" t="s">
+        <v>1519</v>
+      </c>
       <c r="G367" s="7"/>
       <c r="H367" s="7"/>
       <c r="I367" s="6"/>
@@ -18199,7 +18676,9 @@
       <c r="O367" s="7"/>
       <c r="P367" s="7"/>
       <c r="Q367" s="6"/>
-      <c r="R367" s="7"/>
+      <c r="R367" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S367" s="7"/>
       <c r="T367" s="6"/>
       <c r="U367" s="6"/>
@@ -18209,12 +18688,18 @@
       <c r="Y367" s="6"/>
     </row>
     <row r="368" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A368" s="7"/>
+      <c r="A368" s="7" t="s">
+        <v>1520</v>
+      </c>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
-      <c r="D368" s="7"/>
+      <c r="D368" s="7" t="s">
+        <v>1521</v>
+      </c>
       <c r="E368" s="7"/>
-      <c r="F368" s="7"/>
+      <c r="F368" s="7" t="s">
+        <v>1522</v>
+      </c>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
       <c r="I368" s="6"/>
@@ -18226,7 +18711,9 @@
       <c r="O368" s="7"/>
       <c r="P368" s="7"/>
       <c r="Q368" s="6"/>
-      <c r="R368" s="7"/>
+      <c r="R368" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S368" s="7"/>
       <c r="T368" s="6"/>
       <c r="U368" s="6"/>
@@ -18236,12 +18723,20 @@
       <c r="Y368" s="6"/>
     </row>
     <row r="369" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A369" s="7"/>
+      <c r="A369" s="7" t="s">
+        <v>1523</v>
+      </c>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
-      <c r="D369" s="7"/>
-      <c r="E369" s="7"/>
-      <c r="F369" s="7"/>
+      <c r="D369" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E369" s="7" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>1524</v>
+      </c>
       <c r="G369" s="7"/>
       <c r="H369" s="7"/>
       <c r="I369" s="6"/>
@@ -18253,7 +18748,9 @@
       <c r="O369" s="7"/>
       <c r="P369" s="7"/>
       <c r="Q369" s="6"/>
-      <c r="R369" s="7"/>
+      <c r="R369" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S369" s="7"/>
       <c r="T369" s="6"/>
       <c r="U369" s="6"/>
@@ -18263,12 +18760,18 @@
       <c r="Y369" s="6"/>
     </row>
     <row r="370" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A370" s="7"/>
+      <c r="A370" s="7" t="s">
+        <v>1525</v>
+      </c>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
-      <c r="D370" s="7"/>
+      <c r="D370" s="7" t="s">
+        <v>1526</v>
+      </c>
       <c r="E370" s="7"/>
-      <c r="F370" s="7"/>
+      <c r="F370" s="7" t="s">
+        <v>1527</v>
+      </c>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
       <c r="I370" s="6"/>
@@ -18280,7 +18783,9 @@
       <c r="O370" s="7"/>
       <c r="P370" s="7"/>
       <c r="Q370" s="6"/>
-      <c r="R370" s="7"/>
+      <c r="R370" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S370" s="7"/>
       <c r="T370" s="6"/>
       <c r="U370" s="6"/>
@@ -18290,12 +18795,18 @@
       <c r="Y370" s="6"/>
     </row>
     <row r="371" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A371" s="7"/>
+      <c r="A371" s="7" t="s">
+        <v>1528</v>
+      </c>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
-      <c r="D371" s="7"/>
+      <c r="D371" s="7" t="s">
+        <v>1529</v>
+      </c>
       <c r="E371" s="7"/>
-      <c r="F371" s="7"/>
+      <c r="F371" s="7" t="s">
+        <v>1530</v>
+      </c>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
       <c r="I371" s="6"/>
@@ -18307,7 +18818,9 @@
       <c r="O371" s="7"/>
       <c r="P371" s="7"/>
       <c r="Q371" s="6"/>
-      <c r="R371" s="7"/>
+      <c r="R371" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S371" s="7"/>
       <c r="T371" s="6"/>
       <c r="U371" s="6"/>
@@ -18317,12 +18830,18 @@
       <c r="Y371" s="6"/>
     </row>
     <row r="372" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A372" s="7"/>
+      <c r="A372" s="7" t="s">
+        <v>1531</v>
+      </c>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
-      <c r="D372" s="7"/>
+      <c r="D372" s="7" t="s">
+        <v>1532</v>
+      </c>
       <c r="E372" s="7"/>
-      <c r="F372" s="7"/>
+      <c r="F372" s="7" t="s">
+        <v>1533</v>
+      </c>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
       <c r="I372" s="6"/>
@@ -18334,7 +18853,9 @@
       <c r="O372" s="7"/>
       <c r="P372" s="7"/>
       <c r="Q372" s="6"/>
-      <c r="R372" s="7"/>
+      <c r="R372" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S372" s="7"/>
       <c r="T372" s="6"/>
       <c r="U372" s="6"/>
@@ -18344,12 +18865,18 @@
       <c r="Y372" s="6"/>
     </row>
     <row r="373" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A373" s="7"/>
+      <c r="A373" s="7" t="s">
+        <v>1534</v>
+      </c>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
-      <c r="D373" s="7"/>
+      <c r="D373" s="7" t="s">
+        <v>1535</v>
+      </c>
       <c r="E373" s="7"/>
-      <c r="F373" s="7"/>
+      <c r="F373" s="7" t="s">
+        <v>1536</v>
+      </c>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
       <c r="I373" s="6"/>
@@ -18361,7 +18888,9 @@
       <c r="O373" s="7"/>
       <c r="P373" s="7"/>
       <c r="Q373" s="6"/>
-      <c r="R373" s="7"/>
+      <c r="R373" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S373" s="7"/>
       <c r="T373" s="6"/>
       <c r="U373" s="6"/>
@@ -18371,12 +18900,18 @@
       <c r="Y373" s="6"/>
     </row>
     <row r="374" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A374" s="7"/>
+      <c r="A374" s="7" t="s">
+        <v>1537</v>
+      </c>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
-      <c r="D374" s="7"/>
+      <c r="D374" s="7" t="s">
+        <v>1538</v>
+      </c>
       <c r="E374" s="7"/>
-      <c r="F374" s="7"/>
+      <c r="F374" s="7" t="s">
+        <v>1539</v>
+      </c>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
       <c r="I374" s="6"/>
@@ -18388,7 +18923,9 @@
       <c r="O374" s="7"/>
       <c r="P374" s="7"/>
       <c r="Q374" s="6"/>
-      <c r="R374" s="7"/>
+      <c r="R374" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S374" s="7"/>
       <c r="T374" s="6"/>
       <c r="U374" s="6"/>
@@ -18398,12 +18935,18 @@
       <c r="Y374" s="6"/>
     </row>
     <row r="375" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A375" s="7"/>
+      <c r="A375" s="7" t="s">
+        <v>1540</v>
+      </c>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
-      <c r="D375" s="7"/>
+      <c r="D375" s="7" t="s">
+        <v>1541</v>
+      </c>
       <c r="E375" s="7"/>
-      <c r="F375" s="7"/>
+      <c r="F375" s="7" t="s">
+        <v>1542</v>
+      </c>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
       <c r="I375" s="6"/>
@@ -18415,7 +18958,9 @@
       <c r="O375" s="7"/>
       <c r="P375" s="7"/>
       <c r="Q375" s="6"/>
-      <c r="R375" s="7"/>
+      <c r="R375" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S375" s="7"/>
       <c r="T375" s="6"/>
       <c r="U375" s="6"/>
@@ -18425,12 +18970,18 @@
       <c r="Y375" s="6"/>
     </row>
     <row r="376" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A376" s="7"/>
+      <c r="A376" s="7" t="s">
+        <v>1543</v>
+      </c>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
-      <c r="D376" s="7"/>
+      <c r="D376" s="7" t="s">
+        <v>1544</v>
+      </c>
       <c r="E376" s="7"/>
-      <c r="F376" s="7"/>
+      <c r="F376" s="7" t="s">
+        <v>1536</v>
+      </c>
       <c r="G376" s="7"/>
       <c r="H376" s="7"/>
       <c r="I376" s="6"/>
@@ -18442,7 +18993,9 @@
       <c r="O376" s="7"/>
       <c r="P376" s="7"/>
       <c r="Q376" s="6"/>
-      <c r="R376" s="7"/>
+      <c r="R376" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S376" s="7"/>
       <c r="T376" s="6"/>
       <c r="U376" s="6"/>
@@ -18452,12 +19005,18 @@
       <c r="Y376" s="6"/>
     </row>
     <row r="377" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A377" s="7"/>
+      <c r="A377" s="7" t="s">
+        <v>1545</v>
+      </c>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
-      <c r="D377" s="7"/>
+      <c r="D377" s="7" t="s">
+        <v>1546</v>
+      </c>
       <c r="E377" s="7"/>
-      <c r="F377" s="7"/>
+      <c r="F377" s="7" t="s">
+        <v>1547</v>
+      </c>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
       <c r="I377" s="6"/>
@@ -18469,7 +19028,9 @@
       <c r="O377" s="7"/>
       <c r="P377" s="7"/>
       <c r="Q377" s="6"/>
-      <c r="R377" s="7"/>
+      <c r="R377" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S377" s="7"/>
       <c r="T377" s="6"/>
       <c r="U377" s="6"/>
@@ -18479,12 +19040,18 @@
       <c r="Y377" s="6"/>
     </row>
     <row r="378" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A378" s="7"/>
+      <c r="A378" s="7" t="s">
+        <v>1548</v>
+      </c>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
-      <c r="D378" s="7"/>
+      <c r="D378" s="7" t="s">
+        <v>1549</v>
+      </c>
       <c r="E378" s="7"/>
-      <c r="F378" s="7"/>
+      <c r="F378" s="7" t="s">
+        <v>1550</v>
+      </c>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
       <c r="I378" s="6"/>
@@ -18496,7 +19063,9 @@
       <c r="O378" s="7"/>
       <c r="P378" s="7"/>
       <c r="Q378" s="6"/>
-      <c r="R378" s="7"/>
+      <c r="R378" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S378" s="7"/>
       <c r="T378" s="6"/>
       <c r="U378" s="6"/>
@@ -18506,12 +19075,18 @@
       <c r="Y378" s="6"/>
     </row>
     <row r="379" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A379" s="7"/>
+      <c r="A379" s="7" t="s">
+        <v>1551</v>
+      </c>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
-      <c r="D379" s="7"/>
+      <c r="D379" s="7" t="s">
+        <v>1552</v>
+      </c>
       <c r="E379" s="7"/>
-      <c r="F379" s="7"/>
+      <c r="F379" s="7" t="s">
+        <v>1553</v>
+      </c>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
       <c r="I379" s="6"/>
@@ -18523,7 +19098,9 @@
       <c r="O379" s="7"/>
       <c r="P379" s="7"/>
       <c r="Q379" s="6"/>
-      <c r="R379" s="7"/>
+      <c r="R379" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S379" s="7"/>
       <c r="T379" s="6"/>
       <c r="U379" s="6"/>
@@ -18533,12 +19110,18 @@
       <c r="Y379" s="6"/>
     </row>
     <row r="380" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A380" s="7"/>
+      <c r="A380" s="7" t="s">
+        <v>1554</v>
+      </c>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
-      <c r="D380" s="7"/>
+      <c r="D380" s="7" t="s">
+        <v>1555</v>
+      </c>
       <c r="E380" s="7"/>
-      <c r="F380" s="7"/>
+      <c r="F380" s="7" t="s">
+        <v>1556</v>
+      </c>
       <c r="G380" s="7"/>
       <c r="H380" s="7"/>
       <c r="I380" s="6"/>
@@ -18550,7 +19133,9 @@
       <c r="O380" s="7"/>
       <c r="P380" s="7"/>
       <c r="Q380" s="6"/>
-      <c r="R380" s="7"/>
+      <c r="R380" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S380" s="7"/>
       <c r="T380" s="6"/>
       <c r="U380" s="6"/>
@@ -18560,12 +19145,18 @@
       <c r="Y380" s="6"/>
     </row>
     <row r="381" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A381" s="7"/>
+      <c r="A381" s="7" t="s">
+        <v>1557</v>
+      </c>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
-      <c r="D381" s="7"/>
+      <c r="D381" s="7" t="s">
+        <v>1558</v>
+      </c>
       <c r="E381" s="7"/>
-      <c r="F381" s="7"/>
+      <c r="F381" s="7" t="s">
+        <v>1533</v>
+      </c>
       <c r="G381" s="7"/>
       <c r="H381" s="7"/>
       <c r="I381" s="6"/>
@@ -18577,7 +19168,9 @@
       <c r="O381" s="7"/>
       <c r="P381" s="7"/>
       <c r="Q381" s="6"/>
-      <c r="R381" s="7"/>
+      <c r="R381" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S381" s="7"/>
       <c r="T381" s="6"/>
       <c r="U381" s="6"/>
@@ -18587,12 +19180,18 @@
       <c r="Y381" s="6"/>
     </row>
     <row r="382" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A382" s="7"/>
+      <c r="A382" s="7" t="s">
+        <v>1559</v>
+      </c>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
-      <c r="D382" s="7"/>
+      <c r="D382" s="7" t="s">
+        <v>1560</v>
+      </c>
       <c r="E382" s="7"/>
-      <c r="F382" s="7"/>
+      <c r="F382" s="7" t="s">
+        <v>1561</v>
+      </c>
       <c r="G382" s="7"/>
       <c r="H382" s="7"/>
       <c r="I382" s="6"/>
@@ -18604,7 +19203,9 @@
       <c r="O382" s="7"/>
       <c r="P382" s="7"/>
       <c r="Q382" s="6"/>
-      <c r="R382" s="7"/>
+      <c r="R382" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S382" s="7"/>
       <c r="T382" s="6"/>
       <c r="U382" s="6"/>
@@ -18614,12 +19215,18 @@
       <c r="Y382" s="6"/>
     </row>
     <row r="383" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A383" s="7"/>
+      <c r="A383" s="7" t="s">
+        <v>1562</v>
+      </c>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
-      <c r="D383" s="7"/>
+      <c r="D383" s="7" t="s">
+        <v>1563</v>
+      </c>
       <c r="E383" s="7"/>
-      <c r="F383" s="7"/>
+      <c r="F383" s="7" t="s">
+        <v>1564</v>
+      </c>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
       <c r="I383" s="6"/>
@@ -18631,7 +19238,9 @@
       <c r="O383" s="7"/>
       <c r="P383" s="7"/>
       <c r="Q383" s="6"/>
-      <c r="R383" s="7"/>
+      <c r="R383" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S383" s="7"/>
       <c r="T383" s="6"/>
       <c r="U383" s="6"/>
@@ -18641,12 +19250,20 @@
       <c r="Y383" s="6"/>
     </row>
     <row r="384" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A384" s="7"/>
+      <c r="A384" s="7" t="s">
+        <v>1565</v>
+      </c>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
-      <c r="D384" s="7"/>
-      <c r="E384" s="7"/>
-      <c r="F384" s="7"/>
+      <c r="D384" s="7" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F384" s="7" t="s">
+        <v>1566</v>
+      </c>
       <c r="G384" s="7"/>
       <c r="H384" s="7"/>
       <c r="I384" s="6"/>
@@ -18658,7 +19275,9 @@
       <c r="O384" s="7"/>
       <c r="P384" s="7"/>
       <c r="Q384" s="6"/>
-      <c r="R384" s="7"/>
+      <c r="R384" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S384" s="7"/>
       <c r="T384" s="6"/>
       <c r="U384" s="6"/>
@@ -18668,12 +19287,20 @@
       <c r="Y384" s="6"/>
     </row>
     <row r="385" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A385" s="7"/>
+      <c r="A385" s="7" t="s">
+        <v>1567</v>
+      </c>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
-      <c r="D385" s="7"/>
-      <c r="E385" s="7"/>
-      <c r="F385" s="7"/>
+      <c r="D385" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>1568</v>
+      </c>
       <c r="G385" s="7"/>
       <c r="H385" s="7"/>
       <c r="I385" s="6"/>
@@ -18685,7 +19312,9 @@
       <c r="O385" s="7"/>
       <c r="P385" s="7"/>
       <c r="Q385" s="6"/>
-      <c r="R385" s="7"/>
+      <c r="R385" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S385" s="7"/>
       <c r="T385" s="6"/>
       <c r="U385" s="6"/>
@@ -18695,12 +19324,18 @@
       <c r="Y385" s="6"/>
     </row>
     <row r="386" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A386" s="7"/>
+      <c r="A386" s="7" t="s">
+        <v>1569</v>
+      </c>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
-      <c r="D386" s="7"/>
+      <c r="D386" s="7" t="s">
+        <v>1555</v>
+      </c>
       <c r="E386" s="7"/>
-      <c r="F386" s="7"/>
+      <c r="F386" s="7" t="s">
+        <v>1570</v>
+      </c>
       <c r="G386" s="7"/>
       <c r="H386" s="7"/>
       <c r="I386" s="6"/>
@@ -18712,7 +19347,9 @@
       <c r="O386" s="7"/>
       <c r="P386" s="7"/>
       <c r="Q386" s="6"/>
-      <c r="R386" s="7"/>
+      <c r="R386" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S386" s="7"/>
       <c r="T386" s="6"/>
       <c r="U386" s="6"/>
@@ -18722,12 +19359,18 @@
       <c r="Y386" s="6"/>
     </row>
     <row r="387" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A387" s="7"/>
+      <c r="A387" s="7" t="s">
+        <v>1571</v>
+      </c>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
-      <c r="D387" s="7"/>
+      <c r="D387" s="7" t="s">
+        <v>1572</v>
+      </c>
       <c r="E387" s="7"/>
-      <c r="F387" s="7"/>
+      <c r="F387" s="7" t="s">
+        <v>1573</v>
+      </c>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
       <c r="I387" s="6"/>
@@ -18739,7 +19382,9 @@
       <c r="O387" s="7"/>
       <c r="P387" s="7"/>
       <c r="Q387" s="6"/>
-      <c r="R387" s="7"/>
+      <c r="R387" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S387" s="7"/>
       <c r="T387" s="6"/>
       <c r="U387" s="6"/>
@@ -18749,12 +19394,18 @@
       <c r="Y387" s="6"/>
     </row>
     <row r="388" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A388" s="7"/>
+      <c r="A388" s="7" t="s">
+        <v>1574</v>
+      </c>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
-      <c r="D388" s="7"/>
+      <c r="D388" s="7" t="s">
+        <v>1575</v>
+      </c>
       <c r="E388" s="7"/>
-      <c r="F388" s="7"/>
+      <c r="F388" s="7" t="s">
+        <v>1576</v>
+      </c>
       <c r="G388" s="7"/>
       <c r="H388" s="7"/>
       <c r="I388" s="6"/>
@@ -18766,7 +19417,9 @@
       <c r="O388" s="7"/>
       <c r="P388" s="7"/>
       <c r="Q388" s="6"/>
-      <c r="R388" s="7"/>
+      <c r="R388" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S388" s="7"/>
       <c r="T388" s="6"/>
       <c r="U388" s="6"/>
@@ -18776,12 +19429,18 @@
       <c r="Y388" s="6"/>
     </row>
     <row r="389" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A389" s="7"/>
+      <c r="A389" s="7" t="s">
+        <v>1577</v>
+      </c>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
-      <c r="D389" s="7"/>
+      <c r="D389" s="7" t="s">
+        <v>1578</v>
+      </c>
       <c r="E389" s="7"/>
-      <c r="F389" s="7"/>
+      <c r="F389" s="7" t="s">
+        <v>1579</v>
+      </c>
       <c r="G389" s="7"/>
       <c r="H389" s="7"/>
       <c r="I389" s="6"/>
@@ -18793,7 +19452,9 @@
       <c r="O389" s="7"/>
       <c r="P389" s="7"/>
       <c r="Q389" s="6"/>
-      <c r="R389" s="7"/>
+      <c r="R389" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S389" s="7"/>
       <c r="T389" s="6"/>
       <c r="U389" s="6"/>
@@ -18803,12 +19464,20 @@
       <c r="Y389" s="6"/>
     </row>
     <row r="390" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A390" s="7"/>
+      <c r="A390" s="7" t="s">
+        <v>1580</v>
+      </c>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
-      <c r="D390" s="7"/>
-      <c r="E390" s="7"/>
-      <c r="F390" s="7"/>
+      <c r="D390" s="7" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E390" s="7" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F390" s="7" t="s">
+        <v>1581</v>
+      </c>
       <c r="G390" s="7"/>
       <c r="H390" s="7"/>
       <c r="I390" s="6"/>
@@ -18820,7 +19489,9 @@
       <c r="O390" s="7"/>
       <c r="P390" s="7"/>
       <c r="Q390" s="6"/>
-      <c r="R390" s="7"/>
+      <c r="R390" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S390" s="7"/>
       <c r="T390" s="6"/>
       <c r="U390" s="6"/>
@@ -18830,12 +19501,18 @@
       <c r="Y390" s="6"/>
     </row>
     <row r="391" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A391" s="7"/>
+      <c r="A391" s="7" t="s">
+        <v>1582</v>
+      </c>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
-      <c r="D391" s="7"/>
+      <c r="D391" s="7" t="s">
+        <v>1583</v>
+      </c>
       <c r="E391" s="7"/>
-      <c r="F391" s="7"/>
+      <c r="F391" s="7" t="s">
+        <v>1584</v>
+      </c>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
       <c r="I391" s="6"/>
@@ -18847,7 +19524,9 @@
       <c r="O391" s="7"/>
       <c r="P391" s="7"/>
       <c r="Q391" s="6"/>
-      <c r="R391" s="7"/>
+      <c r="R391" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S391" s="7"/>
       <c r="T391" s="6"/>
       <c r="U391" s="6"/>
@@ -18857,12 +19536,18 @@
       <c r="Y391" s="6"/>
     </row>
     <row r="392" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A392" s="7"/>
+      <c r="A392" s="7" t="s">
+        <v>1585</v>
+      </c>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
-      <c r="D392" s="7"/>
+      <c r="D392" s="7" t="s">
+        <v>1586</v>
+      </c>
       <c r="E392" s="7"/>
-      <c r="F392" s="7"/>
+      <c r="F392" s="7" t="s">
+        <v>1587</v>
+      </c>
       <c r="G392" s="7"/>
       <c r="H392" s="7"/>
       <c r="I392" s="6"/>
@@ -18874,7 +19559,9 @@
       <c r="O392" s="7"/>
       <c r="P392" s="7"/>
       <c r="Q392" s="6"/>
-      <c r="R392" s="7"/>
+      <c r="R392" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S392" s="7"/>
       <c r="T392" s="6"/>
       <c r="U392" s="6"/>
@@ -18884,12 +19571,18 @@
       <c r="Y392" s="6"/>
     </row>
     <row r="393" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A393" s="7"/>
+      <c r="A393" s="7" t="s">
+        <v>1588</v>
+      </c>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
-      <c r="D393" s="7"/>
+      <c r="D393" s="7" t="s">
+        <v>1589</v>
+      </c>
       <c r="E393" s="7"/>
-      <c r="F393" s="7"/>
+      <c r="F393" s="7" t="s">
+        <v>1590</v>
+      </c>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
       <c r="I393" s="6"/>
@@ -18901,7 +19594,9 @@
       <c r="O393" s="7"/>
       <c r="P393" s="7"/>
       <c r="Q393" s="6"/>
-      <c r="R393" s="7"/>
+      <c r="R393" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S393" s="7"/>
       <c r="T393" s="6"/>
       <c r="U393" s="6"/>
@@ -18911,12 +19606,18 @@
       <c r="Y393" s="6"/>
     </row>
     <row r="394" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A394" s="7"/>
+      <c r="A394" s="7" t="s">
+        <v>1591</v>
+      </c>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
-      <c r="D394" s="7"/>
+      <c r="D394" s="7" t="s">
+        <v>1592</v>
+      </c>
       <c r="E394" s="7"/>
-      <c r="F394" s="7"/>
+      <c r="F394" s="7" t="s">
+        <v>1593</v>
+      </c>
       <c r="G394" s="7"/>
       <c r="H394" s="7"/>
       <c r="I394" s="6"/>
@@ -18928,7 +19629,9 @@
       <c r="O394" s="7"/>
       <c r="P394" s="7"/>
       <c r="Q394" s="6"/>
-      <c r="R394" s="7"/>
+      <c r="R394" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S394" s="7"/>
       <c r="T394" s="6"/>
       <c r="U394" s="6"/>
@@ -18938,12 +19641,18 @@
       <c r="Y394" s="6"/>
     </row>
     <row r="395" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A395" s="7"/>
+      <c r="A395" s="7" t="s">
+        <v>1594</v>
+      </c>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
-      <c r="D395" s="7"/>
+      <c r="D395" s="7" t="s">
+        <v>1595</v>
+      </c>
       <c r="E395" s="7"/>
-      <c r="F395" s="7"/>
+      <c r="F395" s="7" t="s">
+        <v>1596</v>
+      </c>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
       <c r="I395" s="6"/>
@@ -18955,7 +19664,9 @@
       <c r="O395" s="7"/>
       <c r="P395" s="7"/>
       <c r="Q395" s="6"/>
-      <c r="R395" s="7"/>
+      <c r="R395" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S395" s="7"/>
       <c r="T395" s="6"/>
       <c r="U395" s="6"/>
@@ -18965,12 +19676,18 @@
       <c r="Y395" s="6"/>
     </row>
     <row r="396" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A396" s="7"/>
+      <c r="A396" s="7" t="s">
+        <v>1597</v>
+      </c>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
-      <c r="D396" s="7"/>
+      <c r="D396" s="7" t="s">
+        <v>1598</v>
+      </c>
       <c r="E396" s="7"/>
-      <c r="F396" s="7"/>
+      <c r="F396" s="7" t="s">
+        <v>1599</v>
+      </c>
       <c r="G396" s="7"/>
       <c r="H396" s="7"/>
       <c r="I396" s="6"/>
@@ -18982,7 +19699,9 @@
       <c r="O396" s="7"/>
       <c r="P396" s="7"/>
       <c r="Q396" s="6"/>
-      <c r="R396" s="7"/>
+      <c r="R396" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S396" s="7"/>
       <c r="T396" s="6"/>
       <c r="U396" s="6"/>
@@ -18992,12 +19711,18 @@
       <c r="Y396" s="6"/>
     </row>
     <row r="397" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A397" s="7"/>
+      <c r="A397" s="7" t="s">
+        <v>1600</v>
+      </c>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
-      <c r="D397" s="7"/>
+      <c r="D397" s="7" t="s">
+        <v>1601</v>
+      </c>
       <c r="E397" s="7"/>
-      <c r="F397" s="7"/>
+      <c r="F397" s="7" t="s">
+        <v>1602</v>
+      </c>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
       <c r="I397" s="6"/>
@@ -19009,7 +19734,9 @@
       <c r="O397" s="7"/>
       <c r="P397" s="7"/>
       <c r="Q397" s="6"/>
-      <c r="R397" s="7"/>
+      <c r="R397" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S397" s="7"/>
       <c r="T397" s="6"/>
       <c r="U397" s="6"/>
@@ -19019,7 +19746,9 @@
       <c r="Y397" s="6"/>
     </row>
     <row r="398" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A398" s="7"/>
+      <c r="A398" s="7" t="s">
+        <v>1603</v>
+      </c>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
       <c r="D398" s="7"/>
@@ -19030,23 +19759,31 @@
       <c r="I398" s="6"/>
       <c r="J398" s="8"/>
       <c r="K398" s="7"/>
-      <c r="L398" s="7"/>
+      <c r="L398" s="7" t="s">
+        <v>1616</v>
+      </c>
       <c r="M398" s="7"/>
       <c r="N398" s="7"/>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
       <c r="Q398" s="6"/>
-      <c r="R398" s="7"/>
+      <c r="R398" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S398" s="7"/>
       <c r="T398" s="6"/>
       <c r="U398" s="6"/>
-      <c r="V398" s="7"/>
+      <c r="V398" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="W398" s="7"/>
       <c r="X398" s="6"/>
       <c r="Y398" s="6"/>
     </row>
     <row r="399" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A399" s="7"/>
+      <c r="A399" s="7" t="s">
+        <v>1604</v>
+      </c>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
       <c r="D399" s="7"/>
@@ -19057,17 +19794,23 @@
       <c r="I399" s="6"/>
       <c r="J399" s="8"/>
       <c r="K399" s="7"/>
-      <c r="L399" s="7"/>
+      <c r="L399" s="7" t="s">
+        <v>1617</v>
+      </c>
       <c r="M399" s="7"/>
       <c r="N399" s="7"/>
       <c r="O399" s="7"/>
       <c r="P399" s="7"/>
       <c r="Q399" s="6"/>
-      <c r="R399" s="7"/>
+      <c r="R399" s="7" t="s">
+        <v>1618</v>
+      </c>
       <c r="S399" s="7"/>
       <c r="T399" s="6"/>
       <c r="U399" s="6"/>
-      <c r="V399" s="7"/>
+      <c r="V399" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="W399" s="7"/>
       <c r="X399" s="6"/>
       <c r="Y399" s="6"/>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03809EDA-6A93-4161-9A12-E0522682573B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7D292-1028-414F-9E96-156EDBFA4EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="1932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="1940">
   <si>
     <t>artist</t>
   </si>
@@ -6382,6 +6382,30 @@
   </si>
   <si>
     <t xml:space="preserve">1986 - </t>
+  </si>
+  <si>
+    <t>ute-becker</t>
+  </si>
+  <si>
+    <t>Becker</t>
+  </si>
+  <si>
+    <t>Ute</t>
+  </si>
+  <si>
+    <t>Ute_Becker.png</t>
+  </si>
+  <si>
+    <t>thomas-zaufke</t>
+  </si>
+  <si>
+    <t>Zaufke</t>
+  </si>
+  <si>
+    <t>Thomas_Zaufke.png</t>
+  </si>
+  <si>
+    <t>1966-12-11</t>
   </si>
 </sst>
 </file>
@@ -7395,7 +7419,7 @@
       <c r="Y11" s="8"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>80</v>
       </c>
@@ -23536,12 +23560,18 @@
       <c r="Y469" s="6"/>
     </row>
     <row r="470" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A470" s="7"/>
+      <c r="A470" s="7" t="s">
+        <v>1932</v>
+      </c>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
-      <c r="D470" s="7"/>
+      <c r="D470" s="7" t="s">
+        <v>1933</v>
+      </c>
       <c r="E470" s="7"/>
-      <c r="F470" s="7"/>
+      <c r="F470" s="7" t="s">
+        <v>1934</v>
+      </c>
       <c r="G470" s="7"/>
       <c r="H470" s="7"/>
       <c r="I470" s="6"/>
@@ -23551,9 +23581,13 @@
       <c r="M470" s="7"/>
       <c r="N470" s="7"/>
       <c r="O470" s="7"/>
-      <c r="P470" s="7"/>
+      <c r="P470" s="7" t="s">
+        <v>1935</v>
+      </c>
       <c r="Q470" s="6"/>
-      <c r="R470" s="7"/>
+      <c r="R470" s="7" t="s">
+        <v>1874</v>
+      </c>
       <c r="S470" s="7"/>
       <c r="T470" s="6"/>
       <c r="U470" s="6"/>
@@ -23563,12 +23597,18 @@
       <c r="Y470" s="6"/>
     </row>
     <row r="471" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A471" s="7"/>
+      <c r="A471" s="7" t="s">
+        <v>1936</v>
+      </c>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
-      <c r="D471" s="7"/>
+      <c r="D471" s="7" t="s">
+        <v>1937</v>
+      </c>
       <c r="E471" s="7"/>
-      <c r="F471" s="7"/>
+      <c r="F471" s="7" t="s">
+        <v>1909</v>
+      </c>
       <c r="G471" s="7"/>
       <c r="H471" s="7"/>
       <c r="I471" s="6"/>
@@ -23578,10 +23618,16 @@
       <c r="M471" s="7"/>
       <c r="N471" s="7"/>
       <c r="O471" s="7"/>
-      <c r="P471" s="7"/>
+      <c r="P471" s="7" t="s">
+        <v>1938</v>
+      </c>
       <c r="Q471" s="6"/>
-      <c r="R471" s="7"/>
-      <c r="S471" s="7"/>
+      <c r="R471" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="S471" s="7" t="s">
+        <v>1939</v>
+      </c>
       <c r="T471" s="6"/>
       <c r="U471" s="6"/>
       <c r="V471" s="7"/>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7D292-1028-414F-9E96-156EDBFA4EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6759F92F-C567-4ADB-A89A-B6391D974B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="1940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="2012">
   <si>
     <t>artist</t>
   </si>
@@ -6406,6 +6406,223 @@
   </si>
   <si>
     <t>1966-12-11</t>
+  </si>
+  <si>
+    <t>caio-cesar</t>
+  </si>
+  <si>
+    <t>César</t>
+  </si>
+  <si>
+    <t>Caio</t>
+  </si>
+  <si>
+    <t>Caio César Ignácio Cardoso de Melo</t>
+  </si>
+  <si>
+    <t>Caio_Cesar.png</t>
+  </si>
+  <si>
+    <t>1988-09-28</t>
+  </si>
+  <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
+    <t>Caio César was also a &lt;b&gt;Police officer&lt;/b&gt;, and was shot in the neck while he and his colleagues were conducting a routine patrol, two days after his 27th birthday. He was taken to the hospital, where he underwent emergency surgery; however, he succumbed to his injuries.</t>
+  </si>
+  <si>
+    <t>isaac-schneider</t>
+  </si>
+  <si>
+    <t>Schneider</t>
+  </si>
+  <si>
+    <t>Isaac</t>
+  </si>
+  <si>
+    <t>Isaac_Schneider.png</t>
+  </si>
+  <si>
+    <t>1939-06-30</t>
+  </si>
+  <si>
+    <t>2023-04-18</t>
+  </si>
+  <si>
+    <t>mauro-ramos</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>Mauro</t>
+  </si>
+  <si>
+    <t>Mauro_Ramos.png</t>
+  </si>
+  <si>
+    <t>1961-02-13</t>
+  </si>
+  <si>
+    <t>garcia-junior</t>
+  </si>
+  <si>
+    <t>Júnior</t>
+  </si>
+  <si>
+    <t>Garcia Júnior</t>
+  </si>
+  <si>
+    <t>Manoel Garcia Júnior</t>
+  </si>
+  <si>
+    <t>Manny Garcia Júnior
+Garcia Jr.</t>
+  </si>
+  <si>
+    <t>Garcia_Júnior.png</t>
+  </si>
+  <si>
+    <t>1967-03-02</t>
+  </si>
+  <si>
+    <t>ju-cassou</t>
+  </si>
+  <si>
+    <t>Cassou</t>
+  </si>
+  <si>
+    <t>Ju</t>
+  </si>
+  <si>
+    <t>Jucelene Cassou Guimarães</t>
+  </si>
+  <si>
+    <t>Ju_Cassou.png</t>
+  </si>
+  <si>
+    <t>1965-05-14</t>
+  </si>
+  <si>
+    <t>geisa-vidal</t>
+  </si>
+  <si>
+    <t>Vidal</t>
+  </si>
+  <si>
+    <t>Geisa</t>
+  </si>
+  <si>
+    <t>Geisa_Vidal.png</t>
+  </si>
+  <si>
+    <t>1941-05-21</t>
+  </si>
+  <si>
+    <t>2023-04-04</t>
+  </si>
+  <si>
+    <t>pietro-mario</t>
+  </si>
+  <si>
+    <t>Mário</t>
+  </si>
+  <si>
+    <t>Pietro</t>
+  </si>
+  <si>
+    <t>Pietro_Mário.png</t>
+  </si>
+  <si>
+    <t>Pietro Mario Francesco Bogianchini</t>
+  </si>
+  <si>
+    <t>1939-06-29</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchiniv&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
+  </si>
+  <si>
+    <t>pedro-eugenio</t>
+  </si>
+  <si>
+    <t>Eugênio</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Pedro_Eugenio.png</t>
+  </si>
+  <si>
+    <t>1958-08-20</t>
+  </si>
+  <si>
+    <t>kiara-sasso</t>
+  </si>
+  <si>
+    <t>Sasso</t>
+  </si>
+  <si>
+    <t>Kiara</t>
+  </si>
+  <si>
+    <t>Chiara Sasso (&lt;i&gt;real name&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t>Chiara Francesca Perin Di Santolo Sasso de Menezes</t>
+  </si>
+  <si>
+    <t>Kiara_Sasso.png</t>
+  </si>
+  <si>
+    <t>1979-01-27</t>
+  </si>
+  <si>
+    <t>dolores-machado</t>
+  </si>
+  <si>
+    <t>Dolores</t>
+  </si>
+  <si>
+    <t>Dolores_Machado.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 May 19?? - </t>
+  </si>
+  <si>
+    <t>francisco-jose</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Francisco_Jose.png</t>
+  </si>
+  <si>
+    <t>1940</t>
+  </si>
+  <si>
+    <t>mauricio-berger</t>
+  </si>
+  <si>
+    <t>Berger</t>
+  </si>
+  <si>
+    <t>Maurício</t>
+  </si>
+  <si>
+    <t>Mauricio_Berger.png</t>
+  </si>
+  <si>
+    <t>1965-03-11</t>
+  </si>
+  <si>
+    <t>Maurício Paglarelli Bergqvist</t>
   </si>
 </sst>
 </file>
@@ -6564,7 +6781,17 @@
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -6909,7 +7136,7 @@
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="30.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="40.140625" customWidth="1"/>
@@ -23636,39 +23863,63 @@
       <c r="Y471" s="6"/>
     </row>
     <row r="472" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A472" s="7"/>
+      <c r="A472" s="7" t="s">
+        <v>1940</v>
+      </c>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
-      <c r="D472" s="7"/>
+      <c r="D472" s="7" t="s">
+        <v>1941</v>
+      </c>
       <c r="E472" s="7"/>
-      <c r="F472" s="7"/>
+      <c r="F472" s="7" t="s">
+        <v>1942</v>
+      </c>
       <c r="G472" s="7"/>
       <c r="H472" s="7"/>
-      <c r="I472" s="6"/>
+      <c r="I472" s="6" t="s">
+        <v>1943</v>
+      </c>
       <c r="J472" s="8"/>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c r="M472" s="7"/>
       <c r="N472" s="7"/>
       <c r="O472" s="7"/>
-      <c r="P472" s="7"/>
+      <c r="P472" s="7" t="s">
+        <v>1944</v>
+      </c>
       <c r="Q472" s="6"/>
-      <c r="R472" s="7"/>
+      <c r="R472" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S472" s="7"/>
-      <c r="T472" s="6"/>
-      <c r="U472" s="6"/>
+      <c r="T472" s="6" t="s">
+        <v>1945</v>
+      </c>
+      <c r="U472" s="6" t="s">
+        <v>1946</v>
+      </c>
       <c r="V472" s="7"/>
       <c r="W472" s="7"/>
       <c r="X472" s="6"/>
-      <c r="Y472" s="6"/>
+      <c r="Y472" s="6" t="s">
+        <v>1947</v>
+      </c>
     </row>
     <row r="473" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A473" s="7"/>
+      <c r="A473" s="7" t="s">
+        <v>1948</v>
+      </c>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
-      <c r="D473" s="7"/>
+      <c r="D473" s="7" t="s">
+        <v>1949</v>
+      </c>
       <c r="E473" s="7"/>
-      <c r="F473" s="7"/>
+      <c r="F473" s="7" t="s">
+        <v>1950</v>
+      </c>
       <c r="G473" s="7"/>
       <c r="H473" s="7"/>
       <c r="I473" s="6"/>
@@ -23678,24 +23929,38 @@
       <c r="M473" s="7"/>
       <c r="N473" s="7"/>
       <c r="O473" s="7"/>
-      <c r="P473" s="7"/>
+      <c r="P473" s="7" t="s">
+        <v>1951</v>
+      </c>
       <c r="Q473" s="6"/>
-      <c r="R473" s="7"/>
+      <c r="R473" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S473" s="7"/>
-      <c r="T473" s="6"/>
-      <c r="U473" s="6"/>
+      <c r="T473" s="6" t="s">
+        <v>1952</v>
+      </c>
+      <c r="U473" s="6" t="s">
+        <v>1953</v>
+      </c>
       <c r="V473" s="7"/>
       <c r="W473" s="7"/>
       <c r="X473" s="6"/>
       <c r="Y473" s="6"/>
     </row>
     <row r="474" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A474" s="7"/>
+      <c r="A474" s="7" t="s">
+        <v>1954</v>
+      </c>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
-      <c r="D474" s="7"/>
+      <c r="D474" s="7" t="s">
+        <v>1955</v>
+      </c>
       <c r="E474" s="7"/>
-      <c r="F474" s="7"/>
+      <c r="F474" s="7" t="s">
+        <v>1956</v>
+      </c>
       <c r="G474" s="7"/>
       <c r="H474" s="7"/>
       <c r="I474" s="6"/>
@@ -23705,38 +23970,60 @@
       <c r="M474" s="7"/>
       <c r="N474" s="7"/>
       <c r="O474" s="7"/>
-      <c r="P474" s="7"/>
+      <c r="P474" s="7" t="s">
+        <v>1957</v>
+      </c>
       <c r="Q474" s="6"/>
-      <c r="R474" s="7"/>
+      <c r="R474" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S474" s="7"/>
-      <c r="T474" s="6"/>
+      <c r="T474" s="6" t="s">
+        <v>1958</v>
+      </c>
       <c r="U474" s="6"/>
       <c r="V474" s="7"/>
       <c r="W474" s="7"/>
       <c r="X474" s="6"/>
       <c r="Y474" s="6"/>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A475" s="7"/>
+    <row r="475" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A475" s="7" t="s">
+        <v>1959</v>
+      </c>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
-      <c r="D475" s="7"/>
+      <c r="D475" s="7" t="s">
+        <v>1960</v>
+      </c>
       <c r="E475" s="7"/>
-      <c r="F475" s="7"/>
+      <c r="F475" s="7" t="s">
+        <v>1961</v>
+      </c>
       <c r="G475" s="7"/>
       <c r="H475" s="7"/>
-      <c r="I475" s="6"/>
-      <c r="J475" s="8"/>
+      <c r="I475" s="6" t="s">
+        <v>1962</v>
+      </c>
+      <c r="J475" s="8" t="s">
+        <v>1963</v>
+      </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
       <c r="M475" s="7"/>
       <c r="N475" s="7"/>
       <c r="O475" s="7"/>
-      <c r="P475" s="7"/>
+      <c r="P475" s="7" t="s">
+        <v>1964</v>
+      </c>
       <c r="Q475" s="6"/>
-      <c r="R475" s="7"/>
+      <c r="R475" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S475" s="7"/>
-      <c r="T475" s="6"/>
+      <c r="T475" s="6" t="s">
+        <v>1965</v>
+      </c>
       <c r="U475" s="6"/>
       <c r="V475" s="7"/>
       <c r="W475" s="7"/>
@@ -23744,26 +24031,40 @@
       <c r="Y475" s="6"/>
     </row>
     <row r="476" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A476" s="7"/>
+      <c r="A476" s="7" t="s">
+        <v>1966</v>
+      </c>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
-      <c r="D476" s="7"/>
+      <c r="D476" s="7" t="s">
+        <v>1967</v>
+      </c>
       <c r="E476" s="7"/>
-      <c r="F476" s="7"/>
+      <c r="F476" s="7" t="s">
+        <v>1968</v>
+      </c>
       <c r="G476" s="7"/>
       <c r="H476" s="7"/>
-      <c r="I476" s="6"/>
+      <c r="I476" s="6" t="s">
+        <v>1969</v>
+      </c>
       <c r="J476" s="8"/>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
       <c r="M476" s="7"/>
       <c r="N476" s="7"/>
       <c r="O476" s="7"/>
-      <c r="P476" s="7"/>
+      <c r="P476" s="7" t="s">
+        <v>1970</v>
+      </c>
       <c r="Q476" s="6"/>
-      <c r="R476" s="7"/>
+      <c r="R476" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S476" s="7"/>
-      <c r="T476" s="6"/>
+      <c r="T476" s="6" t="s">
+        <v>1971</v>
+      </c>
       <c r="U476" s="6"/>
       <c r="V476" s="7"/>
       <c r="W476" s="7"/>
@@ -23771,12 +24072,18 @@
       <c r="Y476" s="6"/>
     </row>
     <row r="477" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A477" s="7"/>
+      <c r="A477" s="7" t="s">
+        <v>1972</v>
+      </c>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
-      <c r="D477" s="7"/>
+      <c r="D477" s="7" t="s">
+        <v>1973</v>
+      </c>
       <c r="E477" s="7"/>
-      <c r="F477" s="7"/>
+      <c r="F477" s="7" t="s">
+        <v>1974</v>
+      </c>
       <c r="G477" s="7"/>
       <c r="H477" s="7"/>
       <c r="I477" s="6"/>
@@ -23786,51 +24093,83 @@
       <c r="M477" s="7"/>
       <c r="N477" s="7"/>
       <c r="O477" s="7"/>
-      <c r="P477" s="7"/>
+      <c r="P477" s="7" t="s">
+        <v>1975</v>
+      </c>
       <c r="Q477" s="6"/>
-      <c r="R477" s="7"/>
+      <c r="R477" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S477" s="7"/>
-      <c r="T477" s="6"/>
-      <c r="U477" s="6"/>
+      <c r="T477" s="6" t="s">
+        <v>1976</v>
+      </c>
+      <c r="U477" s="6" t="s">
+        <v>1977</v>
+      </c>
       <c r="V477" s="7"/>
       <c r="W477" s="7"/>
       <c r="X477" s="6"/>
       <c r="Y477" s="6"/>
     </row>
     <row r="478" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A478" s="7"/>
+      <c r="A478" s="7" t="s">
+        <v>1978</v>
+      </c>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
-      <c r="D478" s="7"/>
+      <c r="D478" s="7" t="s">
+        <v>1979</v>
+      </c>
       <c r="E478" s="7"/>
-      <c r="F478" s="7"/>
+      <c r="F478" s="7" t="s">
+        <v>1980</v>
+      </c>
       <c r="G478" s="7"/>
       <c r="H478" s="7"/>
-      <c r="I478" s="6"/>
+      <c r="I478" s="6" t="s">
+        <v>1982</v>
+      </c>
       <c r="J478" s="8"/>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
       <c r="M478" s="7"/>
       <c r="N478" s="7"/>
       <c r="O478" s="7"/>
-      <c r="P478" s="7"/>
+      <c r="P478" s="7" t="s">
+        <v>1981</v>
+      </c>
       <c r="Q478" s="6"/>
-      <c r="R478" s="7"/>
+      <c r="R478" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S478" s="7"/>
-      <c r="T478" s="6"/>
-      <c r="U478" s="6"/>
+      <c r="T478" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="U478" s="6" t="s">
+        <v>1984</v>
+      </c>
       <c r="V478" s="7"/>
       <c r="W478" s="7"/>
       <c r="X478" s="6"/>
-      <c r="Y478" s="6"/>
+      <c r="Y478" s="6" t="s">
+        <v>1985</v>
+      </c>
     </row>
     <row r="479" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A479" s="7"/>
+      <c r="A479" s="7" t="s">
+        <v>1986</v>
+      </c>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
-      <c r="D479" s="7"/>
+      <c r="D479" s="7" t="s">
+        <v>1987</v>
+      </c>
       <c r="E479" s="7"/>
-      <c r="F479" s="7"/>
+      <c r="F479" s="7" t="s">
+        <v>1988</v>
+      </c>
       <c r="G479" s="7"/>
       <c r="H479" s="7"/>
       <c r="I479" s="6"/>
@@ -23840,11 +24179,17 @@
       <c r="M479" s="7"/>
       <c r="N479" s="7"/>
       <c r="O479" s="7"/>
-      <c r="P479" s="7"/>
+      <c r="P479" s="7" t="s">
+        <v>1989</v>
+      </c>
       <c r="Q479" s="6"/>
-      <c r="R479" s="7"/>
+      <c r="R479" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S479" s="7"/>
-      <c r="T479" s="6"/>
+      <c r="T479" s="6" t="s">
+        <v>1990</v>
+      </c>
       <c r="U479" s="6"/>
       <c r="V479" s="7"/>
       <c r="W479" s="7"/>
@@ -23852,26 +24197,42 @@
       <c r="Y479" s="6"/>
     </row>
     <row r="480" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A480" s="7"/>
+      <c r="A480" s="7" t="s">
+        <v>1991</v>
+      </c>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
-      <c r="D480" s="7"/>
+      <c r="D480" s="7" t="s">
+        <v>1992</v>
+      </c>
       <c r="E480" s="7"/>
-      <c r="F480" s="7"/>
+      <c r="F480" s="7" t="s">
+        <v>1993</v>
+      </c>
       <c r="G480" s="7"/>
       <c r="H480" s="7"/>
-      <c r="I480" s="6"/>
-      <c r="J480" s="8"/>
+      <c r="I480" s="6" t="s">
+        <v>1995</v>
+      </c>
+      <c r="J480" s="6" t="s">
+        <v>1994</v>
+      </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
       <c r="M480" s="7"/>
       <c r="N480" s="7"/>
       <c r="O480" s="7"/>
-      <c r="P480" s="7"/>
+      <c r="P480" s="7" t="s">
+        <v>1996</v>
+      </c>
       <c r="Q480" s="6"/>
-      <c r="R480" s="7"/>
+      <c r="R480" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S480" s="7"/>
-      <c r="T480" s="6"/>
+      <c r="T480" s="6" t="s">
+        <v>1997</v>
+      </c>
       <c r="U480" s="6"/>
       <c r="V480" s="7"/>
       <c r="W480" s="7"/>
@@ -23879,12 +24240,18 @@
       <c r="Y480" s="6"/>
     </row>
     <row r="481" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A481" s="7"/>
+      <c r="A481" s="7" t="s">
+        <v>1998</v>
+      </c>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
-      <c r="D481" s="7"/>
+      <c r="D481" s="7" t="s">
+        <v>905</v>
+      </c>
       <c r="E481" s="7"/>
-      <c r="F481" s="7"/>
+      <c r="F481" s="7" t="s">
+        <v>1999</v>
+      </c>
       <c r="G481" s="7"/>
       <c r="H481" s="7"/>
       <c r="I481" s="6"/>
@@ -23894,10 +24261,16 @@
       <c r="M481" s="7"/>
       <c r="N481" s="7"/>
       <c r="O481" s="7"/>
-      <c r="P481" s="7"/>
+      <c r="P481" s="7" t="s">
+        <v>2000</v>
+      </c>
       <c r="Q481" s="6"/>
-      <c r="R481" s="7"/>
-      <c r="S481" s="7"/>
+      <c r="R481" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="S481" s="7" t="s">
+        <v>2001</v>
+      </c>
       <c r="T481" s="6"/>
       <c r="U481" s="6"/>
       <c r="V481" s="7"/>
@@ -23906,12 +24279,18 @@
       <c r="Y481" s="6"/>
     </row>
     <row r="482" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A482" s="7"/>
+      <c r="A482" s="7" t="s">
+        <v>2002</v>
+      </c>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
-      <c r="D482" s="7"/>
+      <c r="D482" s="7" t="s">
+        <v>341</v>
+      </c>
       <c r="E482" s="7"/>
-      <c r="F482" s="7"/>
+      <c r="F482" s="7" t="s">
+        <v>2003</v>
+      </c>
       <c r="G482" s="7"/>
       <c r="H482" s="7"/>
       <c r="I482" s="6"/>
@@ -23921,11 +24300,17 @@
       <c r="M482" s="7"/>
       <c r="N482" s="7"/>
       <c r="O482" s="7"/>
-      <c r="P482" s="7"/>
+      <c r="P482" s="7" t="s">
+        <v>2004</v>
+      </c>
       <c r="Q482" s="6"/>
-      <c r="R482" s="7"/>
+      <c r="R482" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S482" s="7"/>
-      <c r="T482" s="6"/>
+      <c r="T482" s="6" t="s">
+        <v>2005</v>
+      </c>
       <c r="U482" s="6"/>
       <c r="V482" s="7"/>
       <c r="W482" s="7"/>
@@ -23933,26 +24318,40 @@
       <c r="Y482" s="6"/>
     </row>
     <row r="483" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A483" s="7"/>
+      <c r="A483" s="7" t="s">
+        <v>2006</v>
+      </c>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
-      <c r="D483" s="7"/>
+      <c r="D483" s="7" t="s">
+        <v>2007</v>
+      </c>
       <c r="E483" s="7"/>
-      <c r="F483" s="7"/>
+      <c r="F483" s="7" t="s">
+        <v>2008</v>
+      </c>
       <c r="G483" s="7"/>
       <c r="H483" s="7"/>
-      <c r="I483" s="6"/>
+      <c r="I483" s="6" t="s">
+        <v>2011</v>
+      </c>
       <c r="J483" s="8"/>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
       <c r="M483" s="7"/>
       <c r="N483" s="7"/>
       <c r="O483" s="7"/>
-      <c r="P483" s="7"/>
+      <c r="P483" s="7" t="s">
+        <v>2009</v>
+      </c>
       <c r="Q483" s="6"/>
-      <c r="R483" s="7"/>
+      <c r="R483" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S483" s="7"/>
-      <c r="T483" s="6"/>
+      <c r="T483" s="6" t="s">
+        <v>2010</v>
+      </c>
       <c r="U483" s="6"/>
       <c r="V483" s="7"/>
       <c r="W483" s="7"/>
@@ -37894,7 +38293,10 @@
   </sheetData>
   <autoFilter ref="A1:Z343" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1:P1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="H2:H1001" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6759F92F-C567-4ADB-A89A-B6391D974B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FBF6FD-5430-4AB2-8B34-6BAB02CB7B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6544,9 +6544,6 @@
     <t>2020-08-31</t>
   </si>
   <si>
-    <t>Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchiniv&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
-  </si>
-  <si>
     <t>pedro-eugenio</t>
   </si>
   <si>
@@ -6623,6 +6620,9 @@
   </si>
   <si>
     <t>Maurício Paglarelli Bergqvist</t>
+  </si>
+  <si>
+    <t>Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchini&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
   </si>
 </sst>
 </file>
@@ -24154,21 +24154,21 @@
       <c r="W478" s="7"/>
       <c r="X478" s="6"/>
       <c r="Y478" s="6" t="s">
-        <v>1985</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="479" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
       <c r="D479" s="7" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="E479" s="7"/>
       <c r="F479" s="7" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="G479" s="7"/>
       <c r="H479" s="7"/>
@@ -24180,7 +24180,7 @@
       <c r="N479" s="7"/>
       <c r="O479" s="7"/>
       <c r="P479" s="7" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="Q479" s="6"/>
       <c r="R479" s="7" t="s">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="S479" s="7"/>
       <c r="T479" s="6" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="U479" s="6"/>
       <c r="V479" s="7"/>
@@ -24198,24 +24198,24 @@
     </row>
     <row r="480" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A480" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
       <c r="D480" s="7" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="E480" s="7"/>
       <c r="F480" s="7" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="G480" s="7"/>
       <c r="H480" s="7"/>
       <c r="I480" s="6" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="J480" s="6" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -24223,7 +24223,7 @@
       <c r="N480" s="7"/>
       <c r="O480" s="7"/>
       <c r="P480" s="7" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="Q480" s="6"/>
       <c r="R480" s="7" t="s">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="S480" s="7"/>
       <c r="T480" s="6" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="U480" s="6"/>
       <c r="V480" s="7"/>
@@ -24241,7 +24241,7 @@
     </row>
     <row r="481" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
@@ -24250,7 +24250,7 @@
       </c>
       <c r="E481" s="7"/>
       <c r="F481" s="7" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="G481" s="7"/>
       <c r="H481" s="7"/>
@@ -24262,14 +24262,14 @@
       <c r="N481" s="7"/>
       <c r="O481" s="7"/>
       <c r="P481" s="7" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="Q481" s="6"/>
       <c r="R481" s="7" t="s">
         <v>649</v>
       </c>
       <c r="S481" s="7" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="T481" s="6"/>
       <c r="U481" s="6"/>
@@ -24280,7 +24280,7 @@
     </row>
     <row r="482" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="E482" s="7"/>
       <c r="F482" s="7" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="G482" s="7"/>
       <c r="H482" s="7"/>
@@ -24301,7 +24301,7 @@
       <c r="N482" s="7"/>
       <c r="O482" s="7"/>
       <c r="P482" s="7" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="Q482" s="6"/>
       <c r="R482" s="7" t="s">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="S482" s="7"/>
       <c r="T482" s="6" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="U482" s="6"/>
       <c r="V482" s="7"/>
@@ -24319,21 +24319,21 @@
     </row>
     <row r="483" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
       <c r="D483" s="7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E483" s="7"/>
       <c r="F483" s="7" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="G483" s="7"/>
       <c r="H483" s="7"/>
       <c r="I483" s="6" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="J483" s="8"/>
       <c r="K483" s="7"/>
@@ -24342,7 +24342,7 @@
       <c r="N483" s="7"/>
       <c r="O483" s="7"/>
       <c r="P483" s="7" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="Q483" s="6"/>
       <c r="R483" s="7" t="s">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S483" s="7"/>
       <c r="T483" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="U483" s="6"/>
       <c r="V483" s="7"/>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FBF6FD-5430-4AB2-8B34-6BAB02CB7B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E162EA-A78C-41DC-BD4F-92E0B82A4189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6362,10 +6362,6 @@
     <t>14 October 1949 - 2019 (buyout)</t>
   </si>
   <si>
-    <t>Berlin-Lankwitz (1949-2017)
-Berlin-Schöneberg (2017-2019)</t>
-  </si>
-  <si>
     <t>Founded by &lt;b&gt;Wenzel Lüdecke&lt;/b&gt; in 1949, &lt;i&gt;Berliner Synchron GmbH&lt;/i&gt; is the oldest dubbing studio in Germany. It was bought in 2019 by Iyuno Group, and changed name on this occasion.</t>
   </si>
   <si>
@@ -6622,7 +6618,11 @@
     <t>Maurício Paglarelli Bergqvist</t>
   </si>
   <si>
-    <t>Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchini&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;Source : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
+    <t>Berlin-Lankwitz (1949-2017)&lt;br&gt;
+Berlin-Schöneberg (2017-2019)</t>
+  </si>
+  <si>
+    <t>Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchini&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
   </si>
 </sst>
 </file>
@@ -23726,10 +23726,10 @@
         <v>1923</v>
       </c>
       <c r="Q468" s="8" t="s">
-        <v>1925</v>
+        <v>2010</v>
       </c>
       <c r="R468" s="7" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="S468" s="7" t="s">
         <v>1924</v>
@@ -23742,7 +23742,7 @@
       <c r="W468" s="7"/>
       <c r="X468" s="6"/>
       <c r="Y468" s="6" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="469" spans="1:25" x14ac:dyDescent="0.25">
@@ -23760,22 +23760,22 @@
       <c r="J469" s="8"/>
       <c r="K469" s="7"/>
       <c r="L469" s="7" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="M469" s="7"/>
       <c r="N469" s="7"/>
       <c r="O469" s="7"/>
       <c r="P469" s="7" t="s">
+        <v>1927</v>
+      </c>
+      <c r="Q469" s="6" t="s">
+        <v>1929</v>
+      </c>
+      <c r="R469" s="7" t="s">
         <v>1928</v>
       </c>
-      <c r="Q469" s="6" t="s">
+      <c r="S469" s="7" t="s">
         <v>1930</v>
-      </c>
-      <c r="R469" s="7" t="s">
-        <v>1929</v>
-      </c>
-      <c r="S469" s="7" t="s">
-        <v>1931</v>
       </c>
       <c r="T469" s="6"/>
       <c r="U469" s="6"/>
@@ -23788,16 +23788,16 @@
     </row>
     <row r="470" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A470" s="7" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
       <c r="D470" s="7" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="E470" s="7"/>
       <c r="F470" s="7" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="G470" s="7"/>
       <c r="H470" s="7"/>
@@ -23809,7 +23809,7 @@
       <c r="N470" s="7"/>
       <c r="O470" s="7"/>
       <c r="P470" s="7" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="Q470" s="6"/>
       <c r="R470" s="7" t="s">
@@ -23825,12 +23825,12 @@
     </row>
     <row r="471" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A471" s="7" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
       <c r="D471" s="7" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="E471" s="7"/>
       <c r="F471" s="7" t="s">
@@ -23846,14 +23846,14 @@
       <c r="N471" s="7"/>
       <c r="O471" s="7"/>
       <c r="P471" s="7" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="Q471" s="6"/>
       <c r="R471" s="7" t="s">
         <v>1874</v>
       </c>
       <c r="S471" s="7" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="T471" s="6"/>
       <c r="U471" s="6"/>
@@ -23864,21 +23864,21 @@
     </row>
     <row r="472" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A472" s="7" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
       <c r="D472" s="7" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="E472" s="7"/>
       <c r="F472" s="7" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="G472" s="7"/>
       <c r="H472" s="7"/>
       <c r="I472" s="6" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="J472" s="8"/>
       <c r="K472" s="7"/>
@@ -23887,7 +23887,7 @@
       <c r="N472" s="7"/>
       <c r="O472" s="7"/>
       <c r="P472" s="7" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="Q472" s="6"/>
       <c r="R472" s="7" t="s">
@@ -23895,30 +23895,30 @@
       </c>
       <c r="S472" s="7"/>
       <c r="T472" s="6" t="s">
+        <v>1944</v>
+      </c>
+      <c r="U472" s="6" t="s">
         <v>1945</v>
-      </c>
-      <c r="U472" s="6" t="s">
-        <v>1946</v>
       </c>
       <c r="V472" s="7"/>
       <c r="W472" s="7"/>
       <c r="X472" s="6"/>
       <c r="Y472" s="6" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="473" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A473" s="7" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
       <c r="D473" s="7" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="E473" s="7"/>
       <c r="F473" s="7" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="G473" s="7"/>
       <c r="H473" s="7"/>
@@ -23930,7 +23930,7 @@
       <c r="N473" s="7"/>
       <c r="O473" s="7"/>
       <c r="P473" s="7" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="Q473" s="6"/>
       <c r="R473" s="7" t="s">
@@ -23938,10 +23938,10 @@
       </c>
       <c r="S473" s="7"/>
       <c r="T473" s="6" t="s">
+        <v>1951</v>
+      </c>
+      <c r="U473" s="6" t="s">
         <v>1952</v>
-      </c>
-      <c r="U473" s="6" t="s">
-        <v>1953</v>
       </c>
       <c r="V473" s="7"/>
       <c r="W473" s="7"/>
@@ -23950,16 +23950,16 @@
     </row>
     <row r="474" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A474" s="7" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
       <c r="D474" s="7" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="E474" s="7"/>
       <c r="F474" s="7" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="G474" s="7"/>
       <c r="H474" s="7"/>
@@ -23971,7 +23971,7 @@
       <c r="N474" s="7"/>
       <c r="O474" s="7"/>
       <c r="P474" s="7" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="Q474" s="6"/>
       <c r="R474" s="7" t="s">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="S474" s="7"/>
       <c r="T474" s="6" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="U474" s="6"/>
       <c r="V474" s="7"/>
@@ -23989,24 +23989,24 @@
     </row>
     <row r="475" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A475" s="7" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
       <c r="D475" s="7" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="E475" s="7"/>
       <c r="F475" s="7" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="G475" s="7"/>
       <c r="H475" s="7"/>
       <c r="I475" s="6" t="s">
+        <v>1961</v>
+      </c>
+      <c r="J475" s="8" t="s">
         <v>1962</v>
-      </c>
-      <c r="J475" s="8" t="s">
-        <v>1963</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -24014,7 +24014,7 @@
       <c r="N475" s="7"/>
       <c r="O475" s="7"/>
       <c r="P475" s="7" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="Q475" s="6"/>
       <c r="R475" s="7" t="s">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S475" s="7"/>
       <c r="T475" s="6" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="U475" s="6"/>
       <c r="V475" s="7"/>
@@ -24032,21 +24032,21 @@
     </row>
     <row r="476" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A476" s="7" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
       <c r="D476" s="7" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E476" s="7"/>
       <c r="F476" s="7" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G476" s="7"/>
       <c r="H476" s="7"/>
       <c r="I476" s="6" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="J476" s="8"/>
       <c r="K476" s="7"/>
@@ -24055,7 +24055,7 @@
       <c r="N476" s="7"/>
       <c r="O476" s="7"/>
       <c r="P476" s="7" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="Q476" s="6"/>
       <c r="R476" s="7" t="s">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="S476" s="7"/>
       <c r="T476" s="6" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="U476" s="6"/>
       <c r="V476" s="7"/>
@@ -24073,16 +24073,16 @@
     </row>
     <row r="477" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A477" s="7" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
       <c r="D477" s="7" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E477" s="7"/>
       <c r="F477" s="7" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="G477" s="7"/>
       <c r="H477" s="7"/>
@@ -24094,7 +24094,7 @@
       <c r="N477" s="7"/>
       <c r="O477" s="7"/>
       <c r="P477" s="7" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="Q477" s="6"/>
       <c r="R477" s="7" t="s">
@@ -24102,10 +24102,10 @@
       </c>
       <c r="S477" s="7"/>
       <c r="T477" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="U477" s="6" t="s">
         <v>1976</v>
-      </c>
-      <c r="U477" s="6" t="s">
-        <v>1977</v>
       </c>
       <c r="V477" s="7"/>
       <c r="W477" s="7"/>
@@ -24114,21 +24114,21 @@
     </row>
     <row r="478" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A478" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
       <c r="D478" s="7" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="E478" s="7"/>
       <c r="F478" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="G478" s="7"/>
       <c r="H478" s="7"/>
       <c r="I478" s="6" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="J478" s="8"/>
       <c r="K478" s="7"/>
@@ -24137,7 +24137,7 @@
       <c r="N478" s="7"/>
       <c r="O478" s="7"/>
       <c r="P478" s="7" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="Q478" s="6"/>
       <c r="R478" s="7" t="s">
@@ -24145,10 +24145,10 @@
       </c>
       <c r="S478" s="7"/>
       <c r="T478" s="6" t="s">
+        <v>1982</v>
+      </c>
+      <c r="U478" s="6" t="s">
         <v>1983</v>
-      </c>
-      <c r="U478" s="6" t="s">
-        <v>1984</v>
       </c>
       <c r="V478" s="7"/>
       <c r="W478" s="7"/>
@@ -24159,16 +24159,16 @@
     </row>
     <row r="479" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
       <c r="D479" s="7" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="E479" s="7"/>
       <c r="F479" s="7" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="G479" s="7"/>
       <c r="H479" s="7"/>
@@ -24180,7 +24180,7 @@
       <c r="N479" s="7"/>
       <c r="O479" s="7"/>
       <c r="P479" s="7" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="Q479" s="6"/>
       <c r="R479" s="7" t="s">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="S479" s="7"/>
       <c r="T479" s="6" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="U479" s="6"/>
       <c r="V479" s="7"/>
@@ -24198,24 +24198,24 @@
     </row>
     <row r="480" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A480" s="7" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
       <c r="D480" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E480" s="7"/>
       <c r="F480" s="7" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="G480" s="7"/>
       <c r="H480" s="7"/>
       <c r="I480" s="6" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="J480" s="6" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -24223,7 +24223,7 @@
       <c r="N480" s="7"/>
       <c r="O480" s="7"/>
       <c r="P480" s="7" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="Q480" s="6"/>
       <c r="R480" s="7" t="s">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="S480" s="7"/>
       <c r="T480" s="6" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="U480" s="6"/>
       <c r="V480" s="7"/>
@@ -24241,7 +24241,7 @@
     </row>
     <row r="481" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
@@ -24250,7 +24250,7 @@
       </c>
       <c r="E481" s="7"/>
       <c r="F481" s="7" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="G481" s="7"/>
       <c r="H481" s="7"/>
@@ -24262,14 +24262,14 @@
       <c r="N481" s="7"/>
       <c r="O481" s="7"/>
       <c r="P481" s="7" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="Q481" s="6"/>
       <c r="R481" s="7" t="s">
         <v>649</v>
       </c>
       <c r="S481" s="7" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="T481" s="6"/>
       <c r="U481" s="6"/>
@@ -24280,7 +24280,7 @@
     </row>
     <row r="482" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="E482" s="7"/>
       <c r="F482" s="7" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="G482" s="7"/>
       <c r="H482" s="7"/>
@@ -24301,7 +24301,7 @@
       <c r="N482" s="7"/>
       <c r="O482" s="7"/>
       <c r="P482" s="7" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="Q482" s="6"/>
       <c r="R482" s="7" t="s">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="S482" s="7"/>
       <c r="T482" s="6" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="U482" s="6"/>
       <c r="V482" s="7"/>
@@ -24319,21 +24319,21 @@
     </row>
     <row r="483" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
       <c r="D483" s="7" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E483" s="7"/>
       <c r="F483" s="7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="G483" s="7"/>
       <c r="H483" s="7"/>
       <c r="I483" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="J483" s="8"/>
       <c r="K483" s="7"/>
@@ -24342,7 +24342,7 @@
       <c r="N483" s="7"/>
       <c r="O483" s="7"/>
       <c r="P483" s="7" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="Q483" s="6"/>
       <c r="R483" s="7" t="s">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S483" s="7"/>
       <c r="T483" s="6" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="U483" s="6"/>
       <c r="V483" s="7"/>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E162EA-A78C-41DC-BD4F-92E0B82A4189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2A7BFD-2268-48CF-A846-5B89E349F64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Aide" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Artistes!$A$1:$Z$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Artistes!$A$1:$Z$483</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="2012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="2016">
   <si>
     <t>artist</t>
   </si>
@@ -6623,6 +6623,18 @@
   </si>
   <si>
     <t>Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchini&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
+  </si>
+  <si>
+    <t>BRAZIL</t>
+  </si>
+  <si>
+    <t>EGYPT</t>
+  </si>
+  <si>
+    <t>TAIWAN</t>
+  </si>
+  <si>
+    <t>SWEDEN</t>
   </si>
 </sst>
 </file>
@@ -14909,7 +14921,7 @@
         <v>916</v>
       </c>
       <c r="R234" t="s">
-        <v>649</v>
+        <v>2012</v>
       </c>
       <c r="T234" s="7"/>
       <c r="U234" s="7"/>
@@ -18917,7 +18929,7 @@
       <c r="P341" s="7"/>
       <c r="Q341" s="6"/>
       <c r="R341" s="7" t="s">
-        <v>942</v>
+        <v>2013</v>
       </c>
       <c r="S341" s="7"/>
       <c r="T341" s="6"/>
@@ -19572,7 +19584,7 @@
       <c r="P357" s="7"/>
       <c r="Q357" s="6"/>
       <c r="R357" s="7" t="s">
-        <v>1408</v>
+        <v>2014</v>
       </c>
       <c r="S357" s="7"/>
       <c r="T357" s="6"/>
@@ -19609,7 +19621,7 @@
       <c r="P358" s="7"/>
       <c r="Q358" s="6"/>
       <c r="R358" s="7" t="s">
-        <v>1408</v>
+        <v>2014</v>
       </c>
       <c r="S358" s="7"/>
       <c r="T358" s="6"/>
@@ -21033,7 +21045,7 @@
       <c r="P398" s="7"/>
       <c r="Q398" s="6"/>
       <c r="R398" s="7" t="s">
-        <v>1473</v>
+        <v>2015</v>
       </c>
       <c r="S398" s="7"/>
       <c r="T398" s="6"/>
@@ -21068,7 +21080,7 @@
       <c r="P399" s="7"/>
       <c r="Q399" s="6"/>
       <c r="R399" s="7" t="s">
-        <v>1473</v>
+        <v>2015</v>
       </c>
       <c r="S399" s="7"/>
       <c r="T399" s="6"/>
@@ -38291,7 +38303,7 @@
       <c r="Y999" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z343" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Z483" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2A7BFD-2268-48CF-A846-5B89E349F64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33F173F-2C8E-4E46-B05B-969EAD90A957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="2016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="2126">
   <si>
     <t>artist</t>
   </si>
@@ -6635,6 +6635,340 @@
   </si>
   <si>
     <t>SWEDEN</t>
+  </si>
+  <si>
+    <t>nanna-tribuzy</t>
+  </si>
+  <si>
+    <t>Tribuzy</t>
+  </si>
+  <si>
+    <t>Nanná</t>
+  </si>
+  <si>
+    <t>Nanna_Tribuzy.png</t>
+  </si>
+  <si>
+    <t>1968-11-11</t>
+  </si>
+  <si>
+    <t>Ana Paula Villas-Bôas Tribuzy</t>
+  </si>
+  <si>
+    <t>Paula Tribuzy</t>
+  </si>
+  <si>
+    <t>mauricio-luz</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>Mauricio_Luz.png</t>
+  </si>
+  <si>
+    <t>1966</t>
+  </si>
+  <si>
+    <t>José Mauricio da Silva Luz</t>
+  </si>
+  <si>
+    <t>jonas-caforo</t>
+  </si>
+  <si>
+    <t>Cáforo</t>
+  </si>
+  <si>
+    <t>Jonas</t>
+  </si>
+  <si>
+    <t>Jonas_Caforo.png</t>
+  </si>
+  <si>
+    <t>aline-cabral</t>
+  </si>
+  <si>
+    <t>Cabral</t>
+  </si>
+  <si>
+    <t>Aline</t>
+  </si>
+  <si>
+    <t>Aline_Cabral.png</t>
+  </si>
+  <si>
+    <t>alfredo-liryo</t>
+  </si>
+  <si>
+    <t>Liryo</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>Alfredo_Liryo.png</t>
+  </si>
+  <si>
+    <t>Alfredo Lírio</t>
+  </si>
+  <si>
+    <t>augusto-caruso</t>
+  </si>
+  <si>
+    <t>Caruso</t>
+  </si>
+  <si>
+    <t>Augusto</t>
+  </si>
+  <si>
+    <t>Augusto_Caruso.png</t>
+  </si>
+  <si>
+    <t>1957-08-12</t>
+  </si>
+  <si>
+    <t>deco-fiori</t>
+  </si>
+  <si>
+    <t>Fiori</t>
+  </si>
+  <si>
+    <t>Deco</t>
+  </si>
+  <si>
+    <t>Deco_Fiori.png</t>
+  </si>
+  <si>
+    <t>1967-02-24</t>
+  </si>
+  <si>
+    <t>Oswaldo Neto (&lt;i&gt;real name&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t>fernanda-cappelli</t>
+  </si>
+  <si>
+    <t>Cappelli</t>
+  </si>
+  <si>
+    <t>Fernanda_Cappelli.png</t>
+  </si>
+  <si>
+    <t>1965-09-14</t>
+  </si>
+  <si>
+    <t>juliana-franco</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>Juliana_Franco.png</t>
+  </si>
+  <si>
+    <t>1974-06-19</t>
+  </si>
+  <si>
+    <t>kika-tristao</t>
+  </si>
+  <si>
+    <t>Tristão</t>
+  </si>
+  <si>
+    <t>Kika</t>
+  </si>
+  <si>
+    <t>Kika_Tristao.png</t>
+  </si>
+  <si>
+    <t>1964-03-03</t>
+  </si>
+  <si>
+    <t>Christiane Corrêa Tristão</t>
+  </si>
+  <si>
+    <t>marcia-coutinho</t>
+  </si>
+  <si>
+    <t>Coutinho</t>
+  </si>
+  <si>
+    <t>Marcia</t>
+  </si>
+  <si>
+    <t>Marcia_Coutinho.png</t>
+  </si>
+  <si>
+    <t>1971-09-06</t>
+  </si>
+  <si>
+    <t>nadja-daltro</t>
+  </si>
+  <si>
+    <t>Daltro</t>
+  </si>
+  <si>
+    <t>Nadja</t>
+  </si>
+  <si>
+    <t>Nadja_Daltro.png</t>
+  </si>
+  <si>
+    <t>1945-05-15</t>
+  </si>
+  <si>
+    <t>ronaldo-victorio</t>
+  </si>
+  <si>
+    <t>Victorio</t>
+  </si>
+  <si>
+    <t>Ronaldo</t>
+  </si>
+  <si>
+    <t>Ronaldo_Victorio.png</t>
+  </si>
+  <si>
+    <t>simo</t>
+  </si>
+  <si>
+    <t>Simô</t>
+  </si>
+  <si>
+    <t>Broxado Junior</t>
+  </si>
+  <si>
+    <t>Joaquim</t>
+  </si>
+  <si>
+    <t>Joaquim Broxado Junior</t>
+  </si>
+  <si>
+    <t>Simo.png</t>
+  </si>
+  <si>
+    <t>1956-07-22</t>
+  </si>
+  <si>
+    <t>gottsha</t>
+  </si>
+  <si>
+    <t>Gottsha</t>
+  </si>
+  <si>
+    <t>Sandra Maria Braga Gottlieb</t>
+  </si>
+  <si>
+    <t>Gottsha.png</t>
+  </si>
+  <si>
+    <t>1969-10-04</t>
+  </si>
+  <si>
+    <t>marcelo-coutinho</t>
+  </si>
+  <si>
+    <t>Marcelo_Coutinho.png</t>
+  </si>
+  <si>
+    <t>1967-04-10</t>
+  </si>
+  <si>
+    <t>telmo-perle-munch</t>
+  </si>
+  <si>
+    <t>Telmo</t>
+  </si>
+  <si>
+    <t>Perle</t>
+  </si>
+  <si>
+    <t>Münch</t>
+  </si>
+  <si>
+    <t>Telmo de Avelar</t>
+  </si>
+  <si>
+    <t>Telmo_Perle_Munch.png</t>
+  </si>
+  <si>
+    <t>1923-10-02</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>pavlos-euthymiou</t>
+  </si>
+  <si>
+    <t>Euthymiou</t>
+  </si>
+  <si>
+    <t>Pavlos</t>
+  </si>
+  <si>
+    <t>Pavlos_Euthymiou.png</t>
+  </si>
+  <si>
+    <t>1963-03-26</t>
+  </si>
+  <si>
+    <t>Antonio Pavlos Euthymiou</t>
+  </si>
+  <si>
+    <t>luiz-guilherme-dorey</t>
+  </si>
+  <si>
+    <t>Orey</t>
+  </si>
+  <si>
+    <t>D'</t>
+  </si>
+  <si>
+    <t>Luiz Guilherme</t>
+  </si>
+  <si>
+    <t>Luiz_Guilherme_DOrey.png</t>
+  </si>
+  <si>
+    <t>11 July 196?</t>
+  </si>
+  <si>
+    <t>renato-raposo</t>
+  </si>
+  <si>
+    <t>Raposo</t>
+  </si>
+  <si>
+    <t>Renato</t>
+  </si>
+  <si>
+    <t>Renato_Raposo.png</t>
+  </si>
+  <si>
+    <t>delart</t>
+  </si>
+  <si>
+    <t>Delart Estúdios Cinematográficos</t>
+  </si>
+  <si>
+    <t>Delart.png</t>
+  </si>
+  <si>
+    <t>Delart Cine
+Delart TV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Doutor Otávio Kelly, 71 Tijuca
+</t>
+  </si>
+  <si>
+    <t>Created by Spanish sound-engineer &lt;b&gt;Carlos de la Riva Sáez&lt;/b&gt; in 1965 as &lt;i&gt;Tecnisom&lt;/i&gt;, located in the Museum of Modern Art (MAM, &lt;i&gt;Museu de Arte Moderna de São Paulo&lt;/i&gt;); the studio operated until the 1978 fire that destroyed most of the infrastructure. It then moved for a while to Catumbi neighborhood.&lt;br&gt;In October 1984, the studio was renamed &lt;i&gt;Delart&lt;/i&gt;. The new name comes from the combination of &lt;b&gt;DE LA&lt;/b&gt; Riva's and his technician partner, &lt;b&gt;Walter GoulART&lt;/b&gt; : DELART&lt;br&gt;. Years later (&lt;i&gt;date unknown&lt;/i&gt;), the studio moved to its current location in Tijuca.
+&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://mam.rio/cinemateca/homenagem-a-carlos-de-la-riva/" target="_blank" rel="noopener"&gt;MAM&lt;/a&gt;&lt;/small&gt;
+&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://cnpja.com/office/29030236000152" target="_blank" rel="noopener"&gt;CNPjà&lt;/a&gt;&lt;/small&gt;</t>
   </si>
 </sst>
 </file>
@@ -7149,7 +7483,7 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="40.140625" customWidth="1"/>
     <col min="13" max="13" width="36" customWidth="1"/>
@@ -24371,26 +24705,42 @@
       <c r="Y483" s="6"/>
     </row>
     <row r="484" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A484" s="7"/>
+      <c r="A484" s="7" t="s">
+        <v>2016</v>
+      </c>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
-      <c r="D484" s="7"/>
+      <c r="D484" s="7" t="s">
+        <v>2017</v>
+      </c>
       <c r="E484" s="7"/>
-      <c r="F484" s="7"/>
+      <c r="F484" s="7" t="s">
+        <v>2018</v>
+      </c>
       <c r="G484" s="7"/>
       <c r="H484" s="7"/>
-      <c r="I484" s="6"/>
-      <c r="J484" s="8"/>
+      <c r="I484" s="6" t="s">
+        <v>2021</v>
+      </c>
+      <c r="J484" s="8" t="s">
+        <v>2022</v>
+      </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
       <c r="M484" s="7"/>
       <c r="N484" s="7"/>
       <c r="O484" s="7"/>
-      <c r="P484" s="7"/>
+      <c r="P484" s="7" t="s">
+        <v>2019</v>
+      </c>
       <c r="Q484" s="6"/>
-      <c r="R484" s="7"/>
+      <c r="R484" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S484" s="7"/>
-      <c r="T484" s="6"/>
+      <c r="T484" s="6" t="s">
+        <v>2020</v>
+      </c>
       <c r="U484" s="6"/>
       <c r="V484" s="7"/>
       <c r="W484" s="7"/>
@@ -24398,26 +24748,40 @@
       <c r="Y484" s="6"/>
     </row>
     <row r="485" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A485" s="7"/>
+      <c r="A485" s="7" t="s">
+        <v>2023</v>
+      </c>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
-      <c r="D485" s="7"/>
+      <c r="D485" s="7" t="s">
+        <v>2024</v>
+      </c>
       <c r="E485" s="7"/>
-      <c r="F485" s="7"/>
+      <c r="F485" s="7" t="s">
+        <v>2006</v>
+      </c>
       <c r="G485" s="7"/>
       <c r="H485" s="7"/>
-      <c r="I485" s="6"/>
+      <c r="I485" s="6" t="s">
+        <v>2027</v>
+      </c>
       <c r="J485" s="8"/>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c r="M485" s="7"/>
       <c r="N485" s="7"/>
       <c r="O485" s="7"/>
-      <c r="P485" s="7"/>
+      <c r="P485" s="7" t="s">
+        <v>2025</v>
+      </c>
       <c r="Q485" s="6"/>
-      <c r="R485" s="7"/>
+      <c r="R485" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S485" s="7"/>
-      <c r="T485" s="6"/>
+      <c r="T485" s="6" t="s">
+        <v>2026</v>
+      </c>
       <c r="U485" s="6"/>
       <c r="V485" s="7"/>
       <c r="W485" s="7"/>
@@ -24425,12 +24789,18 @@
       <c r="Y485" s="6"/>
     </row>
     <row r="486" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A486" s="7"/>
+      <c r="A486" s="7" t="s">
+        <v>2028</v>
+      </c>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
-      <c r="D486" s="7"/>
+      <c r="D486" s="7" t="s">
+        <v>2029</v>
+      </c>
       <c r="E486" s="7"/>
-      <c r="F486" s="7"/>
+      <c r="F486" s="7" t="s">
+        <v>2030</v>
+      </c>
       <c r="G486" s="7"/>
       <c r="H486" s="7"/>
       <c r="I486" s="6"/>
@@ -24440,9 +24810,13 @@
       <c r="M486" s="7"/>
       <c r="N486" s="7"/>
       <c r="O486" s="7"/>
-      <c r="P486" s="7"/>
+      <c r="P486" s="7" t="s">
+        <v>2031</v>
+      </c>
       <c r="Q486" s="6"/>
-      <c r="R486" s="7"/>
+      <c r="R486" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S486" s="7"/>
       <c r="T486" s="6"/>
       <c r="U486" s="6"/>
@@ -24452,12 +24826,18 @@
       <c r="Y486" s="6"/>
     </row>
     <row r="487" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A487" s="7"/>
+      <c r="A487" s="7" t="s">
+        <v>2032</v>
+      </c>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
-      <c r="D487" s="7"/>
+      <c r="D487" s="7" t="s">
+        <v>2033</v>
+      </c>
       <c r="E487" s="7"/>
-      <c r="F487" s="7"/>
+      <c r="F487" s="7" t="s">
+        <v>2034</v>
+      </c>
       <c r="G487" s="7"/>
       <c r="H487" s="7"/>
       <c r="I487" s="6"/>
@@ -24467,9 +24847,13 @@
       <c r="M487" s="7"/>
       <c r="N487" s="7"/>
       <c r="O487" s="7"/>
-      <c r="P487" s="7"/>
+      <c r="P487" s="7" t="s">
+        <v>2035</v>
+      </c>
       <c r="Q487" s="6"/>
-      <c r="R487" s="7"/>
+      <c r="R487" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S487" s="7"/>
       <c r="T487" s="6"/>
       <c r="U487" s="6"/>
@@ -24479,24 +24863,36 @@
       <c r="Y487" s="6"/>
     </row>
     <row r="488" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A488" s="7"/>
+      <c r="A488" s="7" t="s">
+        <v>2036</v>
+      </c>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
-      <c r="D488" s="7"/>
+      <c r="D488" s="7" t="s">
+        <v>2037</v>
+      </c>
       <c r="E488" s="7"/>
-      <c r="F488" s="7"/>
+      <c r="F488" s="7" t="s">
+        <v>2038</v>
+      </c>
       <c r="G488" s="7"/>
       <c r="H488" s="7"/>
       <c r="I488" s="6"/>
-      <c r="J488" s="8"/>
+      <c r="J488" s="8" t="s">
+        <v>2040</v>
+      </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
       <c r="M488" s="7"/>
       <c r="N488" s="7"/>
       <c r="O488" s="7"/>
-      <c r="P488" s="7"/>
+      <c r="P488" s="7" t="s">
+        <v>2039</v>
+      </c>
       <c r="Q488" s="6"/>
-      <c r="R488" s="7"/>
+      <c r="R488" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S488" s="7"/>
       <c r="T488" s="6"/>
       <c r="U488" s="6"/>
@@ -24506,12 +24902,18 @@
       <c r="Y488" s="6"/>
     </row>
     <row r="489" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A489" s="7"/>
+      <c r="A489" s="7" t="s">
+        <v>2041</v>
+      </c>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
-      <c r="D489" s="7"/>
+      <c r="D489" s="7" t="s">
+        <v>2042</v>
+      </c>
       <c r="E489" s="7"/>
-      <c r="F489" s="7"/>
+      <c r="F489" s="7" t="s">
+        <v>2043</v>
+      </c>
       <c r="G489" s="7"/>
       <c r="H489" s="7"/>
       <c r="I489" s="6"/>
@@ -24521,11 +24923,17 @@
       <c r="M489" s="7"/>
       <c r="N489" s="7"/>
       <c r="O489" s="7"/>
-      <c r="P489" s="7"/>
+      <c r="P489" s="7" t="s">
+        <v>2044</v>
+      </c>
       <c r="Q489" s="6"/>
-      <c r="R489" s="7"/>
+      <c r="R489" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S489" s="7"/>
-      <c r="T489" s="6"/>
+      <c r="T489" s="6" t="s">
+        <v>2045</v>
+      </c>
       <c r="U489" s="6"/>
       <c r="V489" s="7"/>
       <c r="W489" s="7"/>
@@ -24533,26 +24941,40 @@
       <c r="Y489" s="6"/>
     </row>
     <row r="490" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A490" s="7"/>
+      <c r="A490" s="7" t="s">
+        <v>2046</v>
+      </c>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
-      <c r="D490" s="7"/>
+      <c r="D490" s="7" t="s">
+        <v>2047</v>
+      </c>
       <c r="E490" s="7"/>
-      <c r="F490" s="7"/>
+      <c r="F490" s="7" t="s">
+        <v>2048</v>
+      </c>
       <c r="G490" s="7"/>
       <c r="H490" s="7"/>
       <c r="I490" s="6"/>
-      <c r="J490" s="8"/>
+      <c r="J490" s="6" t="s">
+        <v>2051</v>
+      </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
       <c r="M490" s="7"/>
       <c r="N490" s="7"/>
       <c r="O490" s="7"/>
-      <c r="P490" s="7"/>
+      <c r="P490" s="7" t="s">
+        <v>2049</v>
+      </c>
       <c r="Q490" s="6"/>
-      <c r="R490" s="7"/>
+      <c r="R490" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S490" s="7"/>
-      <c r="T490" s="6"/>
+      <c r="T490" s="6" t="s">
+        <v>2050</v>
+      </c>
       <c r="U490" s="6"/>
       <c r="V490" s="7"/>
       <c r="W490" s="7"/>
@@ -24560,12 +24982,18 @@
       <c r="Y490" s="6"/>
     </row>
     <row r="491" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A491" s="7"/>
+      <c r="A491" s="7" t="s">
+        <v>2052</v>
+      </c>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
-      <c r="D491" s="7"/>
+      <c r="D491" s="7" t="s">
+        <v>2053</v>
+      </c>
       <c r="E491" s="7"/>
-      <c r="F491" s="7"/>
+      <c r="F491" s="7" t="s">
+        <v>653</v>
+      </c>
       <c r="G491" s="7"/>
       <c r="H491" s="7"/>
       <c r="I491" s="6"/>
@@ -24575,11 +25003,17 @@
       <c r="M491" s="7"/>
       <c r="N491" s="7"/>
       <c r="O491" s="7"/>
-      <c r="P491" s="7"/>
+      <c r="P491" s="7" t="s">
+        <v>2054</v>
+      </c>
       <c r="Q491" s="6"/>
-      <c r="R491" s="7"/>
+      <c r="R491" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S491" s="7"/>
-      <c r="T491" s="6"/>
+      <c r="T491" s="6" t="s">
+        <v>2055</v>
+      </c>
       <c r="U491" s="6"/>
       <c r="V491" s="7"/>
       <c r="W491" s="7"/>
@@ -24587,12 +25021,18 @@
       <c r="Y491" s="6"/>
     </row>
     <row r="492" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A492" s="7"/>
+      <c r="A492" s="7" t="s">
+        <v>2056</v>
+      </c>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
-      <c r="D492" s="7"/>
+      <c r="D492" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="E492" s="7"/>
-      <c r="F492" s="7"/>
+      <c r="F492" s="7" t="s">
+        <v>2058</v>
+      </c>
       <c r="G492" s="7"/>
       <c r="H492" s="7"/>
       <c r="I492" s="6"/>
@@ -24602,11 +25042,17 @@
       <c r="M492" s="7"/>
       <c r="N492" s="7"/>
       <c r="O492" s="7"/>
-      <c r="P492" s="7"/>
+      <c r="P492" s="7" t="s">
+        <v>2059</v>
+      </c>
       <c r="Q492" s="6"/>
-      <c r="R492" s="7"/>
+      <c r="R492" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S492" s="7"/>
-      <c r="T492" s="6"/>
+      <c r="T492" s="6" t="s">
+        <v>2060</v>
+      </c>
       <c r="U492" s="6"/>
       <c r="V492" s="7"/>
       <c r="W492" s="7"/>
@@ -24614,26 +25060,40 @@
       <c r="Y492" s="6"/>
     </row>
     <row r="493" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A493" s="7"/>
+      <c r="A493" s="7" t="s">
+        <v>2061</v>
+      </c>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
-      <c r="D493" s="7"/>
+      <c r="D493" s="7" t="s">
+        <v>2062</v>
+      </c>
       <c r="E493" s="7"/>
-      <c r="F493" s="7"/>
+      <c r="F493" s="7" t="s">
+        <v>2063</v>
+      </c>
       <c r="G493" s="7"/>
       <c r="H493" s="7"/>
-      <c r="I493" s="6"/>
+      <c r="I493" s="6" t="s">
+        <v>2066</v>
+      </c>
       <c r="J493" s="8"/>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
       <c r="M493" s="7"/>
       <c r="N493" s="7"/>
       <c r="O493" s="7"/>
-      <c r="P493" s="7"/>
+      <c r="P493" s="7" t="s">
+        <v>2064</v>
+      </c>
       <c r="Q493" s="6"/>
-      <c r="R493" s="7"/>
+      <c r="R493" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S493" s="7"/>
-      <c r="T493" s="6"/>
+      <c r="T493" s="6" t="s">
+        <v>2065</v>
+      </c>
       <c r="U493" s="6"/>
       <c r="V493" s="7"/>
       <c r="W493" s="7"/>
@@ -24641,12 +25101,18 @@
       <c r="Y493" s="6"/>
     </row>
     <row r="494" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A494" s="7"/>
+      <c r="A494" s="7" t="s">
+        <v>2067</v>
+      </c>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
-      <c r="D494" s="7"/>
+      <c r="D494" s="7" t="s">
+        <v>2068</v>
+      </c>
       <c r="E494" s="7"/>
-      <c r="F494" s="7"/>
+      <c r="F494" s="7" t="s">
+        <v>2069</v>
+      </c>
       <c r="G494" s="7"/>
       <c r="H494" s="7"/>
       <c r="I494" s="6"/>
@@ -24656,11 +25122,17 @@
       <c r="M494" s="7"/>
       <c r="N494" s="7"/>
       <c r="O494" s="7"/>
-      <c r="P494" s="7"/>
+      <c r="P494" s="7" t="s">
+        <v>2070</v>
+      </c>
       <c r="Q494" s="6"/>
-      <c r="R494" s="7"/>
+      <c r="R494" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S494" s="7"/>
-      <c r="T494" s="6"/>
+      <c r="T494" s="6" t="s">
+        <v>2071</v>
+      </c>
       <c r="U494" s="6"/>
       <c r="V494" s="7"/>
       <c r="W494" s="7"/>
@@ -24668,12 +25140,18 @@
       <c r="Y494" s="6"/>
     </row>
     <row r="495" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A495" s="7"/>
+      <c r="A495" s="7" t="s">
+        <v>2072</v>
+      </c>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
-      <c r="D495" s="7"/>
+      <c r="D495" s="7" t="s">
+        <v>2073</v>
+      </c>
       <c r="E495" s="7"/>
-      <c r="F495" s="7"/>
+      <c r="F495" s="7" t="s">
+        <v>2074</v>
+      </c>
       <c r="G495" s="7"/>
       <c r="H495" s="7"/>
       <c r="I495" s="6"/>
@@ -24683,11 +25161,17 @@
       <c r="M495" s="7"/>
       <c r="N495" s="7"/>
       <c r="O495" s="7"/>
-      <c r="P495" s="7"/>
+      <c r="P495" s="7" t="s">
+        <v>2075</v>
+      </c>
       <c r="Q495" s="6"/>
-      <c r="R495" s="7"/>
+      <c r="R495" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S495" s="7"/>
-      <c r="T495" s="6"/>
+      <c r="T495" s="6" t="s">
+        <v>2076</v>
+      </c>
       <c r="U495" s="6"/>
       <c r="V495" s="7"/>
       <c r="W495" s="7"/>
@@ -24695,12 +25179,18 @@
       <c r="Y495" s="6"/>
     </row>
     <row r="496" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A496" s="7"/>
+      <c r="A496" s="7" t="s">
+        <v>2077</v>
+      </c>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
-      <c r="D496" s="7"/>
+      <c r="D496" s="7" t="s">
+        <v>2078</v>
+      </c>
       <c r="E496" s="7"/>
-      <c r="F496" s="7"/>
+      <c r="F496" s="7" t="s">
+        <v>2079</v>
+      </c>
       <c r="G496" s="7"/>
       <c r="H496" s="7"/>
       <c r="I496" s="6"/>
@@ -24710,9 +25200,13 @@
       <c r="M496" s="7"/>
       <c r="N496" s="7"/>
       <c r="O496" s="7"/>
-      <c r="P496" s="7"/>
+      <c r="P496" s="7" t="s">
+        <v>2080</v>
+      </c>
       <c r="Q496" s="6"/>
-      <c r="R496" s="7"/>
+      <c r="R496" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S496" s="7"/>
       <c r="T496" s="6"/>
       <c r="U496" s="6"/>
@@ -24722,26 +25216,44 @@
       <c r="Y496" s="6"/>
     </row>
     <row r="497" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A497" s="7"/>
-      <c r="B497" s="7"/>
+      <c r="A497" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B497" s="7" t="s">
+        <v>2082</v>
+      </c>
       <c r="C497" s="7"/>
-      <c r="D497" s="7"/>
+      <c r="D497" s="7" t="s">
+        <v>2083</v>
+      </c>
       <c r="E497" s="7"/>
-      <c r="F497" s="7"/>
+      <c r="F497" s="7" t="s">
+        <v>2084</v>
+      </c>
       <c r="G497" s="7"/>
       <c r="H497" s="7"/>
-      <c r="I497" s="6"/>
+      <c r="I497" s="6" t="s">
+        <v>2085</v>
+      </c>
       <c r="J497" s="8"/>
       <c r="K497" s="7"/>
-      <c r="L497" s="7"/>
+      <c r="L497" s="7" t="s">
+        <v>2082</v>
+      </c>
       <c r="M497" s="7"/>
       <c r="N497" s="7"/>
       <c r="O497" s="7"/>
-      <c r="P497" s="7"/>
+      <c r="P497" s="7" t="s">
+        <v>2086</v>
+      </c>
       <c r="Q497" s="6"/>
-      <c r="R497" s="7"/>
+      <c r="R497" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S497" s="7"/>
-      <c r="T497" s="6"/>
+      <c r="T497" s="6" t="s">
+        <v>2087</v>
+      </c>
       <c r="U497" s="6"/>
       <c r="V497" s="7"/>
       <c r="W497" s="7"/>
@@ -24749,26 +25261,40 @@
       <c r="Y497" s="6"/>
     </row>
     <row r="498" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A498" s="7"/>
-      <c r="B498" s="7"/>
+      <c r="A498" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B498" s="7" t="s">
+        <v>2089</v>
+      </c>
       <c r="C498" s="7"/>
       <c r="D498" s="7"/>
       <c r="E498" s="7"/>
       <c r="F498" s="7"/>
       <c r="G498" s="7"/>
       <c r="H498" s="7"/>
-      <c r="I498" s="6"/>
+      <c r="I498" s="6" t="s">
+        <v>2090</v>
+      </c>
       <c r="J498" s="8"/>
       <c r="K498" s="7"/>
-      <c r="L498" s="7"/>
+      <c r="L498" s="7" t="s">
+        <v>2089</v>
+      </c>
       <c r="M498" s="7"/>
       <c r="N498" s="7"/>
       <c r="O498" s="7"/>
-      <c r="P498" s="7"/>
+      <c r="P498" s="7" t="s">
+        <v>2091</v>
+      </c>
       <c r="Q498" s="6"/>
-      <c r="R498" s="7"/>
+      <c r="R498" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S498" s="7"/>
-      <c r="T498" s="6"/>
+      <c r="T498" s="6" t="s">
+        <v>2092</v>
+      </c>
       <c r="U498" s="6"/>
       <c r="V498" s="7"/>
       <c r="W498" s="7"/>
@@ -24776,12 +25302,18 @@
       <c r="Y498" s="6"/>
     </row>
     <row r="499" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A499" s="7"/>
+      <c r="A499" s="7" t="s">
+        <v>2093</v>
+      </c>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
-      <c r="D499" s="7"/>
+      <c r="D499" s="7" t="s">
+        <v>2068</v>
+      </c>
       <c r="E499" s="7"/>
-      <c r="F499" s="7"/>
+      <c r="F499" s="7" t="s">
+        <v>658</v>
+      </c>
       <c r="G499" s="7"/>
       <c r="H499" s="7"/>
       <c r="I499" s="6"/>
@@ -24791,11 +25323,17 @@
       <c r="M499" s="7"/>
       <c r="N499" s="7"/>
       <c r="O499" s="7"/>
-      <c r="P499" s="7"/>
+      <c r="P499" s="7" t="s">
+        <v>2094</v>
+      </c>
       <c r="Q499" s="6"/>
-      <c r="R499" s="7"/>
+      <c r="R499" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S499" s="7"/>
-      <c r="T499" s="6"/>
+      <c r="T499" s="6" t="s">
+        <v>2095</v>
+      </c>
       <c r="U499" s="6"/>
       <c r="V499" s="7"/>
       <c r="W499" s="7"/>
@@ -24803,53 +25341,85 @@
       <c r="Y499" s="6"/>
     </row>
     <row r="500" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A500" s="7"/>
+      <c r="A500" s="7" t="s">
+        <v>2096</v>
+      </c>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
-      <c r="D500" s="7"/>
-      <c r="E500" s="7"/>
-      <c r="F500" s="7"/>
+      <c r="D500" s="7" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E500" s="7" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F500" s="7" t="s">
+        <v>2097</v>
+      </c>
       <c r="G500" s="7"/>
       <c r="H500" s="7"/>
       <c r="I500" s="6"/>
-      <c r="J500" s="8"/>
+      <c r="J500" s="8" t="s">
+        <v>2100</v>
+      </c>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
       <c r="M500" s="7"/>
       <c r="N500" s="7"/>
       <c r="O500" s="7"/>
-      <c r="P500" s="7"/>
+      <c r="P500" s="7" t="s">
+        <v>2101</v>
+      </c>
       <c r="Q500" s="6"/>
-      <c r="R500" s="7"/>
+      <c r="R500" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S500" s="7"/>
-      <c r="T500" s="6"/>
-      <c r="U500" s="6"/>
+      <c r="T500" s="6" t="s">
+        <v>2102</v>
+      </c>
+      <c r="U500" s="6" t="s">
+        <v>2103</v>
+      </c>
       <c r="V500" s="7"/>
       <c r="W500" s="7"/>
       <c r="X500" s="6"/>
       <c r="Y500" s="6"/>
     </row>
     <row r="501" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A501" s="7"/>
+      <c r="A501" s="7" t="s">
+        <v>2104</v>
+      </c>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
-      <c r="D501" s="7"/>
+      <c r="D501" s="7" t="s">
+        <v>2106</v>
+      </c>
       <c r="E501" s="7"/>
-      <c r="F501" s="7"/>
+      <c r="F501" s="7" t="s">
+        <v>2105</v>
+      </c>
       <c r="G501" s="7"/>
       <c r="H501" s="7"/>
-      <c r="I501" s="6"/>
+      <c r="I501" s="6" t="s">
+        <v>2109</v>
+      </c>
       <c r="J501" s="8"/>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
       <c r="M501" s="7"/>
       <c r="N501" s="7"/>
       <c r="O501" s="7"/>
-      <c r="P501" s="7"/>
+      <c r="P501" s="7" t="s">
+        <v>2107</v>
+      </c>
       <c r="Q501" s="6"/>
-      <c r="R501" s="7"/>
+      <c r="R501" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S501" s="7"/>
-      <c r="T501" s="6"/>
+      <c r="T501" s="6" t="s">
+        <v>2108</v>
+      </c>
       <c r="U501" s="6"/>
       <c r="V501" s="7"/>
       <c r="W501" s="7"/>
@@ -24857,12 +25427,20 @@
       <c r="Y501" s="6"/>
     </row>
     <row r="502" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A502" s="7"/>
+      <c r="A502" s="7" t="s">
+        <v>2110</v>
+      </c>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
-      <c r="D502" s="7"/>
-      <c r="E502" s="7"/>
-      <c r="F502" s="7"/>
+      <c r="D502" s="7" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E502" s="7" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F502" s="7" t="s">
+        <v>2113</v>
+      </c>
       <c r="G502" s="7"/>
       <c r="H502" s="7"/>
       <c r="I502" s="6"/>
@@ -24872,10 +25450,16 @@
       <c r="M502" s="7"/>
       <c r="N502" s="7"/>
       <c r="O502" s="7"/>
-      <c r="P502" s="7"/>
+      <c r="P502" s="7" t="s">
+        <v>2114</v>
+      </c>
       <c r="Q502" s="6"/>
-      <c r="R502" s="7"/>
-      <c r="S502" s="7"/>
+      <c r="R502" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="S502" s="7" t="s">
+        <v>2115</v>
+      </c>
       <c r="T502" s="6"/>
       <c r="U502" s="6"/>
       <c r="V502" s="7"/>
@@ -24884,12 +25468,18 @@
       <c r="Y502" s="6"/>
     </row>
     <row r="503" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A503" s="7"/>
+      <c r="A503" s="7" t="s">
+        <v>2116</v>
+      </c>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
-      <c r="D503" s="7"/>
+      <c r="D503" s="7" t="s">
+        <v>2117</v>
+      </c>
       <c r="E503" s="7"/>
-      <c r="F503" s="7"/>
+      <c r="F503" s="7" t="s">
+        <v>2118</v>
+      </c>
       <c r="G503" s="7"/>
       <c r="H503" s="7"/>
       <c r="I503" s="6"/>
@@ -24899,9 +25489,13 @@
       <c r="M503" s="7"/>
       <c r="N503" s="7"/>
       <c r="O503" s="7"/>
-      <c r="P503" s="7"/>
+      <c r="P503" s="7" t="s">
+        <v>2119</v>
+      </c>
       <c r="Q503" s="6"/>
-      <c r="R503" s="7"/>
+      <c r="R503" s="7" t="s">
+        <v>649</v>
+      </c>
       <c r="S503" s="7"/>
       <c r="T503" s="6"/>
       <c r="U503" s="6"/>
@@ -24910,8 +25504,10 @@
       <c r="X503" s="6"/>
       <c r="Y503" s="6"/>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A504" s="7"/>
+    <row r="504" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A504" s="7" t="s">
+        <v>2120</v>
+      </c>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
       <c r="D504" s="7"/>
@@ -24920,22 +25516,34 @@
       <c r="G504" s="7"/>
       <c r="H504" s="7"/>
       <c r="I504" s="6"/>
-      <c r="J504" s="8"/>
+      <c r="J504" s="8" t="s">
+        <v>2123</v>
+      </c>
       <c r="K504" s="7"/>
-      <c r="L504" s="7"/>
+      <c r="L504" s="7" t="s">
+        <v>2121</v>
+      </c>
       <c r="M504" s="7"/>
       <c r="N504" s="7"/>
       <c r="O504" s="7"/>
-      <c r="P504" s="7"/>
-      <c r="Q504" s="6"/>
-      <c r="R504" s="7"/>
+      <c r="P504" s="7" t="s">
+        <v>2122</v>
+      </c>
+      <c r="Q504" s="8" t="s">
+        <v>2124</v>
+      </c>
+      <c r="R504" s="7" t="s">
+        <v>2012</v>
+      </c>
       <c r="S504" s="7"/>
       <c r="T504" s="6"/>
       <c r="U504" s="6"/>
       <c r="V504" s="7"/>
       <c r="W504" s="7"/>
       <c r="X504" s="6"/>
-      <c r="Y504" s="6"/>
+      <c r="Y504" s="6" t="s">
+        <v>2125</v>
+      </c>
     </row>
     <row r="505" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A505" s="7"/>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33F173F-2C8E-4E46-B05B-969EAD90A957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CB7FDE-E533-45C8-A4AD-84F60B57DF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="2126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="2126">
   <si>
     <t>artist</t>
   </si>
@@ -11876,7 +11876,7 @@
       <c r="Y111" s="8"/>
       <c r="Z111" s="9"/>
     </row>
-    <row r="112" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>449</v>
       </c>
@@ -25538,7 +25538,9 @@
       <c r="S504" s="7"/>
       <c r="T504" s="6"/>
       <c r="U504" s="6"/>
-      <c r="V504" s="7"/>
+      <c r="V504" s="7" t="s">
+        <v>569</v>
+      </c>
       <c r="W504" s="7"/>
       <c r="X504" s="6"/>
       <c r="Y504" s="6" t="s">

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA54D3A8-83B6-4D18-B124-55235075441B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AD27ED-4AC9-431C-96F3-9BCA6D51B0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6966,7 +6966,7 @@
 </t>
   </si>
   <si>
-    <t>Created by Spanish sound-engineer &lt;b&gt;Carlos de la Riva Sáez&lt;/b&gt; in 1965 as &lt;i&gt;Tecnisom&lt;/i&gt;, located in the Museum of Modern Art (MAM, &lt;i&gt;Museu de Arte Moderna de São Paulo&lt;/i&gt;); the studio operated until the 1978 fire that destroyed most of the infrastructure. It then moved for a while to Catumbi neighborhood.&lt;br&gt;In October 1984, the studio was renamed &lt;i&gt;Delart&lt;/i&gt;. The new name comes from the combination of &lt;b&gt;DE LA&lt;/b&gt; Riva's and his technician partner, &lt;b&gt;Walter GoulART&lt;/b&gt; : DELART.&lt;br&gt; Years later (&lt;i&gt;date unknown&lt;/i&gt;), the studio moved to its current location in Tijuca.
+    <t>Created by Spanish sound-engineer &lt;b&gt;Carlos de la Riva Sáez&lt;/b&gt; in 1965 as &lt;i&gt;Tecnisom&lt;/i&gt;, located in the Museum of Modern Art (MAM, &lt;i&gt;Museu de Arte Moderna&lt;/i&gt;); the studio operated until the 1978 fire that destroyed most of the infrastructure. It then moved for a while to Catumbi neighborhood.&lt;br&gt;In October 1984, the studio was renamed &lt;i&gt;Delart&lt;/i&gt;. The new name comes from the name combination of &lt;b&gt;DE LA&lt;/b&gt; Riva and his technician partner, &lt;b&gt;Walter GoulART&lt;/b&gt; : DELART.&lt;br&gt; Years later (&lt;i&gt;exact date unknown&lt;/i&gt;), the studio moved to its current location in Tijuca.
 &lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://mam.rio/cinemateca/homenagem-a-carlos-de-la-riva/" target="_blank" rel="noopener"&gt;MAM&lt;/a&gt;&lt;/small&gt;
 &lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://cnpja.com/office/29030236000152" target="_blank" rel="noopener"&gt;CNPjà&lt;/a&gt;&lt;/small&gt;</t>
   </si>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaume.cervellin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AD27ED-4AC9-431C-96F3-9BCA6D51B0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E80910E-3C74-401A-B81A-F43F7E136D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6966,7 +6966,7 @@
 </t>
   </si>
   <si>
-    <t>Created by Spanish sound-engineer &lt;b&gt;Carlos de la Riva Sáez&lt;/b&gt; in 1965 as &lt;i&gt;Tecnisom&lt;/i&gt;, located in the Museum of Modern Art (MAM, &lt;i&gt;Museu de Arte Moderna&lt;/i&gt;); the studio operated until the 1978 fire that destroyed most of the infrastructure. It then moved for a while to Catumbi neighborhood.&lt;br&gt;In October 1984, the studio was renamed &lt;i&gt;Delart&lt;/i&gt;. The new name comes from the name combination of &lt;b&gt;DE LA&lt;/b&gt; Riva and his technician partner, &lt;b&gt;Walter GoulART&lt;/b&gt; : DELART.&lt;br&gt; Years later (&lt;i&gt;exact date unknown&lt;/i&gt;), the studio moved to its current location in Tijuca.
+    <t>Created by Spanish sound-engineer &lt;b&gt;Carlos de la Riva Sáez&lt;/b&gt; in 1965 as &lt;i&gt;Tecnisom&lt;/i&gt;, located in the Museum of Modern Art (MAM, &lt;i&gt;Museu de Arte Moderna&lt;/i&gt;); the studio operated until the 1978 fire that destroyed most of the infrastructure. It then moved for a while to Catumbi neighborhood.&lt;br&gt;In October 1984, the studio was renamed &lt;i&gt;Delart&lt;/i&gt;. The new name comes from the name combination of &lt;b&gt;DE LA&lt;/b&gt; Riva and his technician partner, Walter Goul&lt;b&gt;ART&lt;/b&gt; : DELART.&lt;br&gt; Years later (&lt;i&gt;exact date unknown&lt;/i&gt;), the studio moved to its current location in Tijuca.
 &lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://mam.rio/cinemateca/homenagem-a-carlos-de-la-riva/" target="_blank" rel="noopener"&gt;MAM&lt;/a&gt;&lt;/small&gt;
 &lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://cnpja.com/office/29030236000152" target="_blank" rel="noopener"&gt;CNPjà&lt;/a&gt;&lt;/small&gt;</t>
   </si>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -6759,7 +6759,7 @@
     <t xml:space="preserve">Júnior</t>
   </si>
   <si>
-    <t xml:space="preserve">Garcia Júnior</t>
+    <t xml:space="preserve">Garcia</t>
   </si>
   <si>
     <t xml:space="preserve">Manoel Garcia Júnior</t>
@@ -7579,76 +7579,80 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -39568,239 +39572,239 @@
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>2092</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>2093</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>2094</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>2095</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>2096</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>2097</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>2098</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>2099</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>2100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>2101</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>2102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>2103</v>
       </c>
-      <c r="B8" s="15"/>
+      <c r="B8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>2104</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>2105</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>2106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>2107</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>2108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>2109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>2110</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>2111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="16" t="s">
         <v>2112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>2113</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>2114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>2115</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>2116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="16" t="s">
         <v>2117</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>2118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="17" t="s">
         <v>2119</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="16" t="s">
         <v>2120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>2121</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>2122</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>2123</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>2124</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>2125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="16" t="s">
         <v>2126</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="16" t="s">
         <v>2127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>2128</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="16" t="s">
         <v>2129</v>
       </c>
     </row>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -6836,7 +6836,7 @@
 Pietro_Mario_1.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchini&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes since May.&lt;br&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
+    <t xml:space="preserve">Pietro Mário was born in &lt;b&gt;Omegna&lt;/b&gt;, Italy, and moved to Brazil in 1947. His father &lt;i&gt;Maiolo Martino Bogianchini&lt;/i&gt;, who had already moved to Brazil in 1938 before his birth, met him for the first time there when he was already 7 years old.&lt;br&gt;He eventually died from &lt;b&gt;cardiac arrest&lt;/b&gt;, after suffering several strokes for a few months.&lt;br&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://comunitaitaliana.com/illettoreracconta-2/" target="_blank" rel="noopener"&gt;Comunità Italiana&lt;/a&gt;&lt;/small&gt;&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a href="https://g1.globo.com/jornal-nacional/noticia/2020/08/31/morre-aos-81-anos-o-ator-e-dublador-pietro-mario.ghtml" target="_blank" rel="noopener"&gt;Jornal Nacional&lt;/a&gt;&lt;/small&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">pedro-eugenio</t>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3023" uniqueCount="2131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="2132">
   <si>
     <t xml:space="preserve">artist</t>
   </si>
@@ -5890,6 +5890,9 @@
   </si>
   <si>
     <t xml:space="preserve">Marcel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcel Navarro Báguena</t>
   </si>
   <si>
     <t xml:space="preserve">Marcel_Navarro.png</t>
@@ -22342,7 +22345,9 @@
       </c>
       <c r="G408" s="11"/>
       <c r="H408" s="7"/>
-      <c r="I408" s="11"/>
+      <c r="I408" s="7" t="s">
+        <v>1639</v>
+      </c>
       <c r="J408" s="10"/>
       <c r="K408" s="11"/>
       <c r="L408" s="11"/>
@@ -22350,7 +22355,7 @@
       <c r="N408" s="11"/>
       <c r="O408" s="7"/>
       <c r="P408" s="7" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="Q408" s="11"/>
       <c r="R408" s="7" t="s">
@@ -22366,7 +22371,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="7" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B409" s="11"/>
       <c r="C409" s="11"/>
@@ -22380,7 +22385,7 @@
       <c r="G409" s="11"/>
       <c r="H409" s="7"/>
       <c r="I409" s="7" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J409" s="10"/>
       <c r="K409" s="11"/>
@@ -22389,7 +22394,7 @@
       <c r="N409" s="11"/>
       <c r="O409" s="7"/>
       <c r="P409" s="7" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="Q409" s="11"/>
       <c r="R409" s="7" t="s">
@@ -22405,22 +22410,22 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B410" s="11"/>
       <c r="C410" s="11"/>
       <c r="D410" s="7" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E410" s="11"/>
       <c r="F410" s="7" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="G410" s="11"/>
       <c r="H410" s="7"/>
       <c r="I410" s="11"/>
       <c r="J410" s="8" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="K410" s="11"/>
       <c r="L410" s="11"/>
@@ -22428,7 +22433,7 @@
       <c r="N410" s="11"/>
       <c r="O410" s="7"/>
       <c r="P410" s="7" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="Q410" s="11"/>
       <c r="R410" s="7" t="s">
@@ -22444,22 +22449,22 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="7" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B411" s="11"/>
       <c r="C411" s="11"/>
       <c r="D411" s="7" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="E411" s="11"/>
       <c r="F411" s="7" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="G411" s="11"/>
       <c r="H411" s="7"/>
       <c r="I411" s="11"/>
       <c r="J411" s="8" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="K411" s="11"/>
       <c r="L411" s="11"/>
@@ -22467,7 +22472,7 @@
       <c r="N411" s="11"/>
       <c r="O411" s="7"/>
       <c r="P411" s="7" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="Q411" s="11"/>
       <c r="R411" s="7" t="s">
@@ -22475,7 +22480,7 @@
       </c>
       <c r="S411" s="11"/>
       <c r="T411" s="7" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="U411" s="11"/>
       <c r="V411" s="7"/>
@@ -22485,16 +22490,16 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="7" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B412" s="11"/>
       <c r="C412" s="11"/>
       <c r="D412" s="7" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="E412" s="11"/>
       <c r="F412" s="7" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="G412" s="11"/>
       <c r="H412" s="7"/>
@@ -22506,7 +22511,7 @@
       <c r="N412" s="11"/>
       <c r="O412" s="7"/>
       <c r="P412" s="7" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="Q412" s="11"/>
       <c r="R412" s="7" t="s">
@@ -22514,7 +22519,7 @@
       </c>
       <c r="S412" s="11"/>
       <c r="T412" s="7" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="U412" s="11"/>
       <c r="V412" s="7"/>
@@ -22524,12 +22529,12 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="7" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B413" s="11"/>
       <c r="C413" s="11"/>
       <c r="D413" s="7" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="E413" s="11"/>
       <c r="F413" s="7" t="s">
@@ -22545,7 +22550,7 @@
       <c r="N413" s="11"/>
       <c r="O413" s="7"/>
       <c r="P413" s="7" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="Q413" s="11"/>
       <c r="R413" s="7" t="s">
@@ -22553,7 +22558,7 @@
       </c>
       <c r="S413" s="11"/>
       <c r="T413" s="7" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="U413" s="11"/>
       <c r="V413" s="7"/>
@@ -22563,7 +22568,7 @@
     </row>
     <row r="414" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="7" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B414" s="11"/>
       <c r="C414" s="11"/>
@@ -22580,7 +22585,7 @@
       <c r="H414" s="7"/>
       <c r="I414" s="11"/>
       <c r="J414" s="8" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="K414" s="11"/>
       <c r="L414" s="11"/>
@@ -22588,7 +22593,7 @@
       <c r="N414" s="11"/>
       <c r="O414" s="7"/>
       <c r="P414" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="Q414" s="11"/>
       <c r="R414" s="7" t="s">
@@ -22604,16 +22609,16 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="7" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B415" s="11"/>
       <c r="C415" s="11"/>
       <c r="D415" s="7" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E415" s="11"/>
       <c r="F415" s="7" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G415" s="11"/>
       <c r="H415" s="7"/>
@@ -22625,14 +22630,14 @@
       <c r="N415" s="11"/>
       <c r="O415" s="7"/>
       <c r="P415" s="7" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="Q415" s="11"/>
       <c r="R415" s="7" t="s">
         <v>42</v>
       </c>
       <c r="S415" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="T415" s="11"/>
       <c r="U415" s="11"/>
@@ -22643,16 +22648,16 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="7" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B416" s="11"/>
       <c r="C416" s="11"/>
       <c r="D416" s="7" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="E416" s="11"/>
       <c r="F416" s="7" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="G416" s="11"/>
       <c r="H416" s="7"/>
@@ -22664,7 +22669,7 @@
       <c r="N416" s="11"/>
       <c r="O416" s="7"/>
       <c r="P416" s="7" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="Q416" s="11"/>
       <c r="R416" s="7" t="s">
@@ -22672,7 +22677,7 @@
       </c>
       <c r="S416" s="11"/>
       <c r="T416" s="7" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="U416" s="11"/>
       <c r="V416" s="7"/>
@@ -22682,16 +22687,16 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="7" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B417" s="11"/>
       <c r="C417" s="11"/>
       <c r="D417" s="7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E417" s="11"/>
       <c r="F417" s="7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="G417" s="11"/>
       <c r="H417" s="7"/>
@@ -22703,14 +22708,14 @@
       <c r="N417" s="11"/>
       <c r="O417" s="7"/>
       <c r="P417" s="7" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="Q417" s="11"/>
       <c r="R417" s="7" t="s">
         <v>42</v>
       </c>
       <c r="S417" s="7" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="T417" s="11"/>
       <c r="U417" s="11"/>
@@ -22721,12 +22726,12 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="7" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B418" s="11"/>
       <c r="C418" s="11"/>
       <c r="D418" s="7" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="E418" s="11"/>
       <c r="F418" s="7" t="s">
@@ -22742,7 +22747,7 @@
       <c r="N418" s="11"/>
       <c r="O418" s="7"/>
       <c r="P418" s="7" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="Q418" s="11"/>
       <c r="R418" s="7" t="s">
@@ -22758,16 +22763,16 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="7" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B419" s="11"/>
       <c r="C419" s="11"/>
       <c r="D419" s="7" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="E419" s="11"/>
       <c r="F419" s="7" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G419" s="11"/>
       <c r="H419" s="7"/>
@@ -22779,7 +22784,7 @@
       <c r="N419" s="11"/>
       <c r="O419" s="7"/>
       <c r="P419" s="7" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="Q419" s="11"/>
       <c r="R419" s="7" t="s">
@@ -22787,7 +22792,7 @@
       </c>
       <c r="S419" s="11"/>
       <c r="T419" s="7" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="U419" s="11"/>
       <c r="V419" s="7"/>
@@ -22797,12 +22802,12 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="7" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B420" s="11"/>
       <c r="C420" s="11"/>
       <c r="D420" s="7" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="E420" s="11"/>
       <c r="F420" s="7" t="s">
@@ -22811,7 +22816,7 @@
       <c r="G420" s="11"/>
       <c r="H420" s="7"/>
       <c r="I420" s="7" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="J420" s="10"/>
       <c r="K420" s="11"/>
@@ -22820,7 +22825,7 @@
       <c r="N420" s="11"/>
       <c r="O420" s="7"/>
       <c r="P420" s="7" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="Q420" s="11"/>
       <c r="R420" s="7" t="s">
@@ -22828,7 +22833,7 @@
       </c>
       <c r="S420" s="11"/>
       <c r="T420" s="7" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="U420" s="11"/>
       <c r="V420" s="7"/>
@@ -22838,12 +22843,12 @@
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="7" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B421" s="11"/>
       <c r="C421" s="11"/>
       <c r="D421" s="7" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="E421" s="11"/>
       <c r="F421" s="7" t="s">
@@ -22859,7 +22864,7 @@
       <c r="N421" s="11"/>
       <c r="O421" s="7"/>
       <c r="P421" s="7" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="Q421" s="11"/>
       <c r="R421" s="7" t="s">
@@ -22875,16 +22880,16 @@
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="7" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B422" s="11"/>
       <c r="C422" s="11"/>
       <c r="D422" s="7" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="E422" s="11"/>
       <c r="F422" s="7" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G422" s="11"/>
       <c r="H422" s="7"/>
@@ -22896,7 +22901,7 @@
       <c r="N422" s="11"/>
       <c r="O422" s="7"/>
       <c r="P422" s="7" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="Q422" s="11"/>
       <c r="R422" s="7" t="s">
@@ -22912,12 +22917,12 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="7" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B423" s="11"/>
       <c r="C423" s="11"/>
       <c r="D423" s="7" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E423" s="11"/>
       <c r="F423" s="7" t="s">
@@ -22933,7 +22938,7 @@
       <c r="N423" s="11"/>
       <c r="O423" s="7"/>
       <c r="P423" s="7" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="Q423" s="11"/>
       <c r="R423" s="7" t="s">
@@ -22949,12 +22954,12 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="7" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B424" s="11"/>
       <c r="C424" s="11"/>
       <c r="D424" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="E424" s="11"/>
       <c r="F424" s="7" t="s">
@@ -22970,7 +22975,7 @@
       <c r="N424" s="11"/>
       <c r="O424" s="7"/>
       <c r="P424" s="7" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="Q424" s="11"/>
       <c r="R424" s="7" t="s">
@@ -22986,15 +22991,15 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="7" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B425" s="11"/>
       <c r="C425" s="11"/>
       <c r="D425" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="E425" s="7" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="F425" s="7" t="s">
         <v>101</v>
@@ -23009,7 +23014,7 @@
       <c r="N425" s="11"/>
       <c r="O425" s="7"/>
       <c r="P425" s="7" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="Q425" s="11"/>
       <c r="R425" s="7" t="s">
@@ -23025,16 +23030,16 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="7" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B426" s="11"/>
       <c r="C426" s="11"/>
       <c r="D426" s="7" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="E426" s="11"/>
       <c r="F426" s="7" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="G426" s="11"/>
       <c r="H426" s="7"/>
@@ -23046,7 +23051,7 @@
       <c r="N426" s="11"/>
       <c r="O426" s="7"/>
       <c r="P426" s="7" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="Q426" s="11"/>
       <c r="R426" s="7" t="s">
@@ -23062,16 +23067,16 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="7" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B427" s="11"/>
       <c r="C427" s="11"/>
       <c r="D427" s="7" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="E427" s="11"/>
       <c r="F427" s="7" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G427" s="11"/>
       <c r="H427" s="7"/>
@@ -23083,7 +23088,7 @@
       <c r="N427" s="11"/>
       <c r="O427" s="7"/>
       <c r="P427" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="Q427" s="11"/>
       <c r="R427" s="7" t="s">
@@ -23099,16 +23104,16 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="7" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B428" s="11"/>
       <c r="C428" s="11"/>
       <c r="D428" s="7" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="E428" s="11"/>
       <c r="F428" s="7" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G428" s="11"/>
       <c r="H428" s="7"/>
@@ -23120,7 +23125,7 @@
       <c r="N428" s="11"/>
       <c r="O428" s="7"/>
       <c r="P428" s="7" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="Q428" s="11"/>
       <c r="R428" s="7" t="s">
@@ -23136,21 +23141,21 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="7" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B429" s="11"/>
       <c r="C429" s="11"/>
       <c r="D429" s="7" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="E429" s="11"/>
       <c r="F429" s="7" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G429" s="11"/>
       <c r="H429" s="7"/>
       <c r="I429" s="7" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="J429" s="10"/>
       <c r="K429" s="11"/>
@@ -23159,7 +23164,7 @@
       <c r="N429" s="11"/>
       <c r="O429" s="7"/>
       <c r="P429" s="7" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="Q429" s="11"/>
       <c r="R429" s="7" t="s">
@@ -23175,16 +23180,16 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="7" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B430" s="11"/>
       <c r="C430" s="11"/>
       <c r="D430" s="7" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E430" s="11"/>
       <c r="F430" s="7" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G430" s="11"/>
       <c r="H430" s="7"/>
@@ -23196,7 +23201,7 @@
       <c r="N430" s="11"/>
       <c r="O430" s="7"/>
       <c r="P430" s="7" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="Q430" s="11"/>
       <c r="R430" s="7" t="s">
@@ -23212,21 +23217,21 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="7" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B431" s="11"/>
       <c r="C431" s="11"/>
       <c r="D431" s="7" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E431" s="11"/>
       <c r="F431" s="7" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G431" s="11"/>
       <c r="H431" s="7"/>
       <c r="I431" s="7" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="J431" s="10"/>
       <c r="K431" s="11"/>
@@ -23235,7 +23240,7 @@
       <c r="N431" s="11"/>
       <c r="O431" s="7"/>
       <c r="P431" s="7" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="Q431" s="11"/>
       <c r="R431" s="7" t="s">
@@ -23243,7 +23248,7 @@
       </c>
       <c r="S431" s="11"/>
       <c r="T431" s="7" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="U431" s="11"/>
       <c r="V431" s="7"/>
@@ -23253,16 +23258,16 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="7" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B432" s="11"/>
       <c r="C432" s="11"/>
       <c r="D432" s="7" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="E432" s="11"/>
       <c r="F432" s="7" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G432" s="11"/>
       <c r="H432" s="7"/>
@@ -23274,7 +23279,7 @@
       <c r="N432" s="11"/>
       <c r="O432" s="7"/>
       <c r="P432" s="7" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="Q432" s="11"/>
       <c r="R432" s="7" t="s">
@@ -23290,7 +23295,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="7" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B433" s="11"/>
       <c r="C433" s="11"/>
@@ -23299,7 +23304,7 @@
       </c>
       <c r="E433" s="11"/>
       <c r="F433" s="7" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G433" s="11"/>
       <c r="H433" s="7"/>
@@ -23311,7 +23316,7 @@
       <c r="N433" s="11"/>
       <c r="O433" s="7"/>
       <c r="P433" s="7" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="Q433" s="11"/>
       <c r="R433" s="7" t="s">
@@ -23327,21 +23332,21 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="7" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B434" s="11"/>
       <c r="C434" s="11"/>
       <c r="D434" s="7" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="E434" s="11"/>
       <c r="F434" s="7" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G434" s="11"/>
       <c r="H434" s="7"/>
       <c r="I434" s="7" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="J434" s="10"/>
       <c r="K434" s="11"/>
@@ -23350,7 +23355,7 @@
       <c r="N434" s="11"/>
       <c r="O434" s="7"/>
       <c r="P434" s="7" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="Q434" s="11"/>
       <c r="R434" s="7" t="s">
@@ -23366,12 +23371,12 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="7" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B435" s="11"/>
       <c r="C435" s="11"/>
       <c r="D435" s="7" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="E435" s="11"/>
       <c r="F435" s="7" t="s">
@@ -23380,7 +23385,7 @@
       <c r="G435" s="11"/>
       <c r="H435" s="7"/>
       <c r="I435" s="7" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="J435" s="10"/>
       <c r="K435" s="11"/>
@@ -23389,7 +23394,7 @@
       <c r="N435" s="11"/>
       <c r="O435" s="7"/>
       <c r="P435" s="7" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="Q435" s="11"/>
       <c r="R435" s="7" t="s">
@@ -23397,7 +23402,7 @@
       </c>
       <c r="S435" s="11"/>
       <c r="T435" s="7" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="U435" s="11"/>
       <c r="V435" s="7"/>
@@ -23407,16 +23412,16 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="7" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B436" s="11"/>
       <c r="C436" s="11"/>
       <c r="D436" s="7" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="E436" s="11"/>
       <c r="F436" s="7" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G436" s="11"/>
       <c r="H436" s="7"/>
@@ -23428,7 +23433,7 @@
       <c r="N436" s="11"/>
       <c r="O436" s="7"/>
       <c r="P436" s="7" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="Q436" s="11"/>
       <c r="R436" s="7" t="s">
@@ -23444,12 +23449,12 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="7" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B437" s="11"/>
       <c r="C437" s="11"/>
       <c r="D437" s="7" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="E437" s="11"/>
       <c r="F437" s="7" t="s">
@@ -23465,7 +23470,7 @@
       <c r="N437" s="11"/>
       <c r="O437" s="7"/>
       <c r="P437" s="7" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="Q437" s="11"/>
       <c r="R437" s="7" t="s">
@@ -23481,16 +23486,16 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="7" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B438" s="11"/>
       <c r="C438" s="11"/>
       <c r="D438" s="7" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="E438" s="11"/>
       <c r="F438" s="7" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G438" s="11"/>
       <c r="H438" s="7"/>
@@ -23502,7 +23507,7 @@
       <c r="N438" s="11"/>
       <c r="O438" s="7"/>
       <c r="P438" s="7" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="Q438" s="11"/>
       <c r="R438" s="7" t="s">
@@ -23518,16 +23523,16 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="7" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B439" s="11"/>
       <c r="C439" s="11"/>
       <c r="D439" s="7" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E439" s="11"/>
       <c r="F439" s="7" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G439" s="11"/>
       <c r="H439" s="7"/>
@@ -23539,7 +23544,7 @@
       <c r="N439" s="11"/>
       <c r="O439" s="7"/>
       <c r="P439" s="7" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="Q439" s="11"/>
       <c r="R439" s="7" t="s">
@@ -23547,7 +23552,7 @@
       </c>
       <c r="S439" s="11"/>
       <c r="T439" s="7" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="U439" s="11"/>
       <c r="V439" s="7"/>
@@ -23557,12 +23562,12 @@
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="7" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B440" s="11"/>
       <c r="C440" s="11"/>
       <c r="D440" s="7" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E440" s="11"/>
       <c r="F440" s="7" t="s">
@@ -23578,7 +23583,7 @@
       <c r="N440" s="11"/>
       <c r="O440" s="7"/>
       <c r="P440" s="7" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="Q440" s="11"/>
       <c r="R440" s="7" t="s">
@@ -23594,16 +23599,16 @@
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="7" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B441" s="11"/>
       <c r="C441" s="11"/>
       <c r="D441" s="7" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E441" s="11"/>
       <c r="F441" s="7" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G441" s="11"/>
       <c r="H441" s="7"/>
@@ -23615,7 +23620,7 @@
       <c r="N441" s="11"/>
       <c r="O441" s="7"/>
       <c r="P441" s="7" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="Q441" s="11"/>
       <c r="R441" s="7" t="s">
@@ -23631,18 +23636,18 @@
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="7" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B442" s="11"/>
       <c r="C442" s="11"/>
       <c r="D442" s="7" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E442" s="7" t="s">
         <v>237</v>
       </c>
       <c r="F442" s="7" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="G442" s="11"/>
       <c r="H442" s="7"/>
@@ -23654,7 +23659,7 @@
       <c r="N442" s="11"/>
       <c r="O442" s="7"/>
       <c r="P442" s="7" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="Q442" s="11"/>
       <c r="R442" s="7" t="s">
@@ -23670,7 +23675,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="7" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B443" s="11"/>
       <c r="C443" s="11"/>
@@ -23679,12 +23684,12 @@
       </c>
       <c r="E443" s="11"/>
       <c r="F443" s="7" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G443" s="11"/>
       <c r="H443" s="7"/>
       <c r="I443" s="7" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="J443" s="10"/>
       <c r="K443" s="11"/>
@@ -23693,7 +23698,7 @@
       <c r="N443" s="11"/>
       <c r="O443" s="7"/>
       <c r="P443" s="7" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="Q443" s="11"/>
       <c r="R443" s="7" t="s">
@@ -23709,24 +23714,24 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="7" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B444" s="11"/>
       <c r="C444" s="11"/>
       <c r="D444" s="7" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="E444" s="7" t="s">
         <v>136</v>
       </c>
       <c r="F444" s="7" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G444" s="11"/>
       <c r="H444" s="7"/>
       <c r="I444" s="11"/>
       <c r="J444" s="8" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K444" s="11"/>
       <c r="L444" s="11"/>
@@ -23734,7 +23739,7 @@
       <c r="N444" s="11"/>
       <c r="O444" s="7"/>
       <c r="P444" s="7" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="Q444" s="11"/>
       <c r="R444" s="7" t="s">
@@ -23742,7 +23747,7 @@
       </c>
       <c r="S444" s="11"/>
       <c r="T444" s="7" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="U444" s="11"/>
       <c r="V444" s="7"/>
@@ -23752,16 +23757,16 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="7" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B445" s="11"/>
       <c r="C445" s="11"/>
       <c r="D445" s="7" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E445" s="11"/>
       <c r="F445" s="7" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G445" s="11"/>
       <c r="H445" s="7"/>
@@ -23773,7 +23778,7 @@
       <c r="N445" s="11"/>
       <c r="O445" s="7"/>
       <c r="P445" s="7" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="Q445" s="11"/>
       <c r="R445" s="7" t="s">
@@ -23789,16 +23794,16 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="7" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B446" s="11"/>
       <c r="C446" s="11"/>
       <c r="D446" s="7" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="E446" s="11"/>
       <c r="F446" s="7" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="G446" s="11"/>
       <c r="H446" s="7"/>
@@ -23810,7 +23815,7 @@
       <c r="N446" s="11"/>
       <c r="O446" s="7"/>
       <c r="P446" s="7" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="Q446" s="11"/>
       <c r="R446" s="7" t="s">
@@ -23826,7 +23831,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="7" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B447" s="11"/>
       <c r="C447" s="11"/>
@@ -23835,7 +23840,7 @@
       </c>
       <c r="E447" s="11"/>
       <c r="F447" s="7" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="G447" s="11"/>
       <c r="H447" s="7"/>
@@ -23847,7 +23852,7 @@
       <c r="N447" s="11"/>
       <c r="O447" s="7"/>
       <c r="P447" s="7" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="Q447" s="11"/>
       <c r="R447" s="7" t="s">
@@ -23863,7 +23868,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="7" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B448" s="11"/>
       <c r="C448" s="11"/>
@@ -23886,7 +23891,7 @@
       <c r="N448" s="11"/>
       <c r="O448" s="7"/>
       <c r="P448" s="7" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="Q448" s="11"/>
       <c r="R448" s="7" t="s">
@@ -23902,7 +23907,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="7" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B449" s="11"/>
       <c r="C449" s="11"/>
@@ -23911,7 +23916,7 @@
       </c>
       <c r="E449" s="11"/>
       <c r="F449" s="7" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="G449" s="11"/>
       <c r="H449" s="7"/>
@@ -23923,7 +23928,7 @@
       <c r="N449" s="11"/>
       <c r="O449" s="7"/>
       <c r="P449" s="7" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="Q449" s="11"/>
       <c r="R449" s="7" t="s">
@@ -23939,16 +23944,16 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="7" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B450" s="11"/>
       <c r="C450" s="11"/>
       <c r="D450" s="7" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="E450" s="11"/>
       <c r="F450" s="7" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="G450" s="11"/>
       <c r="H450" s="7"/>
@@ -23960,7 +23965,7 @@
       <c r="N450" s="11"/>
       <c r="O450" s="7"/>
       <c r="P450" s="7" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="Q450" s="11"/>
       <c r="R450" s="7" t="s">
@@ -23976,7 +23981,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B451" s="11"/>
       <c r="C451" s="11"/>
@@ -23997,7 +24002,7 @@
       <c r="N451" s="11"/>
       <c r="O451" s="7"/>
       <c r="P451" s="7" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="Q451" s="11"/>
       <c r="R451" s="7" t="s">
@@ -24013,12 +24018,12 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="7" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B452" s="11"/>
       <c r="C452" s="11"/>
       <c r="D452" s="7" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="E452" s="11"/>
       <c r="F452" s="7" t="s">
@@ -24034,11 +24039,11 @@
       <c r="N452" s="11"/>
       <c r="O452" s="7"/>
       <c r="P452" s="7" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="Q452" s="11"/>
       <c r="R452" s="7" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="S452" s="11"/>
       <c r="T452" s="11"/>
@@ -24050,7 +24055,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="7" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B453" s="11"/>
       <c r="C453" s="11"/>
@@ -24058,7 +24063,7 @@
         <v>1629</v>
       </c>
       <c r="E453" s="7" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="F453" s="7" t="s">
         <v>197</v>
@@ -24073,11 +24078,11 @@
       <c r="N453" s="11"/>
       <c r="O453" s="7"/>
       <c r="P453" s="7" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="Q453" s="11"/>
       <c r="R453" s="7" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="S453" s="11"/>
       <c r="T453" s="11"/>
@@ -24089,16 +24094,16 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="7" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B454" s="11"/>
       <c r="C454" s="11"/>
       <c r="D454" s="7" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="E454" s="11"/>
       <c r="F454" s="7" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="G454" s="11"/>
       <c r="H454" s="7"/>
@@ -24110,11 +24115,11 @@
       <c r="N454" s="11"/>
       <c r="O454" s="7"/>
       <c r="P454" s="7" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="Q454" s="11"/>
       <c r="R454" s="7" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="S454" s="11"/>
       <c r="T454" s="11"/>
@@ -24126,12 +24131,12 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="7" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B455" s="11"/>
       <c r="C455" s="11"/>
       <c r="D455" s="7" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="E455" s="11"/>
       <c r="F455" s="7" t="s">
@@ -24147,11 +24152,11 @@
       <c r="N455" s="11"/>
       <c r="O455" s="7"/>
       <c r="P455" s="7" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="Q455" s="11"/>
       <c r="R455" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S455" s="11"/>
       <c r="T455" s="11"/>
@@ -24163,16 +24168,16 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="7" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B456" s="11"/>
       <c r="C456" s="11"/>
       <c r="D456" s="7" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E456" s="11"/>
       <c r="F456" s="7" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="G456" s="11"/>
       <c r="H456" s="7"/>
@@ -24184,15 +24189,15 @@
       <c r="N456" s="11"/>
       <c r="O456" s="7"/>
       <c r="P456" s="7" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="Q456" s="11"/>
       <c r="R456" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S456" s="11"/>
       <c r="T456" s="7" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="U456" s="11"/>
       <c r="V456" s="7"/>
@@ -24202,12 +24207,12 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="7" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B457" s="11"/>
       <c r="C457" s="11"/>
       <c r="D457" s="7" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="E457" s="11"/>
       <c r="F457" s="7" t="s">
@@ -24223,18 +24228,18 @@
       <c r="N457" s="11"/>
       <c r="O457" s="7"/>
       <c r="P457" s="7" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="Q457" s="11"/>
       <c r="R457" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S457" s="11"/>
       <c r="T457" s="7" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="U457" s="7" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="V457" s="7"/>
       <c r="W457" s="7"/>
@@ -24243,16 +24248,16 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="7" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B458" s="11"/>
       <c r="C458" s="11"/>
       <c r="D458" s="7" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="E458" s="11"/>
       <c r="F458" s="7" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G458" s="11"/>
       <c r="H458" s="7"/>
@@ -24264,15 +24269,15 @@
       <c r="N458" s="11"/>
       <c r="O458" s="7"/>
       <c r="P458" s="7" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="Q458" s="11"/>
       <c r="R458" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S458" s="11"/>
       <c r="T458" s="7" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="U458" s="11"/>
       <c r="V458" s="7"/>
@@ -24282,16 +24287,16 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="7" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B459" s="11"/>
       <c r="C459" s="11"/>
       <c r="D459" s="7" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="E459" s="11"/>
       <c r="F459" s="7" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G459" s="11"/>
       <c r="H459" s="7"/>
@@ -24303,18 +24308,18 @@
       <c r="N459" s="11"/>
       <c r="O459" s="7"/>
       <c r="P459" s="7" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="Q459" s="11"/>
       <c r="R459" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S459" s="11"/>
       <c r="T459" s="7" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="U459" s="7" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="V459" s="7"/>
       <c r="W459" s="7"/>
@@ -24323,18 +24328,18 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="7" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B460" s="11"/>
       <c r="C460" s="11"/>
       <c r="D460" s="7" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="E460" s="7" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="F460" s="7" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="G460" s="11"/>
       <c r="H460" s="7"/>
@@ -24346,15 +24351,15 @@
       <c r="N460" s="11"/>
       <c r="O460" s="7"/>
       <c r="P460" s="7" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="Q460" s="11"/>
       <c r="R460" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S460" s="11"/>
       <c r="T460" s="7" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="U460" s="11"/>
       <c r="V460" s="7"/>
@@ -24364,16 +24369,16 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="7" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B461" s="11"/>
       <c r="C461" s="11"/>
       <c r="D461" s="7" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="E461" s="11"/>
       <c r="F461" s="7" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G461" s="11"/>
       <c r="H461" s="7"/>
@@ -24385,18 +24390,18 @@
       <c r="N461" s="11"/>
       <c r="O461" s="7"/>
       <c r="P461" s="7" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="Q461" s="11"/>
       <c r="R461" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S461" s="11"/>
       <c r="T461" s="7" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="U461" s="7" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="V461" s="7"/>
       <c r="W461" s="7"/>
@@ -24405,16 +24410,16 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="7" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B462" s="11"/>
       <c r="C462" s="11"/>
       <c r="D462" s="7" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="E462" s="11"/>
       <c r="F462" s="7" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="G462" s="11"/>
       <c r="H462" s="7"/>
@@ -24426,15 +24431,15 @@
       <c r="N462" s="11"/>
       <c r="O462" s="7"/>
       <c r="P462" s="7" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="Q462" s="11"/>
       <c r="R462" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S462" s="11"/>
       <c r="T462" s="7" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="U462" s="11"/>
       <c r="V462" s="7"/>
@@ -24444,22 +24449,22 @@
     </row>
     <row r="463" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="7" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B463" s="11"/>
       <c r="C463" s="11"/>
       <c r="D463" s="7" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="E463" s="11"/>
       <c r="F463" s="7" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G463" s="11"/>
       <c r="H463" s="7"/>
       <c r="I463" s="11"/>
       <c r="J463" s="8" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="K463" s="11"/>
       <c r="L463" s="11"/>
@@ -24467,11 +24472,11 @@
       <c r="N463" s="11"/>
       <c r="O463" s="7"/>
       <c r="P463" s="7" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="Q463" s="11"/>
       <c r="R463" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S463" s="11"/>
       <c r="T463" s="11"/>
@@ -24483,16 +24488,16 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="7" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B464" s="11"/>
       <c r="C464" s="11"/>
       <c r="D464" s="7" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="E464" s="11"/>
       <c r="F464" s="7" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G464" s="11"/>
       <c r="H464" s="7"/>
@@ -24504,18 +24509,18 @@
       <c r="N464" s="11"/>
       <c r="O464" s="7"/>
       <c r="P464" s="7" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="Q464" s="11"/>
       <c r="R464" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S464" s="11"/>
       <c r="T464" s="7" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="U464" s="7" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="V464" s="7"/>
       <c r="W464" s="7"/>
@@ -24524,18 +24529,18 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="7" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B465" s="11"/>
       <c r="C465" s="11"/>
       <c r="D465" s="7" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="E465" s="7" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="F465" s="7" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="G465" s="11"/>
       <c r="H465" s="7"/>
@@ -24547,15 +24552,15 @@
       <c r="N465" s="11"/>
       <c r="O465" s="7"/>
       <c r="P465" s="7" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="Q465" s="11"/>
       <c r="R465" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S465" s="11"/>
       <c r="T465" s="7" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="U465" s="11"/>
       <c r="V465" s="7"/>
@@ -24565,12 +24570,12 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="7" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B466" s="11"/>
       <c r="C466" s="11"/>
       <c r="D466" s="7" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="E466" s="11"/>
       <c r="F466" s="7" t="s">
@@ -24586,15 +24591,15 @@
       <c r="N466" s="11"/>
       <c r="O466" s="7"/>
       <c r="P466" s="7" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="Q466" s="11"/>
       <c r="R466" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S466" s="11"/>
       <c r="T466" s="7" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="U466" s="11"/>
       <c r="V466" s="7"/>
@@ -24604,16 +24609,16 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="7" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B467" s="11"/>
       <c r="C467" s="11"/>
       <c r="D467" s="7" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="E467" s="11"/>
       <c r="F467" s="7" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="G467" s="11"/>
       <c r="H467" s="7"/>
@@ -24625,11 +24630,11 @@
       <c r="N467" s="11"/>
       <c r="O467" s="7"/>
       <c r="P467" s="7" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="Q467" s="11"/>
       <c r="R467" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S467" s="11"/>
       <c r="T467" s="11"/>
@@ -24641,7 +24646,7 @@
     </row>
     <row r="468" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="7" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B468" s="11"/>
       <c r="C468" s="11"/>
@@ -24654,22 +24659,22 @@
       <c r="J468" s="10"/>
       <c r="K468" s="11"/>
       <c r="L468" s="7" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="M468" s="11"/>
       <c r="N468" s="11"/>
       <c r="O468" s="7"/>
       <c r="P468" s="7" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="Q468" s="8" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="R468" s="7" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="S468" s="7" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="T468" s="11"/>
       <c r="U468" s="11"/>
@@ -24679,12 +24684,12 @@
       <c r="W468" s="7"/>
       <c r="X468" s="11"/>
       <c r="Y468" s="7" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="7" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B469" s="11"/>
       <c r="C469" s="11"/>
@@ -24697,22 +24702,22 @@
       <c r="J469" s="10"/>
       <c r="K469" s="11"/>
       <c r="L469" s="7" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="M469" s="11"/>
       <c r="N469" s="11"/>
       <c r="O469" s="7"/>
       <c r="P469" s="7" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="Q469" s="7" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="R469" s="7" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="S469" s="7" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="T469" s="11"/>
       <c r="U469" s="11"/>
@@ -24725,16 +24730,16 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="7" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B470" s="11"/>
       <c r="C470" s="11"/>
       <c r="D470" s="7" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="E470" s="11"/>
       <c r="F470" s="7" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G470" s="11"/>
       <c r="H470" s="7"/>
@@ -24746,11 +24751,11 @@
       <c r="N470" s="11"/>
       <c r="O470" s="7"/>
       <c r="P470" s="7" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="Q470" s="11"/>
       <c r="R470" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S470" s="11"/>
       <c r="T470" s="11"/>
@@ -24762,16 +24767,16 @@
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="7" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B471" s="11"/>
       <c r="C471" s="11"/>
       <c r="D471" s="7" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="E471" s="11"/>
       <c r="F471" s="7" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G471" s="11"/>
       <c r="H471" s="7"/>
@@ -24783,14 +24788,14 @@
       <c r="N471" s="11"/>
       <c r="O471" s="7"/>
       <c r="P471" s="7" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="Q471" s="11"/>
       <c r="R471" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="S471" s="7" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="T471" s="11"/>
       <c r="U471" s="11"/>
@@ -24801,21 +24806,21 @@
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="7" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B472" s="11"/>
       <c r="C472" s="11"/>
       <c r="D472" s="7" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="E472" s="11"/>
       <c r="F472" s="7" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G472" s="11"/>
       <c r="H472" s="7"/>
       <c r="I472" s="7" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="J472" s="10"/>
       <c r="K472" s="11"/>
@@ -24824,7 +24829,7 @@
       <c r="N472" s="11"/>
       <c r="O472" s="7"/>
       <c r="P472" s="7" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="Q472" s="11"/>
       <c r="R472" s="7" t="s">
@@ -24832,30 +24837,30 @@
       </c>
       <c r="S472" s="11"/>
       <c r="T472" s="7" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="U472" s="7" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="V472" s="7"/>
       <c r="W472" s="7"/>
       <c r="X472" s="11"/>
       <c r="Y472" s="7" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="7" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B473" s="11"/>
       <c r="C473" s="11"/>
       <c r="D473" s="7" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="E473" s="11"/>
       <c r="F473" s="7" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G473" s="11"/>
       <c r="H473" s="7"/>
@@ -24867,7 +24872,7 @@
       <c r="N473" s="11"/>
       <c r="O473" s="7"/>
       <c r="P473" s="7" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="Q473" s="11"/>
       <c r="R473" s="7" t="s">
@@ -24875,10 +24880,10 @@
       </c>
       <c r="S473" s="11"/>
       <c r="T473" s="7" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="U473" s="7" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="V473" s="7"/>
       <c r="W473" s="7"/>
@@ -24887,16 +24892,16 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="7" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B474" s="11"/>
       <c r="C474" s="11"/>
       <c r="D474" s="7" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="E474" s="11"/>
       <c r="F474" s="7" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G474" s="11"/>
       <c r="H474" s="7"/>
@@ -24908,7 +24913,7 @@
       <c r="N474" s="11"/>
       <c r="O474" s="7"/>
       <c r="P474" s="7" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="Q474" s="11"/>
       <c r="R474" s="7" t="s">
@@ -24916,7 +24921,7 @@
       </c>
       <c r="S474" s="11"/>
       <c r="T474" s="7" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="U474" s="11"/>
       <c r="V474" s="7"/>
@@ -24926,24 +24931,24 @@
     </row>
     <row r="475" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="7" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B475" s="11"/>
       <c r="C475" s="11"/>
       <c r="D475" s="7" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="E475" s="11"/>
       <c r="F475" s="7" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G475" s="11"/>
       <c r="H475" s="7"/>
       <c r="I475" s="7" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="J475" s="8" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="K475" s="11"/>
       <c r="L475" s="11"/>
@@ -24951,7 +24956,7 @@
       <c r="N475" s="11"/>
       <c r="O475" s="7"/>
       <c r="P475" s="7" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="Q475" s="11"/>
       <c r="R475" s="7" t="s">
@@ -24959,7 +24964,7 @@
       </c>
       <c r="S475" s="11"/>
       <c r="T475" s="7" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="U475" s="11"/>
       <c r="V475" s="7"/>
@@ -24969,21 +24974,21 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="7" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B476" s="11"/>
       <c r="C476" s="11"/>
       <c r="D476" s="7" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="E476" s="11"/>
       <c r="F476" s="7" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G476" s="11"/>
       <c r="H476" s="7"/>
       <c r="I476" s="7" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="J476" s="10"/>
       <c r="K476" s="11"/>
@@ -24992,7 +24997,7 @@
       <c r="N476" s="11"/>
       <c r="O476" s="7"/>
       <c r="P476" s="7" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="Q476" s="11"/>
       <c r="R476" s="7" t="s">
@@ -25000,7 +25005,7 @@
       </c>
       <c r="S476" s="11"/>
       <c r="T476" s="7" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="U476" s="11"/>
       <c r="V476" s="7"/>
@@ -25010,16 +25015,16 @@
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="7" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B477" s="11"/>
       <c r="C477" s="11"/>
       <c r="D477" s="7" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="E477" s="11"/>
       <c r="F477" s="7" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G477" s="11"/>
       <c r="H477" s="7"/>
@@ -25031,7 +25036,7 @@
       <c r="N477" s="11"/>
       <c r="O477" s="7"/>
       <c r="P477" s="7" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="Q477" s="11"/>
       <c r="R477" s="7" t="s">
@@ -25039,10 +25044,10 @@
       </c>
       <c r="S477" s="11"/>
       <c r="T477" s="7" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="U477" s="7" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="V477" s="7"/>
       <c r="W477" s="7"/>
@@ -25051,21 +25056,21 @@
     </row>
     <row r="478" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="7" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B478" s="11"/>
       <c r="C478" s="11"/>
       <c r="D478" s="7" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="E478" s="11"/>
       <c r="F478" s="7" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G478" s="11"/>
       <c r="H478" s="7"/>
       <c r="I478" s="7" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="J478" s="10"/>
       <c r="K478" s="11"/>
@@ -25074,7 +25079,7 @@
       <c r="N478" s="11"/>
       <c r="O478" s="7"/>
       <c r="P478" s="7" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="Q478" s="11"/>
       <c r="R478" s="7" t="s">
@@ -25082,32 +25087,32 @@
       </c>
       <c r="S478" s="11"/>
       <c r="T478" s="7" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="U478" s="7" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="V478" s="7"/>
       <c r="W478" s="7"/>
       <c r="X478" s="8" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="Y478" s="7" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="7" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B479" s="11"/>
       <c r="C479" s="11"/>
       <c r="D479" s="7" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="E479" s="11"/>
       <c r="F479" s="7" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G479" s="11"/>
       <c r="H479" s="7"/>
@@ -25119,7 +25124,7 @@
       <c r="N479" s="11"/>
       <c r="O479" s="7"/>
       <c r="P479" s="7" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Q479" s="11"/>
       <c r="R479" s="7" t="s">
@@ -25127,7 +25132,7 @@
       </c>
       <c r="S479" s="11"/>
       <c r="T479" s="7" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="U479" s="11"/>
       <c r="V479" s="7"/>
@@ -25137,24 +25142,24 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="7" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B480" s="11"/>
       <c r="C480" s="11"/>
       <c r="D480" s="7" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="E480" s="11"/>
       <c r="F480" s="7" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G480" s="11"/>
       <c r="H480" s="7"/>
       <c r="I480" s="7" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="J480" s="7" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="K480" s="11"/>
       <c r="L480" s="11"/>
@@ -25162,7 +25167,7 @@
       <c r="N480" s="11"/>
       <c r="O480" s="7"/>
       <c r="P480" s="7" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="Q480" s="11"/>
       <c r="R480" s="7" t="s">
@@ -25170,7 +25175,7 @@
       </c>
       <c r="S480" s="11"/>
       <c r="T480" s="7" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="U480" s="11"/>
       <c r="V480" s="7"/>
@@ -25180,7 +25185,7 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="7" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B481" s="11"/>
       <c r="C481" s="11"/>
@@ -25189,7 +25194,7 @@
       </c>
       <c r="E481" s="11"/>
       <c r="F481" s="7" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G481" s="11"/>
       <c r="H481" s="7"/>
@@ -25201,14 +25206,14 @@
       <c r="N481" s="11"/>
       <c r="O481" s="7"/>
       <c r="P481" s="7" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="Q481" s="11"/>
       <c r="R481" s="7" t="s">
         <v>649</v>
       </c>
       <c r="S481" s="7" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="T481" s="11"/>
       <c r="U481" s="11"/>
@@ -25219,7 +25224,7 @@
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="7" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B482" s="11"/>
       <c r="C482" s="11"/>
@@ -25228,7 +25233,7 @@
       </c>
       <c r="E482" s="11"/>
       <c r="F482" s="7" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G482" s="11"/>
       <c r="H482" s="7"/>
@@ -25240,7 +25245,7 @@
       <c r="N482" s="11"/>
       <c r="O482" s="7"/>
       <c r="P482" s="7" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="Q482" s="11"/>
       <c r="R482" s="7" t="s">
@@ -25248,7 +25253,7 @@
       </c>
       <c r="S482" s="11"/>
       <c r="T482" s="7" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="U482" s="11"/>
       <c r="V482" s="7"/>
@@ -25258,21 +25263,21 @@
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="7" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B483" s="11"/>
       <c r="C483" s="11"/>
       <c r="D483" s="7" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="E483" s="11"/>
       <c r="F483" s="7" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G483" s="11"/>
       <c r="H483" s="7"/>
       <c r="I483" s="7" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="J483" s="10"/>
       <c r="K483" s="11"/>
@@ -25281,7 +25286,7 @@
       <c r="N483" s="11"/>
       <c r="O483" s="7"/>
       <c r="P483" s="7" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="Q483" s="11"/>
       <c r="R483" s="7" t="s">
@@ -25289,7 +25294,7 @@
       </c>
       <c r="S483" s="11"/>
       <c r="T483" s="7" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="U483" s="11"/>
       <c r="V483" s="7"/>
@@ -25299,24 +25304,24 @@
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="7" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B484" s="11"/>
       <c r="C484" s="11"/>
       <c r="D484" s="7" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="E484" s="11"/>
       <c r="F484" s="7" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G484" s="11"/>
       <c r="H484" s="7"/>
       <c r="I484" s="7" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="J484" s="8" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="K484" s="11"/>
       <c r="L484" s="11"/>
@@ -25324,7 +25329,7 @@
       <c r="N484" s="11"/>
       <c r="O484" s="7"/>
       <c r="P484" s="7" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="Q484" s="11"/>
       <c r="R484" s="7" t="s">
@@ -25332,7 +25337,7 @@
       </c>
       <c r="S484" s="11"/>
       <c r="T484" s="7" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="U484" s="11"/>
       <c r="V484" s="7"/>
@@ -25342,21 +25347,21 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="7" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B485" s="11"/>
       <c r="C485" s="11"/>
       <c r="D485" s="7" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="E485" s="11"/>
       <c r="F485" s="7" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G485" s="11"/>
       <c r="H485" s="7"/>
       <c r="I485" s="7" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="J485" s="10"/>
       <c r="K485" s="11"/>
@@ -25365,7 +25370,7 @@
       <c r="N485" s="11"/>
       <c r="O485" s="7"/>
       <c r="P485" s="7" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="Q485" s="11"/>
       <c r="R485" s="7" t="s">
@@ -25373,7 +25378,7 @@
       </c>
       <c r="S485" s="11"/>
       <c r="T485" s="7" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="U485" s="11"/>
       <c r="V485" s="7"/>
@@ -25383,16 +25388,16 @@
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="7" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B486" s="11"/>
       <c r="C486" s="11"/>
       <c r="D486" s="7" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="E486" s="11"/>
       <c r="F486" s="7" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G486" s="11"/>
       <c r="H486" s="7"/>
@@ -25404,7 +25409,7 @@
       <c r="N486" s="11"/>
       <c r="O486" s="7"/>
       <c r="P486" s="7" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Q486" s="11"/>
       <c r="R486" s="7" t="s">
@@ -25420,16 +25425,16 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="7" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B487" s="11"/>
       <c r="C487" s="11"/>
       <c r="D487" s="7" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="E487" s="11"/>
       <c r="F487" s="7" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G487" s="11"/>
       <c r="H487" s="7"/>
@@ -25441,7 +25446,7 @@
       <c r="N487" s="11"/>
       <c r="O487" s="7"/>
       <c r="P487" s="7" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="Q487" s="11"/>
       <c r="R487" s="7" t="s">
@@ -25457,22 +25462,22 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="7" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B488" s="11"/>
       <c r="C488" s="11"/>
       <c r="D488" s="7" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="E488" s="11"/>
       <c r="F488" s="7" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G488" s="11"/>
       <c r="H488" s="7"/>
       <c r="I488" s="11"/>
       <c r="J488" s="8" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="K488" s="11"/>
       <c r="L488" s="11"/>
@@ -25480,7 +25485,7 @@
       <c r="N488" s="11"/>
       <c r="O488" s="7"/>
       <c r="P488" s="7" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="Q488" s="11"/>
       <c r="R488" s="7" t="s">
@@ -25496,16 +25501,16 @@
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="7" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B489" s="11"/>
       <c r="C489" s="11"/>
       <c r="D489" s="7" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="E489" s="11"/>
       <c r="F489" s="7" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G489" s="11"/>
       <c r="H489" s="7"/>
@@ -25517,7 +25522,7 @@
       <c r="N489" s="11"/>
       <c r="O489" s="7"/>
       <c r="P489" s="7" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="Q489" s="11"/>
       <c r="R489" s="7" t="s">
@@ -25525,7 +25530,7 @@
       </c>
       <c r="S489" s="11"/>
       <c r="T489" s="7" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="U489" s="11"/>
       <c r="V489" s="7"/>
@@ -25535,22 +25540,22 @@
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="7" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B490" s="11"/>
       <c r="C490" s="11"/>
       <c r="D490" s="7" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E490" s="11"/>
       <c r="F490" s="7" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G490" s="11"/>
       <c r="H490" s="7"/>
       <c r="I490" s="11"/>
       <c r="J490" s="7" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="K490" s="11"/>
       <c r="L490" s="11"/>
@@ -25558,7 +25563,7 @@
       <c r="N490" s="11"/>
       <c r="O490" s="7"/>
       <c r="P490" s="7" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Q490" s="11"/>
       <c r="R490" s="7" t="s">
@@ -25566,7 +25571,7 @@
       </c>
       <c r="S490" s="11"/>
       <c r="T490" s="7" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="U490" s="11"/>
       <c r="V490" s="7"/>
@@ -25576,12 +25581,12 @@
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="7" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B491" s="11"/>
       <c r="C491" s="11"/>
       <c r="D491" s="7" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E491" s="11"/>
       <c r="F491" s="7" t="s">
@@ -25597,7 +25602,7 @@
       <c r="N491" s="11"/>
       <c r="O491" s="7"/>
       <c r="P491" s="7" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Q491" s="11"/>
       <c r="R491" s="7" t="s">
@@ -25605,7 +25610,7 @@
       </c>
       <c r="S491" s="11"/>
       <c r="T491" s="7" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="U491" s="11"/>
       <c r="V491" s="7"/>
@@ -25615,16 +25620,16 @@
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="7" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B492" s="11"/>
       <c r="C492" s="11"/>
       <c r="D492" s="7" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E492" s="11"/>
       <c r="F492" s="7" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G492" s="11"/>
       <c r="H492" s="7"/>
@@ -25636,7 +25641,7 @@
       <c r="N492" s="11"/>
       <c r="O492" s="7"/>
       <c r="P492" s="7" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q492" s="11"/>
       <c r="R492" s="7" t="s">
@@ -25644,7 +25649,7 @@
       </c>
       <c r="S492" s="11"/>
       <c r="T492" s="7" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="U492" s="11"/>
       <c r="V492" s="7"/>
@@ -25654,21 +25659,21 @@
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="7" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B493" s="11"/>
       <c r="C493" s="11"/>
       <c r="D493" s="7" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E493" s="11"/>
       <c r="F493" s="7" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G493" s="11"/>
       <c r="H493" s="7"/>
       <c r="I493" s="7" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J493" s="10"/>
       <c r="K493" s="11"/>
@@ -25677,7 +25682,7 @@
       <c r="N493" s="11"/>
       <c r="O493" s="7"/>
       <c r="P493" s="7" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="Q493" s="11"/>
       <c r="R493" s="7" t="s">
@@ -25685,7 +25690,7 @@
       </c>
       <c r="S493" s="11"/>
       <c r="T493" s="7" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="U493" s="11"/>
       <c r="V493" s="7"/>
@@ -25695,16 +25700,16 @@
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="7" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B494" s="11"/>
       <c r="C494" s="11"/>
       <c r="D494" s="7" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="E494" s="11"/>
       <c r="F494" s="7" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G494" s="11"/>
       <c r="H494" s="7"/>
@@ -25716,7 +25721,7 @@
       <c r="N494" s="11"/>
       <c r="O494" s="7"/>
       <c r="P494" s="7" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="Q494" s="11"/>
       <c r="R494" s="7" t="s">
@@ -25724,7 +25729,7 @@
       </c>
       <c r="S494" s="11"/>
       <c r="T494" s="7" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="U494" s="11"/>
       <c r="V494" s="7"/>
@@ -25734,16 +25739,16 @@
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="7" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B495" s="11"/>
       <c r="C495" s="11"/>
       <c r="D495" s="7" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="E495" s="11"/>
       <c r="F495" s="7" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G495" s="11"/>
       <c r="H495" s="7"/>
@@ -25755,7 +25760,7 @@
       <c r="N495" s="11"/>
       <c r="O495" s="7"/>
       <c r="P495" s="7" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Q495" s="11"/>
       <c r="R495" s="7" t="s">
@@ -25763,7 +25768,7 @@
       </c>
       <c r="S495" s="11"/>
       <c r="T495" s="7" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="U495" s="11"/>
       <c r="V495" s="7"/>
@@ -25773,16 +25778,16 @@
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="7" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B496" s="11"/>
       <c r="C496" s="11"/>
       <c r="D496" s="7" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="E496" s="11"/>
       <c r="F496" s="7" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G496" s="11"/>
       <c r="H496" s="7"/>
@@ -25794,7 +25799,7 @@
       <c r="N496" s="11"/>
       <c r="O496" s="7"/>
       <c r="P496" s="7" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Q496" s="11"/>
       <c r="R496" s="7" t="s">
@@ -25810,34 +25815,34 @@
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="7" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="C497" s="11"/>
       <c r="D497" s="7" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="E497" s="11"/>
       <c r="F497" s="7" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G497" s="11"/>
       <c r="H497" s="7"/>
       <c r="I497" s="7" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="J497" s="10"/>
       <c r="K497" s="11"/>
       <c r="L497" s="7" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="M497" s="11"/>
       <c r="N497" s="11"/>
       <c r="O497" s="7"/>
       <c r="P497" s="7" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="Q497" s="11"/>
       <c r="R497" s="7" t="s">
@@ -25845,7 +25850,7 @@
       </c>
       <c r="S497" s="11"/>
       <c r="T497" s="7" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="U497" s="11"/>
       <c r="V497" s="7"/>
@@ -25855,10 +25860,10 @@
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="7" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B498" s="7" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="C498" s="11"/>
       <c r="D498" s="11"/>
@@ -25867,18 +25872,18 @@
       <c r="G498" s="11"/>
       <c r="H498" s="7"/>
       <c r="I498" s="7" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="J498" s="10"/>
       <c r="K498" s="11"/>
       <c r="L498" s="7" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="M498" s="11"/>
       <c r="N498" s="11"/>
       <c r="O498" s="7"/>
       <c r="P498" s="7" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="Q498" s="11"/>
       <c r="R498" s="7" t="s">
@@ -25886,7 +25891,7 @@
       </c>
       <c r="S498" s="11"/>
       <c r="T498" s="7" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="U498" s="11"/>
       <c r="V498" s="7"/>
@@ -25896,12 +25901,12 @@
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="7" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B499" s="11"/>
       <c r="C499" s="11"/>
       <c r="D499" s="7" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="E499" s="11"/>
       <c r="F499" s="7" t="s">
@@ -25917,7 +25922,7 @@
       <c r="N499" s="11"/>
       <c r="O499" s="7"/>
       <c r="P499" s="7" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Q499" s="11"/>
       <c r="R499" s="7" t="s">
@@ -25925,7 +25930,7 @@
       </c>
       <c r="S499" s="11"/>
       <c r="T499" s="7" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="U499" s="11"/>
       <c r="V499" s="7"/>
@@ -25935,24 +25940,24 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="7" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B500" s="11"/>
       <c r="C500" s="11"/>
       <c r="D500" s="7" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="E500" s="7" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="F500" s="7" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G500" s="11"/>
       <c r="H500" s="7"/>
       <c r="I500" s="11"/>
       <c r="J500" s="8" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="K500" s="11"/>
       <c r="L500" s="11"/>
@@ -25960,7 +25965,7 @@
       <c r="N500" s="11"/>
       <c r="O500" s="7"/>
       <c r="P500" s="7" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="Q500" s="11"/>
       <c r="R500" s="7" t="s">
@@ -25968,10 +25973,10 @@
       </c>
       <c r="S500" s="11"/>
       <c r="T500" s="7" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="U500" s="7" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="V500" s="7"/>
       <c r="W500" s="7"/>
@@ -25980,21 +25985,21 @@
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="7" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="B501" s="11"/>
       <c r="C501" s="11"/>
       <c r="D501" s="7" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="E501" s="11"/>
       <c r="F501" s="7" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G501" s="11"/>
       <c r="H501" s="7"/>
       <c r="I501" s="7" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="J501" s="10"/>
       <c r="K501" s="11"/>
@@ -26003,7 +26008,7 @@
       <c r="N501" s="11"/>
       <c r="O501" s="7"/>
       <c r="P501" s="7" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="Q501" s="11"/>
       <c r="R501" s="7" t="s">
@@ -26011,7 +26016,7 @@
       </c>
       <c r="S501" s="11"/>
       <c r="T501" s="7" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="U501" s="11"/>
       <c r="V501" s="7"/>
@@ -26021,18 +26026,18 @@
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="7" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B502" s="11"/>
       <c r="C502" s="11"/>
       <c r="D502" s="7" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="E502" s="7" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="F502" s="7" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G502" s="11"/>
       <c r="H502" s="7"/>
@@ -26044,14 +26049,14 @@
       <c r="N502" s="11"/>
       <c r="O502" s="7"/>
       <c r="P502" s="7" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="Q502" s="11"/>
       <c r="R502" s="7" t="s">
         <v>649</v>
       </c>
       <c r="S502" s="7" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="T502" s="11"/>
       <c r="U502" s="11"/>
@@ -26062,16 +26067,16 @@
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="7" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B503" s="11"/>
       <c r="C503" s="11"/>
       <c r="D503" s="7" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="E503" s="11"/>
       <c r="F503" s="7" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G503" s="11"/>
       <c r="H503" s="7"/>
@@ -26083,7 +26088,7 @@
       <c r="N503" s="11"/>
       <c r="O503" s="7"/>
       <c r="P503" s="7" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="Q503" s="11"/>
       <c r="R503" s="7" t="s">
@@ -26099,7 +26104,7 @@
     </row>
     <row r="504" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="7" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B504" s="11"/>
       <c r="C504" s="11"/>
@@ -26110,20 +26115,20 @@
       <c r="H504" s="7"/>
       <c r="I504" s="11"/>
       <c r="J504" s="8" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="K504" s="11"/>
       <c r="L504" s="7" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="M504" s="11"/>
       <c r="N504" s="11"/>
       <c r="O504" s="7"/>
       <c r="P504" s="7" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="Q504" s="8" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="R504" s="7" t="s">
         <v>917</v>
@@ -26137,12 +26142,12 @@
       <c r="W504" s="7"/>
       <c r="X504" s="11"/>
       <c r="Y504" s="7" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="7" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B505" s="11"/>
       <c r="C505" s="11"/>
@@ -26155,20 +26160,20 @@
       <c r="J505" s="10"/>
       <c r="K505" s="11"/>
       <c r="L505" s="7" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="M505" s="11"/>
       <c r="N505" s="11"/>
       <c r="O505" s="7"/>
       <c r="P505" s="7" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="Q505" s="11"/>
       <c r="R505" s="7" t="s">
         <v>917</v>
       </c>
       <c r="S505" s="7" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="T505" s="11"/>
       <c r="U505" s="11"/>
@@ -39572,48 +39577,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39622,7 +39627,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B8" s="16"/>
     </row>
@@ -39631,23 +39636,23 @@
         <v>0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39655,7 +39660,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39663,7 +39668,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39671,7 +39676,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39679,7 +39684,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39687,7 +39692,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39695,7 +39700,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39703,7 +39708,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39711,7 +39716,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39719,7 +39724,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39727,15 +39732,15 @@
         <v>15</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39743,7 +39748,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39751,7 +39756,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39759,7 +39764,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39767,7 +39772,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39775,7 +39780,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39783,7 +39788,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39791,15 +39796,15 @@
         <v>24</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
   </sheetData>

--- a/_data/artists.xlsx
+++ b/_data/artists.xlsx
@@ -310,13 +310,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>86</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -343,13 +343,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>86</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -376,13 +376,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>86</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -409,13 +409,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>86</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -442,13 +442,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>86</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -475,13 +475,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>86</xdr:colOff>
+                <xdr:colOff>145</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -507,14 +507,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -540,14 +540,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -573,14 +573,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -606,14 +606,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -639,14 +639,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -672,14 +672,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -705,14 +705,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -738,14 +738,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>92</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-37</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="2132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="2504">
   <si>
     <t xml:space="preserve">artist</t>
   </si>
@@ -7266,6 +7266,1125 @@
     <t xml:space="preserve">1993 - </t>
   </si>
   <si>
+    <t xml:space="preserve">roman-stabrnak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Štabrňák</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman_Stabrnak.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1983-08-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veronika-zilkova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Žilková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veronika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veronika_Zilkova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1961-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eva-buresova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burešová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva_Buresova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1993-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandra-pogodova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pogodová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandra_Pogodova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1975-04-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jan-dolansky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dolanský</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan_Dolansky.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1978-02-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ondrej-laznovsky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lázňovský</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondřej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej_Laznovsky.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1975-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zuzana-slavikova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slavíková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuzana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuzana_Slavikova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1965-05-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pavel-tesar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesař</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavel_Tesar.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1967-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otto-rosetzky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rošetzký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otto_Rosetzky.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1965-02-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stanislav_lehky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanislav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanislav_Lehky.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1958-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tereza-martinkova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martinková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tereza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tereza_Martinkova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michaela-tomesova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomešová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michaela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michaela Doubravová (&lt;i&gt;maiden name&lt;/i&gt;)
+Míša Tomešová (&lt;i&gt;nickname&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michaela_Tomesova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1991-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sabina-laurinova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurinová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabina_Laurinova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1972-04-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barbora-sediva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Šedivá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora Červinková
+Bára Šedivá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora_Sediva.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1993-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrea-elsnerova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elsnerová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea_Elsnerova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1977-02-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ivana-korolova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korolová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivana Korolová Veselá (&lt;i&gt;married name&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivana_Korolova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1988-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anezka-pohorska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pohorská</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anežka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anezka_Pohorska.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1987-05-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zuzana-kajnarova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kajnarová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuzana Kajnarová Říčařová (&lt;i&gt;married name&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuzana_Kajnarova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1982-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jaroslav-plesl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plesl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaroslav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaroslav_Plesl.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1974-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tomas-bartunek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bartůněk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomáš</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomas_Bartunek.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1964-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zbysek-pantucek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantůček</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zbyšek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zbysek_Pantucek.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1967-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jaroslav-vlach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vlach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaroslav_Vlach.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1949-12-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ales-prochazka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procházka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleš</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ales_Prochazka.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1963-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michal-michalek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michálek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal_Michalek.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1976-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">karel-gult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karel_Gult.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1947-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ondrej-havel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej_Havel.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1994-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eva-spoustova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoustová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva_Spoustova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1965-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jaromir-meduna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meduna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaromír</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaromir_Meduna.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1953-01-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jan-battek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battěk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan_Battek.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1992-02-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">katerina-bohatova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bohatová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kateřina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kateřina Šildová (&lt;i&gt;maiden name&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katerina_Bohatova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1984-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nikola-navratil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navrátil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikola_Navratil.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1984-12-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matous-ruml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matouš</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matous_Ruml.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1985-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zuzana-skalicka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skalická</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuzana_Skalicka.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1958-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jana-zenahlikova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenáhlíková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jana_Zenahlikova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1977-01-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">karolina-kristalova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Křišťálová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karolína</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karolina_Kristalova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zuzana-mixova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuzana_Mixova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1954-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linda-kristalova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linda_Kristalova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jiri-krejci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krejčí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiří</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri_Krejci.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1983-09-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zbysek-horak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horák</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zbysek_Horak.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1966-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">martin-stransky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stránský</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin_Stransky.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970-02-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tereza-bebarova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebarová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tereza_Bebarova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1975-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vladislav-benes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beneš</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vladislav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vladislav_Benes.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1956-11-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jiri-prager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri_Prager.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1951-01-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hana-kusnjerova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kusnjerová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hana_Kusnjerova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1985-05-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lumir-olsovsky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olšovský</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumír</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumir_Olsovsky.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1973-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pavla-beretova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beretová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavla_Beretova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1983-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zdenek-maryska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maryška</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zdeněk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zdenek_Maryska.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1947-04-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patricie-soukupova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soukupová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricie_Soukupova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1995-02-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">martin-pisarik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Písařík</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin_Pisarik.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1979-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anna-novotna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novotná</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna_Novotna.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">david-novotny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novotný</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David_Novotny.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1969-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jitka-mouckova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moučková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jitka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jitka Moučková Špiková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jitka_Mouckova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1979-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tomas-boruvka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borůvka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomas_Boruvka.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1965-05-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">klara-gibisova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gibišová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klára</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klara_Gibisova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">martina-stastna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Šťastná</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martina_Stastna.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1976-12-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucie-cernikova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Černíková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucie_Cernikova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1981-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vendula-prihodova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Příhodová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendula_Prihodova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1989-11-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jan-vondracek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vondráček</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan_Vondracek.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1966-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucie-pukova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucie_Pukova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jiri-panzner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panzner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri_Panzner.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1982-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hana-bernardova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernardová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hana_Bernardova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anna-theimerova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theimerová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna_Theimerova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1984-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicole-tisotova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tisotová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole_Tisotova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1999-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jan-maxian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxián</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan_Maxian.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1983-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michal-kubousek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuboušek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal_Kubousek.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1994-02-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vit-eduard-gajdos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gajdoš</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vít Eduard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vit_Eduard_Gajdos.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ales-fidler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ales_Fidler.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vit-karas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vit_Karas.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1978-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vojtech-kostiha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostiha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vojtěch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vojtech_Kostiha.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1978-01-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robin-kral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Král</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin_Kral.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eliska-mrazova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mrázová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliška</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Mraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliska_Mrazova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1994-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nada-wepperova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wepperová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naďa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nada_Wepperova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1971-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lada-soukupova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lada_Soukupova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucie-novotna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucie_Novotna.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">radek-seidl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seidl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radek_Seidl.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jaromir-holub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaromir_Holub.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guillermo-teillier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teillier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guillermo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guillermo_Teillier.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970-04-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barbora-jezkova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ježková</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora_Jezkova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michaela-sommerova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sommerová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michaela_Sommerova.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magdalena-dziemidowicz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziemidowicz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magdalena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magdalena Snopek (&lt;i&gt;maiden name&lt;/i&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magdalena_Dziemidowicz.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">studio-virtual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio Virtual®</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio_Virtual.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Náměstí 14. října 2/1307, 150 00, Prague 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 September 1994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio Virtual® is the name under which company &lt;b&gt;AMP s.r.o (&lt;i&gt;Art Media Prague&lt;/i&gt;)&lt;/b&gt; provides dubbing and post-production work.&lt;br&gt;
+&lt;br&gt;&lt;small&gt;&lt;i&gt;Source&lt;/i&gt; : &lt;a ref="https://www.studio-virtual.cz/about/" target="_blank" rel="noopener"&gt;Studio Virtual&lt;/a&gt;&lt;/small&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">COMMENT ÇA MARCHE</t>
   </si>
   <si>
@@ -7446,7 +8565,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7530,6 +8649,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -7606,7 +8732,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7663,11 +8789,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7675,11 +8809,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7693,7 +8827,7 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7720,7 +8854,31 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF888888"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8076,7 +9234,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="32.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="40.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="36"/>
@@ -26185,12 +27343,18 @@
       <c r="Y505" s="11"/>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A506" s="7"/>
+      <c r="A506" s="7" t="s">
+        <v>2094</v>
+      </c>
       <c r="B506" s="11"/>
       <c r="C506" s="11"/>
-      <c r="D506" s="11"/>
+      <c r="D506" s="14" t="s">
+        <v>2095</v>
+      </c>
       <c r="E506" s="11"/>
-      <c r="F506" s="11"/>
+      <c r="F506" s="14" t="s">
+        <v>2096</v>
+      </c>
       <c r="G506" s="11"/>
       <c r="H506" s="7"/>
       <c r="I506" s="11"/>
@@ -26200,11 +27364,17 @@
       <c r="M506" s="11"/>
       <c r="N506" s="11"/>
       <c r="O506" s="7"/>
-      <c r="P506" s="7"/>
+      <c r="P506" s="7" t="s">
+        <v>2097</v>
+      </c>
       <c r="Q506" s="11"/>
-      <c r="R506" s="11"/>
+      <c r="R506" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S506" s="11"/>
-      <c r="T506" s="11"/>
+      <c r="T506" s="14" t="s">
+        <v>2099</v>
+      </c>
       <c r="U506" s="11"/>
       <c r="V506" s="7"/>
       <c r="W506" s="7"/>
@@ -26212,12 +27382,18 @@
       <c r="Y506" s="11"/>
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A507" s="7"/>
+      <c r="A507" s="7" t="s">
+        <v>2100</v>
+      </c>
       <c r="B507" s="11"/>
       <c r="C507" s="11"/>
-      <c r="D507" s="11"/>
+      <c r="D507" s="14" t="s">
+        <v>2101</v>
+      </c>
       <c r="E507" s="11"/>
-      <c r="F507" s="11"/>
+      <c r="F507" s="14" t="s">
+        <v>2102</v>
+      </c>
       <c r="G507" s="11"/>
       <c r="H507" s="7"/>
       <c r="I507" s="11"/>
@@ -26227,11 +27403,17 @@
       <c r="M507" s="11"/>
       <c r="N507" s="11"/>
       <c r="O507" s="7"/>
-      <c r="P507" s="7"/>
+      <c r="P507" s="7" t="s">
+        <v>2103</v>
+      </c>
       <c r="Q507" s="11"/>
-      <c r="R507" s="11"/>
+      <c r="R507" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S507" s="11"/>
-      <c r="T507" s="11"/>
+      <c r="T507" s="14" t="s">
+        <v>2104</v>
+      </c>
       <c r="U507" s="11"/>
       <c r="V507" s="7"/>
       <c r="W507" s="7"/>
@@ -26239,12 +27421,18 @@
       <c r="Y507" s="11"/>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A508" s="7"/>
+      <c r="A508" s="7" t="s">
+        <v>2105</v>
+      </c>
       <c r="B508" s="11"/>
       <c r="C508" s="11"/>
-      <c r="D508" s="11"/>
+      <c r="D508" s="14" t="s">
+        <v>2106</v>
+      </c>
       <c r="E508" s="11"/>
-      <c r="F508" s="11"/>
+      <c r="F508" s="14" t="s">
+        <v>229</v>
+      </c>
       <c r="G508" s="11"/>
       <c r="H508" s="7"/>
       <c r="I508" s="11"/>
@@ -26254,11 +27442,17 @@
       <c r="M508" s="11"/>
       <c r="N508" s="11"/>
       <c r="O508" s="7"/>
-      <c r="P508" s="7"/>
+      <c r="P508" s="7" t="s">
+        <v>2107</v>
+      </c>
       <c r="Q508" s="11"/>
-      <c r="R508" s="11"/>
+      <c r="R508" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S508" s="11"/>
-      <c r="T508" s="11"/>
+      <c r="T508" s="14" t="s">
+        <v>2108</v>
+      </c>
       <c r="U508" s="11"/>
       <c r="V508" s="7"/>
       <c r="W508" s="7"/>
@@ -26266,12 +27460,18 @@
       <c r="Y508" s="11"/>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A509" s="7"/>
+      <c r="A509" s="7" t="s">
+        <v>2109</v>
+      </c>
       <c r="B509" s="11"/>
       <c r="C509" s="11"/>
-      <c r="D509" s="11"/>
+      <c r="D509" s="14" t="s">
+        <v>2110</v>
+      </c>
       <c r="E509" s="11"/>
-      <c r="F509" s="11"/>
+      <c r="F509" s="14" t="s">
+        <v>559</v>
+      </c>
       <c r="G509" s="11"/>
       <c r="H509" s="7"/>
       <c r="I509" s="11"/>
@@ -26281,11 +27481,17 @@
       <c r="M509" s="11"/>
       <c r="N509" s="11"/>
       <c r="O509" s="7"/>
-      <c r="P509" s="7"/>
+      <c r="P509" s="7" t="s">
+        <v>2111</v>
+      </c>
       <c r="Q509" s="11"/>
-      <c r="R509" s="11"/>
+      <c r="R509" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S509" s="11"/>
-      <c r="T509" s="11"/>
+      <c r="T509" s="14" t="s">
+        <v>2112</v>
+      </c>
       <c r="U509" s="11"/>
       <c r="V509" s="7"/>
       <c r="W509" s="7"/>
@@ -26293,12 +27499,18 @@
       <c r="Y509" s="11"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A510" s="7"/>
+      <c r="A510" s="7" t="s">
+        <v>2113</v>
+      </c>
       <c r="B510" s="11"/>
       <c r="C510" s="11"/>
-      <c r="D510" s="11"/>
+      <c r="D510" s="14" t="s">
+        <v>2114</v>
+      </c>
       <c r="E510" s="11"/>
-      <c r="F510" s="11"/>
+      <c r="F510" s="14" t="s">
+        <v>2115</v>
+      </c>
       <c r="G510" s="11"/>
       <c r="H510" s="7"/>
       <c r="I510" s="11"/>
@@ -26308,11 +27520,17 @@
       <c r="M510" s="11"/>
       <c r="N510" s="11"/>
       <c r="O510" s="7"/>
-      <c r="P510" s="7"/>
+      <c r="P510" s="7" t="s">
+        <v>2116</v>
+      </c>
       <c r="Q510" s="11"/>
-      <c r="R510" s="11"/>
+      <c r="R510" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S510" s="11"/>
-      <c r="T510" s="11"/>
+      <c r="T510" s="14" t="s">
+        <v>2117</v>
+      </c>
       <c r="U510" s="11"/>
       <c r="V510" s="7"/>
       <c r="W510" s="7"/>
@@ -26320,12 +27538,18 @@
       <c r="Y510" s="11"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A511" s="7"/>
+      <c r="A511" s="7" t="s">
+        <v>2118</v>
+      </c>
       <c r="B511" s="11"/>
       <c r="C511" s="11"/>
-      <c r="D511" s="11"/>
+      <c r="D511" s="14" t="s">
+        <v>2119</v>
+      </c>
       <c r="E511" s="11"/>
-      <c r="F511" s="11"/>
+      <c r="F511" s="14" t="s">
+        <v>2120</v>
+      </c>
       <c r="G511" s="11"/>
       <c r="H511" s="7"/>
       <c r="I511" s="11"/>
@@ -26335,11 +27559,17 @@
       <c r="M511" s="11"/>
       <c r="N511" s="11"/>
       <c r="O511" s="7"/>
-      <c r="P511" s="7"/>
+      <c r="P511" s="7" t="s">
+        <v>2121</v>
+      </c>
       <c r="Q511" s="11"/>
-      <c r="R511" s="11"/>
+      <c r="R511" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S511" s="11"/>
-      <c r="T511" s="11"/>
+      <c r="T511" s="14" t="s">
+        <v>2122</v>
+      </c>
       <c r="U511" s="11"/>
       <c r="V511" s="7"/>
       <c r="W511" s="7"/>
@@ -26347,12 +27577,18 @@
       <c r="Y511" s="11"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A512" s="7"/>
+      <c r="A512" s="7" t="s">
+        <v>2123</v>
+      </c>
       <c r="B512" s="11"/>
       <c r="C512" s="11"/>
-      <c r="D512" s="11"/>
+      <c r="D512" s="14" t="s">
+        <v>2124</v>
+      </c>
       <c r="E512" s="11"/>
-      <c r="F512" s="11"/>
+      <c r="F512" s="14" t="s">
+        <v>2125</v>
+      </c>
       <c r="G512" s="11"/>
       <c r="H512" s="7"/>
       <c r="I512" s="11"/>
@@ -26362,11 +27598,17 @@
       <c r="M512" s="11"/>
       <c r="N512" s="11"/>
       <c r="O512" s="7"/>
-      <c r="P512" s="7"/>
+      <c r="P512" s="7" t="s">
+        <v>2126</v>
+      </c>
       <c r="Q512" s="11"/>
-      <c r="R512" s="11"/>
+      <c r="R512" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S512" s="11"/>
-      <c r="T512" s="11"/>
+      <c r="T512" s="14" t="s">
+        <v>2127</v>
+      </c>
       <c r="U512" s="11"/>
       <c r="V512" s="7"/>
       <c r="W512" s="7"/>
@@ -26374,12 +27616,18 @@
       <c r="Y512" s="11"/>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A513" s="7"/>
+      <c r="A513" s="7" t="s">
+        <v>2128</v>
+      </c>
       <c r="B513" s="11"/>
       <c r="C513" s="11"/>
-      <c r="D513" s="11"/>
+      <c r="D513" s="14" t="s">
+        <v>2129</v>
+      </c>
       <c r="E513" s="11"/>
-      <c r="F513" s="11"/>
+      <c r="F513" s="14" t="s">
+        <v>2130</v>
+      </c>
       <c r="G513" s="11"/>
       <c r="H513" s="7"/>
       <c r="I513" s="11"/>
@@ -26389,11 +27637,17 @@
       <c r="M513" s="11"/>
       <c r="N513" s="11"/>
       <c r="O513" s="7"/>
-      <c r="P513" s="7"/>
+      <c r="P513" s="7" t="s">
+        <v>2131</v>
+      </c>
       <c r="Q513" s="11"/>
-      <c r="R513" s="11"/>
+      <c r="R513" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S513" s="11"/>
-      <c r="T513" s="11"/>
+      <c r="T513" s="14" t="s">
+        <v>2132</v>
+      </c>
       <c r="U513" s="11"/>
       <c r="V513" s="7"/>
       <c r="W513" s="7"/>
@@ -26401,12 +27655,18 @@
       <c r="Y513" s="11"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A514" s="7"/>
+      <c r="A514" s="7" t="s">
+        <v>2133</v>
+      </c>
       <c r="B514" s="11"/>
       <c r="C514" s="11"/>
-      <c r="D514" s="11"/>
+      <c r="D514" s="14" t="s">
+        <v>2134</v>
+      </c>
       <c r="E514" s="11"/>
-      <c r="F514" s="11"/>
+      <c r="F514" s="14" t="s">
+        <v>2135</v>
+      </c>
       <c r="G514" s="11"/>
       <c r="H514" s="7"/>
       <c r="I514" s="11"/>
@@ -26416,11 +27676,17 @@
       <c r="M514" s="11"/>
       <c r="N514" s="11"/>
       <c r="O514" s="7"/>
-      <c r="P514" s="7"/>
+      <c r="P514" s="7" t="s">
+        <v>2136</v>
+      </c>
       <c r="Q514" s="11"/>
-      <c r="R514" s="11"/>
+      <c r="R514" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S514" s="11"/>
-      <c r="T514" s="11"/>
+      <c r="T514" s="14" t="s">
+        <v>2137</v>
+      </c>
       <c r="U514" s="11"/>
       <c r="V514" s="7"/>
       <c r="W514" s="7"/>
@@ -26428,12 +27694,18 @@
       <c r="Y514" s="11"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="7"/>
+      <c r="A515" s="7" t="s">
+        <v>2138</v>
+      </c>
       <c r="B515" s="11"/>
       <c r="C515" s="11"/>
-      <c r="D515" s="11"/>
+      <c r="D515" s="14" t="s">
+        <v>2139</v>
+      </c>
       <c r="E515" s="11"/>
-      <c r="F515" s="11"/>
+      <c r="F515" s="14" t="s">
+        <v>2140</v>
+      </c>
       <c r="G515" s="11"/>
       <c r="H515" s="7"/>
       <c r="I515" s="11"/>
@@ -26443,11 +27715,17 @@
       <c r="M515" s="11"/>
       <c r="N515" s="11"/>
       <c r="O515" s="7"/>
-      <c r="P515" s="7"/>
+      <c r="P515" s="7" t="s">
+        <v>2141</v>
+      </c>
       <c r="Q515" s="11"/>
-      <c r="R515" s="11"/>
+      <c r="R515" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S515" s="11"/>
-      <c r="T515" s="11"/>
+      <c r="T515" s="14" t="s">
+        <v>2142</v>
+      </c>
       <c r="U515" s="11"/>
       <c r="V515" s="7"/>
       <c r="W515" s="7"/>
@@ -26455,12 +27733,18 @@
       <c r="Y515" s="11"/>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A516" s="7"/>
+      <c r="A516" s="7" t="s">
+        <v>2143</v>
+      </c>
       <c r="B516" s="11"/>
       <c r="C516" s="11"/>
-      <c r="D516" s="11"/>
+      <c r="D516" s="14" t="s">
+        <v>2144</v>
+      </c>
       <c r="E516" s="11"/>
-      <c r="F516" s="11"/>
+      <c r="F516" s="14" t="s">
+        <v>2145</v>
+      </c>
       <c r="G516" s="11"/>
       <c r="H516" s="7"/>
       <c r="I516" s="11"/>
@@ -26470,9 +27754,13 @@
       <c r="M516" s="11"/>
       <c r="N516" s="11"/>
       <c r="O516" s="7"/>
-      <c r="P516" s="7"/>
+      <c r="P516" s="7" t="s">
+        <v>2146</v>
+      </c>
       <c r="Q516" s="11"/>
-      <c r="R516" s="11"/>
+      <c r="R516" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S516" s="11"/>
       <c r="T516" s="11"/>
       <c r="U516" s="11"/>
@@ -26481,27 +27769,41 @@
       <c r="X516" s="11"/>
       <c r="Y516" s="11"/>
     </row>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A517" s="7"/>
+    <row r="517" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A517" s="7" t="s">
+        <v>2147</v>
+      </c>
       <c r="B517" s="11"/>
       <c r="C517" s="11"/>
-      <c r="D517" s="11"/>
+      <c r="D517" s="14" t="s">
+        <v>2148</v>
+      </c>
       <c r="E517" s="11"/>
-      <c r="F517" s="11"/>
+      <c r="F517" s="14" t="s">
+        <v>2149</v>
+      </c>
       <c r="G517" s="11"/>
       <c r="H517" s="7"/>
       <c r="I517" s="11"/>
-      <c r="J517" s="10"/>
+      <c r="J517" s="15" t="s">
+        <v>2150</v>
+      </c>
       <c r="K517" s="11"/>
       <c r="L517" s="11"/>
       <c r="M517" s="11"/>
       <c r="N517" s="11"/>
       <c r="O517" s="7"/>
-      <c r="P517" s="7"/>
+      <c r="P517" s="7" t="s">
+        <v>2151</v>
+      </c>
       <c r="Q517" s="11"/>
-      <c r="R517" s="11"/>
+      <c r="R517" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S517" s="11"/>
-      <c r="T517" s="11"/>
+      <c r="T517" s="14" t="s">
+        <v>2152</v>
+      </c>
       <c r="U517" s="11"/>
       <c r="V517" s="7"/>
       <c r="W517" s="7"/>
@@ -26509,12 +27811,18 @@
       <c r="Y517" s="11"/>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A518" s="7"/>
+      <c r="A518" s="7" t="s">
+        <v>2153</v>
+      </c>
       <c r="B518" s="11"/>
       <c r="C518" s="11"/>
-      <c r="D518" s="11"/>
+      <c r="D518" s="14" t="s">
+        <v>2154</v>
+      </c>
       <c r="E518" s="11"/>
-      <c r="F518" s="11"/>
+      <c r="F518" s="14" t="s">
+        <v>2155</v>
+      </c>
       <c r="G518" s="11"/>
       <c r="H518" s="7"/>
       <c r="I518" s="11"/>
@@ -26524,38 +27832,58 @@
       <c r="M518" s="11"/>
       <c r="N518" s="11"/>
       <c r="O518" s="7"/>
-      <c r="P518" s="7"/>
+      <c r="P518" s="7" t="s">
+        <v>2156</v>
+      </c>
       <c r="Q518" s="11"/>
-      <c r="R518" s="11"/>
+      <c r="R518" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S518" s="11"/>
-      <c r="T518" s="11"/>
+      <c r="T518" s="14" t="s">
+        <v>2157</v>
+      </c>
       <c r="U518" s="11"/>
       <c r="V518" s="7"/>
       <c r="W518" s="7"/>
       <c r="X518" s="11"/>
       <c r="Y518" s="11"/>
     </row>
-    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A519" s="7"/>
+    <row r="519" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A519" s="7" t="s">
+        <v>2158</v>
+      </c>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
-      <c r="D519" s="11"/>
+      <c r="D519" s="14" t="s">
+        <v>2159</v>
+      </c>
       <c r="E519" s="11"/>
-      <c r="F519" s="11"/>
+      <c r="F519" s="14" t="s">
+        <v>2160</v>
+      </c>
       <c r="G519" s="11"/>
       <c r="H519" s="7"/>
       <c r="I519" s="11"/>
-      <c r="J519" s="10"/>
+      <c r="J519" s="15" t="s">
+        <v>2161</v>
+      </c>
       <c r="K519" s="11"/>
       <c r="L519" s="11"/>
       <c r="M519" s="11"/>
       <c r="N519" s="11"/>
       <c r="O519" s="7"/>
-      <c r="P519" s="7"/>
+      <c r="P519" s="7" t="s">
+        <v>2162</v>
+      </c>
       <c r="Q519" s="11"/>
-      <c r="R519" s="11"/>
+      <c r="R519" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S519" s="11"/>
-      <c r="T519" s="11"/>
+      <c r="T519" s="14" t="s">
+        <v>2163</v>
+      </c>
       <c r="U519" s="11"/>
       <c r="V519" s="7"/>
       <c r="W519" s="7"/>
@@ -26563,12 +27891,18 @@
       <c r="Y519" s="11"/>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A520" s="7"/>
+      <c r="A520" s="7" t="s">
+        <v>2164</v>
+      </c>
       <c r="B520" s="11"/>
       <c r="C520" s="11"/>
-      <c r="D520" s="11"/>
+      <c r="D520" s="14" t="s">
+        <v>2165</v>
+      </c>
       <c r="E520" s="11"/>
-      <c r="F520" s="11"/>
+      <c r="F520" s="14" t="s">
+        <v>824</v>
+      </c>
       <c r="G520" s="11"/>
       <c r="H520" s="7"/>
       <c r="I520" s="11"/>
@@ -26578,11 +27912,17 @@
       <c r="M520" s="11"/>
       <c r="N520" s="11"/>
       <c r="O520" s="7"/>
-      <c r="P520" s="7"/>
+      <c r="P520" s="7" t="s">
+        <v>2166</v>
+      </c>
       <c r="Q520" s="11"/>
-      <c r="R520" s="11"/>
+      <c r="R520" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S520" s="11"/>
-      <c r="T520" s="11"/>
+      <c r="T520" s="14" t="s">
+        <v>2167</v>
+      </c>
       <c r="U520" s="11"/>
       <c r="V520" s="7"/>
       <c r="W520" s="7"/>
@@ -26590,26 +27930,40 @@
       <c r="Y520" s="11"/>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A521" s="7"/>
+      <c r="A521" s="7" t="s">
+        <v>2168</v>
+      </c>
       <c r="B521" s="11"/>
       <c r="C521" s="11"/>
-      <c r="D521" s="11"/>
+      <c r="D521" s="14" t="s">
+        <v>2169</v>
+      </c>
       <c r="E521" s="11"/>
-      <c r="F521" s="11"/>
+      <c r="F521" s="14" t="s">
+        <v>2170</v>
+      </c>
       <c r="G521" s="11"/>
       <c r="H521" s="7"/>
       <c r="I521" s="11"/>
-      <c r="J521" s="10"/>
+      <c r="J521" s="15" t="s">
+        <v>2171</v>
+      </c>
       <c r="K521" s="11"/>
       <c r="L521" s="11"/>
       <c r="M521" s="11"/>
       <c r="N521" s="11"/>
       <c r="O521" s="7"/>
-      <c r="P521" s="7"/>
+      <c r="P521" s="7" t="s">
+        <v>2172</v>
+      </c>
       <c r="Q521" s="11"/>
-      <c r="R521" s="11"/>
+      <c r="R521" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S521" s="11"/>
-      <c r="T521" s="11"/>
+      <c r="T521" s="14" t="s">
+        <v>2173</v>
+      </c>
       <c r="U521" s="11"/>
       <c r="V521" s="7"/>
       <c r="W521" s="7"/>
@@ -26617,12 +27971,18 @@
       <c r="Y521" s="11"/>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A522" s="7"/>
+      <c r="A522" s="7" t="s">
+        <v>2174</v>
+      </c>
       <c r="B522" s="11"/>
       <c r="C522" s="11"/>
-      <c r="D522" s="11"/>
+      <c r="D522" s="14" t="s">
+        <v>2175</v>
+      </c>
       <c r="E522" s="11"/>
-      <c r="F522" s="11"/>
+      <c r="F522" s="14" t="s">
+        <v>2176</v>
+      </c>
       <c r="G522" s="11"/>
       <c r="H522" s="7"/>
       <c r="I522" s="11"/>
@@ -26632,11 +27992,17 @@
       <c r="M522" s="11"/>
       <c r="N522" s="11"/>
       <c r="O522" s="7"/>
-      <c r="P522" s="7"/>
+      <c r="P522" s="7" t="s">
+        <v>2177</v>
+      </c>
       <c r="Q522" s="11"/>
-      <c r="R522" s="11"/>
+      <c r="R522" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S522" s="11"/>
-      <c r="T522" s="11"/>
+      <c r="T522" s="14" t="s">
+        <v>2178</v>
+      </c>
       <c r="U522" s="11"/>
       <c r="V522" s="7"/>
       <c r="W522" s="7"/>
@@ -26644,26 +28010,40 @@
       <c r="Y522" s="11"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A523" s="7"/>
+      <c r="A523" s="7" t="s">
+        <v>2179</v>
+      </c>
       <c r="B523" s="11"/>
       <c r="C523" s="11"/>
-      <c r="D523" s="11"/>
+      <c r="D523" s="14" t="s">
+        <v>2180</v>
+      </c>
       <c r="E523" s="11"/>
-      <c r="F523" s="11"/>
+      <c r="F523" s="14" t="s">
+        <v>2125</v>
+      </c>
       <c r="G523" s="11"/>
       <c r="H523" s="7"/>
       <c r="I523" s="11"/>
-      <c r="J523" s="10"/>
+      <c r="J523" s="15" t="s">
+        <v>2181</v>
+      </c>
       <c r="K523" s="11"/>
       <c r="L523" s="11"/>
       <c r="M523" s="11"/>
       <c r="N523" s="11"/>
       <c r="O523" s="7"/>
-      <c r="P523" s="7"/>
+      <c r="P523" s="7" t="s">
+        <v>2182</v>
+      </c>
       <c r="Q523" s="11"/>
-      <c r="R523" s="11"/>
+      <c r="R523" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S523" s="11"/>
-      <c r="T523" s="11"/>
+      <c r="T523" s="14" t="s">
+        <v>2183</v>
+      </c>
       <c r="U523" s="11"/>
       <c r="V523" s="7"/>
       <c r="W523" s="7"/>
@@ -26671,12 +28051,18 @@
       <c r="Y523" s="11"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A524" s="7"/>
+      <c r="A524" s="7" t="s">
+        <v>2184</v>
+      </c>
       <c r="B524" s="11"/>
       <c r="C524" s="11"/>
-      <c r="D524" s="11"/>
+      <c r="D524" s="14" t="s">
+        <v>2185</v>
+      </c>
       <c r="E524" s="11"/>
-      <c r="F524" s="11"/>
+      <c r="F524" s="14" t="s">
+        <v>2186</v>
+      </c>
       <c r="G524" s="11"/>
       <c r="H524" s="7"/>
       <c r="I524" s="11"/>
@@ -26686,11 +28072,17 @@
       <c r="M524" s="11"/>
       <c r="N524" s="11"/>
       <c r="O524" s="7"/>
-      <c r="P524" s="7"/>
+      <c r="P524" s="7" t="s">
+        <v>2187</v>
+      </c>
       <c r="Q524" s="11"/>
-      <c r="R524" s="11"/>
+      <c r="R524" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S524" s="11"/>
-      <c r="T524" s="11"/>
+      <c r="T524" s="14" t="s">
+        <v>2188</v>
+      </c>
       <c r="U524" s="11"/>
       <c r="V524" s="7"/>
       <c r="W524" s="7"/>
@@ -26698,12 +28090,18 @@
       <c r="Y524" s="11"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A525" s="7"/>
+      <c r="A525" s="7" t="s">
+        <v>2189</v>
+      </c>
       <c r="B525" s="11"/>
       <c r="C525" s="11"/>
-      <c r="D525" s="11"/>
+      <c r="D525" s="14" t="s">
+        <v>2190</v>
+      </c>
       <c r="E525" s="11"/>
-      <c r="F525" s="11"/>
+      <c r="F525" s="14" t="s">
+        <v>2191</v>
+      </c>
       <c r="G525" s="11"/>
       <c r="H525" s="7"/>
       <c r="I525" s="11"/>
@@ -26713,11 +28111,17 @@
       <c r="M525" s="11"/>
       <c r="N525" s="11"/>
       <c r="O525" s="7"/>
-      <c r="P525" s="7"/>
+      <c r="P525" s="7" t="s">
+        <v>2192</v>
+      </c>
       <c r="Q525" s="11"/>
-      <c r="R525" s="11"/>
+      <c r="R525" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S525" s="11"/>
-      <c r="T525" s="11"/>
+      <c r="T525" s="14" t="s">
+        <v>2193</v>
+      </c>
       <c r="U525" s="11"/>
       <c r="V525" s="7"/>
       <c r="W525" s="7"/>
@@ -26725,12 +28129,18 @@
       <c r="Y525" s="11"/>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A526" s="7"/>
+      <c r="A526" s="7" t="s">
+        <v>2194</v>
+      </c>
       <c r="B526" s="11"/>
       <c r="C526" s="11"/>
-      <c r="D526" s="11"/>
+      <c r="D526" s="14" t="s">
+        <v>2195</v>
+      </c>
       <c r="E526" s="11"/>
-      <c r="F526" s="11"/>
+      <c r="F526" s="14" t="s">
+        <v>2196</v>
+      </c>
       <c r="G526" s="11"/>
       <c r="H526" s="7"/>
       <c r="I526" s="11"/>
@@ -26740,11 +28150,17 @@
       <c r="M526" s="11"/>
       <c r="N526" s="11"/>
       <c r="O526" s="7"/>
-      <c r="P526" s="7"/>
+      <c r="P526" s="7" t="s">
+        <v>2197</v>
+      </c>
       <c r="Q526" s="11"/>
-      <c r="R526" s="11"/>
+      <c r="R526" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S526" s="11"/>
-      <c r="T526" s="11"/>
+      <c r="T526" s="14" t="s">
+        <v>2198</v>
+      </c>
       <c r="U526" s="11"/>
       <c r="V526" s="7"/>
       <c r="W526" s="7"/>
@@ -26752,12 +28168,18 @@
       <c r="Y526" s="11"/>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A527" s="7"/>
+      <c r="A527" s="7" t="s">
+        <v>2199</v>
+      </c>
       <c r="B527" s="11"/>
       <c r="C527" s="11"/>
-      <c r="D527" s="11"/>
+      <c r="D527" s="14" t="s">
+        <v>2200</v>
+      </c>
       <c r="E527" s="11"/>
-      <c r="F527" s="11"/>
+      <c r="F527" s="14" t="s">
+        <v>2186</v>
+      </c>
       <c r="G527" s="11"/>
       <c r="H527" s="7"/>
       <c r="I527" s="11"/>
@@ -26767,11 +28189,17 @@
       <c r="M527" s="11"/>
       <c r="N527" s="11"/>
       <c r="O527" s="7"/>
-      <c r="P527" s="7"/>
+      <c r="P527" s="7" t="s">
+        <v>2201</v>
+      </c>
       <c r="Q527" s="11"/>
-      <c r="R527" s="11"/>
+      <c r="R527" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S527" s="11"/>
-      <c r="T527" s="11"/>
+      <c r="T527" s="14" t="s">
+        <v>2202</v>
+      </c>
       <c r="U527" s="11"/>
       <c r="V527" s="7"/>
       <c r="W527" s="7"/>
@@ -26779,12 +28207,18 @@
       <c r="Y527" s="11"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A528" s="7"/>
+      <c r="A528" s="7" t="s">
+        <v>2203</v>
+      </c>
       <c r="B528" s="11"/>
       <c r="C528" s="11"/>
-      <c r="D528" s="11"/>
+      <c r="D528" s="14" t="s">
+        <v>2204</v>
+      </c>
       <c r="E528" s="11"/>
-      <c r="F528" s="11"/>
+      <c r="F528" s="14" t="s">
+        <v>2205</v>
+      </c>
       <c r="G528" s="11"/>
       <c r="H528" s="7"/>
       <c r="I528" s="11"/>
@@ -26794,11 +28228,17 @@
       <c r="M528" s="11"/>
       <c r="N528" s="11"/>
       <c r="O528" s="7"/>
-      <c r="P528" s="7"/>
+      <c r="P528" s="7" t="s">
+        <v>2206</v>
+      </c>
       <c r="Q528" s="11"/>
-      <c r="R528" s="11"/>
+      <c r="R528" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S528" s="11"/>
-      <c r="T528" s="11"/>
+      <c r="T528" s="14" t="s">
+        <v>2207</v>
+      </c>
       <c r="U528" s="11"/>
       <c r="V528" s="7"/>
       <c r="W528" s="7"/>
@@ -26806,12 +28246,18 @@
       <c r="Y528" s="11"/>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A529" s="7"/>
+      <c r="A529" s="7" t="s">
+        <v>2208</v>
+      </c>
       <c r="B529" s="11"/>
       <c r="C529" s="11"/>
-      <c r="D529" s="11"/>
+      <c r="D529" s="14" t="s">
+        <v>2209</v>
+      </c>
       <c r="E529" s="11"/>
-      <c r="F529" s="11"/>
+      <c r="F529" s="14" t="s">
+        <v>2210</v>
+      </c>
       <c r="G529" s="11"/>
       <c r="H529" s="7"/>
       <c r="I529" s="11"/>
@@ -26821,11 +28267,17 @@
       <c r="M529" s="11"/>
       <c r="N529" s="11"/>
       <c r="O529" s="7"/>
-      <c r="P529" s="7"/>
+      <c r="P529" s="7" t="s">
+        <v>2211</v>
+      </c>
       <c r="Q529" s="11"/>
-      <c r="R529" s="11"/>
+      <c r="R529" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S529" s="11"/>
-      <c r="T529" s="11"/>
+      <c r="T529" s="14" t="s">
+        <v>2212</v>
+      </c>
       <c r="U529" s="11"/>
       <c r="V529" s="7"/>
       <c r="W529" s="7"/>
@@ -26833,12 +28285,18 @@
       <c r="Y529" s="11"/>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A530" s="7"/>
+      <c r="A530" s="7" t="s">
+        <v>2213</v>
+      </c>
       <c r="B530" s="11"/>
       <c r="C530" s="11"/>
-      <c r="D530" s="11"/>
+      <c r="D530" s="14" t="s">
+        <v>2214</v>
+      </c>
       <c r="E530" s="11"/>
-      <c r="F530" s="11"/>
+      <c r="F530" s="14" t="s">
+        <v>2215</v>
+      </c>
       <c r="G530" s="11"/>
       <c r="H530" s="7"/>
       <c r="I530" s="11"/>
@@ -26848,24 +28306,38 @@
       <c r="M530" s="11"/>
       <c r="N530" s="11"/>
       <c r="O530" s="7"/>
-      <c r="P530" s="7"/>
+      <c r="P530" s="7" t="s">
+        <v>2216</v>
+      </c>
       <c r="Q530" s="11"/>
-      <c r="R530" s="11"/>
+      <c r="R530" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S530" s="11"/>
-      <c r="T530" s="11"/>
-      <c r="U530" s="11"/>
+      <c r="T530" s="14" t="s">
+        <v>2217</v>
+      </c>
+      <c r="U530" s="14" t="s">
+        <v>2218</v>
+      </c>
       <c r="V530" s="7"/>
       <c r="W530" s="7"/>
       <c r="X530" s="11"/>
       <c r="Y530" s="11"/>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A531" s="7"/>
+      <c r="A531" s="7" t="s">
+        <v>2219</v>
+      </c>
       <c r="B531" s="11"/>
       <c r="C531" s="11"/>
-      <c r="D531" s="11"/>
+      <c r="D531" s="14" t="s">
+        <v>2220</v>
+      </c>
       <c r="E531" s="11"/>
-      <c r="F531" s="11"/>
+      <c r="F531" s="14" t="s">
+        <v>2120</v>
+      </c>
       <c r="G531" s="11"/>
       <c r="H531" s="7"/>
       <c r="I531" s="11"/>
@@ -26875,11 +28347,17 @@
       <c r="M531" s="11"/>
       <c r="N531" s="11"/>
       <c r="O531" s="7"/>
-      <c r="P531" s="7"/>
+      <c r="P531" s="7" t="s">
+        <v>2221</v>
+      </c>
       <c r="Q531" s="11"/>
-      <c r="R531" s="11"/>
+      <c r="R531" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S531" s="11"/>
-      <c r="T531" s="11"/>
+      <c r="T531" s="14" t="s">
+        <v>2222</v>
+      </c>
       <c r="U531" s="11"/>
       <c r="V531" s="7"/>
       <c r="W531" s="7"/>
@@ -26887,12 +28365,18 @@
       <c r="Y531" s="11"/>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A532" s="7"/>
+      <c r="A532" s="7" t="s">
+        <v>2223</v>
+      </c>
       <c r="B532" s="11"/>
       <c r="C532" s="11"/>
-      <c r="D532" s="11"/>
+      <c r="D532" s="14" t="s">
+        <v>2224</v>
+      </c>
       <c r="E532" s="11"/>
-      <c r="F532" s="11"/>
+      <c r="F532" s="14" t="s">
+        <v>229</v>
+      </c>
       <c r="G532" s="11"/>
       <c r="H532" s="7"/>
       <c r="I532" s="11"/>
@@ -26902,11 +28386,17 @@
       <c r="M532" s="11"/>
       <c r="N532" s="11"/>
       <c r="O532" s="7"/>
-      <c r="P532" s="7"/>
+      <c r="P532" s="7" t="s">
+        <v>2225</v>
+      </c>
       <c r="Q532" s="11"/>
-      <c r="R532" s="11"/>
+      <c r="R532" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S532" s="11"/>
-      <c r="T532" s="11"/>
+      <c r="T532" s="14" t="s">
+        <v>2226</v>
+      </c>
       <c r="U532" s="11"/>
       <c r="V532" s="7"/>
       <c r="W532" s="7"/>
@@ -26914,12 +28404,18 @@
       <c r="Y532" s="11"/>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A533" s="7"/>
+      <c r="A533" s="7" t="s">
+        <v>2227</v>
+      </c>
       <c r="B533" s="11"/>
       <c r="C533" s="11"/>
-      <c r="D533" s="11"/>
+      <c r="D533" s="14" t="s">
+        <v>2228</v>
+      </c>
       <c r="E533" s="11"/>
-      <c r="F533" s="11"/>
+      <c r="F533" s="14" t="s">
+        <v>2229</v>
+      </c>
       <c r="G533" s="11"/>
       <c r="H533" s="7"/>
       <c r="I533" s="11"/>
@@ -26929,11 +28425,17 @@
       <c r="M533" s="11"/>
       <c r="N533" s="11"/>
       <c r="O533" s="7"/>
-      <c r="P533" s="7"/>
+      <c r="P533" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="Q533" s="11"/>
-      <c r="R533" s="11"/>
+      <c r="R533" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S533" s="11"/>
-      <c r="T533" s="11"/>
+      <c r="T533" s="14" t="s">
+        <v>2231</v>
+      </c>
       <c r="U533" s="11"/>
       <c r="V533" s="7"/>
       <c r="W533" s="7"/>
@@ -26941,12 +28443,18 @@
       <c r="Y533" s="11"/>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A534" s="7"/>
+      <c r="A534" s="7" t="s">
+        <v>2232</v>
+      </c>
       <c r="B534" s="11"/>
       <c r="C534" s="11"/>
-      <c r="D534" s="11"/>
+      <c r="D534" s="14" t="s">
+        <v>2233</v>
+      </c>
       <c r="E534" s="11"/>
-      <c r="F534" s="11"/>
+      <c r="F534" s="14" t="s">
+        <v>2115</v>
+      </c>
       <c r="G534" s="11"/>
       <c r="H534" s="7"/>
       <c r="I534" s="11"/>
@@ -26956,11 +28464,17 @@
       <c r="M534" s="11"/>
       <c r="N534" s="11"/>
       <c r="O534" s="7"/>
-      <c r="P534" s="7"/>
+      <c r="P534" s="7" t="s">
+        <v>2234</v>
+      </c>
       <c r="Q534" s="11"/>
-      <c r="R534" s="11"/>
+      <c r="R534" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S534" s="11"/>
-      <c r="T534" s="11"/>
+      <c r="T534" s="14" t="s">
+        <v>2235</v>
+      </c>
       <c r="U534" s="11"/>
       <c r="V534" s="7"/>
       <c r="W534" s="7"/>
@@ -26968,26 +28482,40 @@
       <c r="Y534" s="11"/>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A535" s="7"/>
+      <c r="A535" s="7" t="s">
+        <v>2236</v>
+      </c>
       <c r="B535" s="11"/>
       <c r="C535" s="11"/>
-      <c r="D535" s="11"/>
+      <c r="D535" s="14" t="s">
+        <v>2237</v>
+      </c>
       <c r="E535" s="11"/>
-      <c r="F535" s="11"/>
+      <c r="F535" s="14" t="s">
+        <v>2238</v>
+      </c>
       <c r="G535" s="11"/>
       <c r="H535" s="7"/>
       <c r="I535" s="11"/>
-      <c r="J535" s="10"/>
+      <c r="J535" s="15" t="s">
+        <v>2239</v>
+      </c>
       <c r="K535" s="11"/>
       <c r="L535" s="11"/>
       <c r="M535" s="11"/>
       <c r="N535" s="11"/>
       <c r="O535" s="7"/>
-      <c r="P535" s="7"/>
+      <c r="P535" s="7" t="s">
+        <v>2240</v>
+      </c>
       <c r="Q535" s="11"/>
-      <c r="R535" s="11"/>
+      <c r="R535" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S535" s="11"/>
-      <c r="T535" s="11"/>
+      <c r="T535" s="14" t="s">
+        <v>2241</v>
+      </c>
       <c r="U535" s="11"/>
       <c r="V535" s="7"/>
       <c r="W535" s="7"/>
@@ -26995,12 +28523,18 @@
       <c r="Y535" s="11"/>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A536" s="7"/>
+      <c r="A536" s="7" t="s">
+        <v>2242</v>
+      </c>
       <c r="B536" s="11"/>
       <c r="C536" s="11"/>
-      <c r="D536" s="11"/>
+      <c r="D536" s="14" t="s">
+        <v>2243</v>
+      </c>
       <c r="E536" s="11"/>
-      <c r="F536" s="11"/>
+      <c r="F536" s="14" t="s">
+        <v>2244</v>
+      </c>
       <c r="G536" s="11"/>
       <c r="H536" s="7"/>
       <c r="I536" s="11"/>
@@ -27010,11 +28544,17 @@
       <c r="M536" s="11"/>
       <c r="N536" s="11"/>
       <c r="O536" s="7"/>
-      <c r="P536" s="7"/>
+      <c r="P536" s="7" t="s">
+        <v>2245</v>
+      </c>
       <c r="Q536" s="11"/>
-      <c r="R536" s="11"/>
+      <c r="R536" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S536" s="11"/>
-      <c r="T536" s="11"/>
+      <c r="T536" s="14" t="s">
+        <v>2246</v>
+      </c>
       <c r="U536" s="11"/>
       <c r="V536" s="7"/>
       <c r="W536" s="7"/>
@@ -27022,12 +28562,18 @@
       <c r="Y536" s="11"/>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A537" s="7"/>
+      <c r="A537" s="7" t="s">
+        <v>2247</v>
+      </c>
       <c r="B537" s="11"/>
       <c r="C537" s="11"/>
-      <c r="D537" s="11"/>
+      <c r="D537" s="14" t="s">
+        <v>2248</v>
+      </c>
       <c r="E537" s="11"/>
-      <c r="F537" s="11"/>
+      <c r="F537" s="14" t="s">
+        <v>2249</v>
+      </c>
       <c r="G537" s="11"/>
       <c r="H537" s="7"/>
       <c r="I537" s="11"/>
@@ -27037,11 +28583,17 @@
       <c r="M537" s="11"/>
       <c r="N537" s="11"/>
       <c r="O537" s="7"/>
-      <c r="P537" s="7"/>
+      <c r="P537" s="7" t="s">
+        <v>2250</v>
+      </c>
       <c r="Q537" s="11"/>
-      <c r="R537" s="11"/>
+      <c r="R537" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S537" s="11"/>
-      <c r="T537" s="11"/>
+      <c r="T537" s="14" t="s">
+        <v>2251</v>
+      </c>
       <c r="U537" s="11"/>
       <c r="V537" s="7"/>
       <c r="W537" s="7"/>
@@ -27049,12 +28601,18 @@
       <c r="Y537" s="11"/>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A538" s="7"/>
+      <c r="A538" s="7" t="s">
+        <v>2252</v>
+      </c>
       <c r="B538" s="11"/>
       <c r="C538" s="11"/>
-      <c r="D538" s="11"/>
+      <c r="D538" s="14" t="s">
+        <v>2253</v>
+      </c>
       <c r="E538" s="11"/>
-      <c r="F538" s="11"/>
+      <c r="F538" s="14" t="s">
+        <v>2125</v>
+      </c>
       <c r="G538" s="11"/>
       <c r="H538" s="7"/>
       <c r="I538" s="11"/>
@@ -27064,11 +28622,17 @@
       <c r="M538" s="11"/>
       <c r="N538" s="11"/>
       <c r="O538" s="7"/>
-      <c r="P538" s="7"/>
+      <c r="P538" s="7" t="s">
+        <v>2254</v>
+      </c>
       <c r="Q538" s="11"/>
-      <c r="R538" s="11"/>
+      <c r="R538" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S538" s="11"/>
-      <c r="T538" s="11"/>
+      <c r="T538" s="14" t="s">
+        <v>2255</v>
+      </c>
       <c r="U538" s="11"/>
       <c r="V538" s="7"/>
       <c r="W538" s="7"/>
@@ -27076,12 +28640,18 @@
       <c r="Y538" s="11"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A539" s="7"/>
+      <c r="A539" s="7" t="s">
+        <v>2256</v>
+      </c>
       <c r="B539" s="11"/>
       <c r="C539" s="11"/>
-      <c r="D539" s="11"/>
+      <c r="D539" s="14" t="s">
+        <v>2257</v>
+      </c>
       <c r="E539" s="11"/>
-      <c r="F539" s="11"/>
+      <c r="F539" s="14" t="s">
+        <v>1138</v>
+      </c>
       <c r="G539" s="11"/>
       <c r="H539" s="7"/>
       <c r="I539" s="11"/>
@@ -27091,11 +28661,17 @@
       <c r="M539" s="11"/>
       <c r="N539" s="11"/>
       <c r="O539" s="7"/>
-      <c r="P539" s="7"/>
+      <c r="P539" s="7" t="s">
+        <v>2258</v>
+      </c>
       <c r="Q539" s="11"/>
-      <c r="R539" s="11"/>
+      <c r="R539" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S539" s="11"/>
-      <c r="T539" s="11"/>
+      <c r="T539" s="14" t="s">
+        <v>2259</v>
+      </c>
       <c r="U539" s="11"/>
       <c r="V539" s="7"/>
       <c r="W539" s="7"/>
@@ -27103,12 +28679,18 @@
       <c r="Y539" s="11"/>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A540" s="7"/>
+      <c r="A540" s="7" t="s">
+        <v>2260</v>
+      </c>
       <c r="B540" s="11"/>
       <c r="C540" s="11"/>
-      <c r="D540" s="11"/>
+      <c r="D540" s="14" t="s">
+        <v>2261</v>
+      </c>
       <c r="E540" s="11"/>
-      <c r="F540" s="11"/>
+      <c r="F540" s="14" t="s">
+        <v>2262</v>
+      </c>
       <c r="G540" s="11"/>
       <c r="H540" s="7"/>
       <c r="I540" s="11"/>
@@ -27118,11 +28700,17 @@
       <c r="M540" s="11"/>
       <c r="N540" s="11"/>
       <c r="O540" s="7"/>
-      <c r="P540" s="7"/>
+      <c r="P540" s="7" t="s">
+        <v>2263</v>
+      </c>
       <c r="Q540" s="11"/>
-      <c r="R540" s="11"/>
+      <c r="R540" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S540" s="11"/>
-      <c r="T540" s="11"/>
+      <c r="T540" s="14" t="s">
+        <v>2264</v>
+      </c>
       <c r="U540" s="11"/>
       <c r="V540" s="7"/>
       <c r="W540" s="7"/>
@@ -27130,12 +28718,18 @@
       <c r="Y540" s="11"/>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A541" s="7"/>
+      <c r="A541" s="7" t="s">
+        <v>2265</v>
+      </c>
       <c r="B541" s="11"/>
       <c r="C541" s="11"/>
-      <c r="D541" s="11"/>
+      <c r="D541" s="14" t="s">
+        <v>2266</v>
+      </c>
       <c r="E541" s="11"/>
-      <c r="F541" s="11"/>
+      <c r="F541" s="14" t="s">
+        <v>2125</v>
+      </c>
       <c r="G541" s="11"/>
       <c r="H541" s="7"/>
       <c r="I541" s="11"/>
@@ -27145,11 +28739,17 @@
       <c r="M541" s="11"/>
       <c r="N541" s="11"/>
       <c r="O541" s="7"/>
-      <c r="P541" s="7"/>
+      <c r="P541" s="7" t="s">
+        <v>2267</v>
+      </c>
       <c r="Q541" s="11"/>
-      <c r="R541" s="11"/>
+      <c r="R541" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S541" s="11"/>
-      <c r="T541" s="11"/>
+      <c r="T541" s="14" t="s">
+        <v>2268</v>
+      </c>
       <c r="U541" s="11"/>
       <c r="V541" s="7"/>
       <c r="W541" s="7"/>
@@ -27157,12 +28757,18 @@
       <c r="Y541" s="11"/>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A542" s="7"/>
+      <c r="A542" s="7" t="s">
+        <v>2269</v>
+      </c>
       <c r="B542" s="11"/>
       <c r="C542" s="11"/>
-      <c r="D542" s="11"/>
+      <c r="D542" s="14" t="s">
+        <v>2261</v>
+      </c>
       <c r="E542" s="11"/>
-      <c r="F542" s="11"/>
+      <c r="F542" s="14" t="s">
+        <v>1489</v>
+      </c>
       <c r="G542" s="11"/>
       <c r="H542" s="7"/>
       <c r="I542" s="11"/>
@@ -27172,11 +28778,17 @@
       <c r="M542" s="11"/>
       <c r="N542" s="11"/>
       <c r="O542" s="7"/>
-      <c r="P542" s="7"/>
+      <c r="P542" s="7" t="s">
+        <v>2270</v>
+      </c>
       <c r="Q542" s="11"/>
-      <c r="R542" s="11"/>
+      <c r="R542" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S542" s="11"/>
-      <c r="T542" s="11"/>
+      <c r="T542" s="14" t="s">
+        <v>2271</v>
+      </c>
       <c r="U542" s="11"/>
       <c r="V542" s="7"/>
       <c r="W542" s="7"/>
@@ -27184,12 +28796,18 @@
       <c r="Y542" s="11"/>
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A543" s="7"/>
+      <c r="A543" s="7" t="s">
+        <v>2272</v>
+      </c>
       <c r="B543" s="11"/>
       <c r="C543" s="11"/>
-      <c r="D543" s="11"/>
+      <c r="D543" s="14" t="s">
+        <v>2273</v>
+      </c>
       <c r="E543" s="11"/>
-      <c r="F543" s="11"/>
+      <c r="F543" s="14" t="s">
+        <v>2274</v>
+      </c>
       <c r="G543" s="11"/>
       <c r="H543" s="7"/>
       <c r="I543" s="11"/>
@@ -27199,11 +28817,17 @@
       <c r="M543" s="11"/>
       <c r="N543" s="11"/>
       <c r="O543" s="7"/>
-      <c r="P543" s="7"/>
+      <c r="P543" s="7" t="s">
+        <v>2275</v>
+      </c>
       <c r="Q543" s="11"/>
-      <c r="R543" s="11"/>
+      <c r="R543" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S543" s="11"/>
-      <c r="T543" s="11"/>
+      <c r="T543" s="14" t="s">
+        <v>2276</v>
+      </c>
       <c r="U543" s="11"/>
       <c r="V543" s="7"/>
       <c r="W543" s="7"/>
@@ -27211,12 +28835,18 @@
       <c r="Y543" s="11"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A544" s="7"/>
+      <c r="A544" s="7" t="s">
+        <v>2277</v>
+      </c>
       <c r="B544" s="11"/>
       <c r="C544" s="11"/>
-      <c r="D544" s="11"/>
+      <c r="D544" s="14" t="s">
+        <v>2278</v>
+      </c>
       <c r="E544" s="11"/>
-      <c r="F544" s="11"/>
+      <c r="F544" s="14" t="s">
+        <v>2196</v>
+      </c>
       <c r="G544" s="11"/>
       <c r="H544" s="7"/>
       <c r="I544" s="11"/>
@@ -27226,11 +28856,17 @@
       <c r="M544" s="11"/>
       <c r="N544" s="11"/>
       <c r="O544" s="7"/>
-      <c r="P544" s="7"/>
+      <c r="P544" s="7" t="s">
+        <v>2279</v>
+      </c>
       <c r="Q544" s="11"/>
-      <c r="R544" s="11"/>
+      <c r="R544" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S544" s="11"/>
-      <c r="T544" s="11"/>
+      <c r="T544" s="14" t="s">
+        <v>2280</v>
+      </c>
       <c r="U544" s="11"/>
       <c r="V544" s="7"/>
       <c r="W544" s="7"/>
@@ -27238,12 +28874,18 @@
       <c r="Y544" s="11"/>
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A545" s="7"/>
+      <c r="A545" s="7" t="s">
+        <v>2281</v>
+      </c>
       <c r="B545" s="11"/>
       <c r="C545" s="11"/>
-      <c r="D545" s="11"/>
+      <c r="D545" s="14" t="s">
+        <v>2282</v>
+      </c>
       <c r="E545" s="11"/>
-      <c r="F545" s="11"/>
+      <c r="F545" s="14" t="s">
+        <v>2283</v>
+      </c>
       <c r="G545" s="11"/>
       <c r="H545" s="7"/>
       <c r="I545" s="11"/>
@@ -27253,11 +28895,17 @@
       <c r="M545" s="11"/>
       <c r="N545" s="11"/>
       <c r="O545" s="7"/>
-      <c r="P545" s="7"/>
+      <c r="P545" s="7" t="s">
+        <v>2284</v>
+      </c>
       <c r="Q545" s="11"/>
-      <c r="R545" s="11"/>
+      <c r="R545" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S545" s="11"/>
-      <c r="T545" s="11"/>
+      <c r="T545" s="14" t="s">
+        <v>2285</v>
+      </c>
       <c r="U545" s="11"/>
       <c r="V545" s="7"/>
       <c r="W545" s="7"/>
@@ -27265,12 +28913,18 @@
       <c r="Y545" s="11"/>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A546" s="7"/>
+      <c r="A546" s="7" t="s">
+        <v>2286</v>
+      </c>
       <c r="B546" s="11"/>
       <c r="C546" s="11"/>
-      <c r="D546" s="11"/>
+      <c r="D546" s="14" t="s">
+        <v>2287</v>
+      </c>
       <c r="E546" s="11"/>
-      <c r="F546" s="11"/>
+      <c r="F546" s="14" t="s">
+        <v>2145</v>
+      </c>
       <c r="G546" s="11"/>
       <c r="H546" s="7"/>
       <c r="I546" s="11"/>
@@ -27280,11 +28934,17 @@
       <c r="M546" s="11"/>
       <c r="N546" s="11"/>
       <c r="O546" s="7"/>
-      <c r="P546" s="7"/>
+      <c r="P546" s="7" t="s">
+        <v>2288</v>
+      </c>
       <c r="Q546" s="11"/>
-      <c r="R546" s="11"/>
+      <c r="R546" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S546" s="11"/>
-      <c r="T546" s="11"/>
+      <c r="T546" s="14" t="s">
+        <v>2289</v>
+      </c>
       <c r="U546" s="11"/>
       <c r="V546" s="7"/>
       <c r="W546" s="7"/>
@@ -27292,12 +28952,18 @@
       <c r="Y546" s="11"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A547" s="7"/>
+      <c r="A547" s="7" t="s">
+        <v>2290</v>
+      </c>
       <c r="B547" s="11"/>
       <c r="C547" s="11"/>
-      <c r="D547" s="11"/>
+      <c r="D547" s="14" t="s">
+        <v>2291</v>
+      </c>
       <c r="E547" s="11"/>
-      <c r="F547" s="11"/>
+      <c r="F547" s="14" t="s">
+        <v>2292</v>
+      </c>
       <c r="G547" s="11"/>
       <c r="H547" s="7"/>
       <c r="I547" s="11"/>
@@ -27307,11 +28973,17 @@
       <c r="M547" s="11"/>
       <c r="N547" s="11"/>
       <c r="O547" s="7"/>
-      <c r="P547" s="7"/>
+      <c r="P547" s="7" t="s">
+        <v>2293</v>
+      </c>
       <c r="Q547" s="11"/>
-      <c r="R547" s="11"/>
+      <c r="R547" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S547" s="11"/>
-      <c r="T547" s="11"/>
+      <c r="T547" s="14" t="s">
+        <v>2294</v>
+      </c>
       <c r="U547" s="11"/>
       <c r="V547" s="7"/>
       <c r="W547" s="7"/>
@@ -27319,12 +28991,18 @@
       <c r="Y547" s="11"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A548" s="7"/>
+      <c r="A548" s="7" t="s">
+        <v>2295</v>
+      </c>
       <c r="B548" s="11"/>
       <c r="C548" s="11"/>
-      <c r="D548" s="11"/>
+      <c r="D548" s="14" t="s">
+        <v>2296</v>
+      </c>
       <c r="E548" s="11"/>
-      <c r="F548" s="11"/>
+      <c r="F548" s="14" t="s">
+        <v>2274</v>
+      </c>
       <c r="G548" s="11"/>
       <c r="H548" s="7"/>
       <c r="I548" s="11"/>
@@ -27334,11 +29012,17 @@
       <c r="M548" s="11"/>
       <c r="N548" s="11"/>
       <c r="O548" s="7"/>
-      <c r="P548" s="7"/>
+      <c r="P548" s="7" t="s">
+        <v>2297</v>
+      </c>
       <c r="Q548" s="11"/>
-      <c r="R548" s="11"/>
+      <c r="R548" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S548" s="11"/>
-      <c r="T548" s="11"/>
+      <c r="T548" s="14" t="s">
+        <v>2298</v>
+      </c>
       <c r="U548" s="11"/>
       <c r="V548" s="7"/>
       <c r="W548" s="7"/>
@@ -27346,12 +29030,18 @@
       <c r="Y548" s="11"/>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A549" s="7"/>
+      <c r="A549" s="7" t="s">
+        <v>2299</v>
+      </c>
       <c r="B549" s="11"/>
       <c r="C549" s="11"/>
-      <c r="D549" s="11"/>
+      <c r="D549" s="14" t="s">
+        <v>2300</v>
+      </c>
       <c r="E549" s="11"/>
-      <c r="F549" s="11"/>
+      <c r="F549" s="14" t="s">
+        <v>2301</v>
+      </c>
       <c r="G549" s="11"/>
       <c r="H549" s="7"/>
       <c r="I549" s="11"/>
@@ -27361,11 +29051,17 @@
       <c r="M549" s="11"/>
       <c r="N549" s="11"/>
       <c r="O549" s="7"/>
-      <c r="P549" s="7"/>
+      <c r="P549" s="7" t="s">
+        <v>2302</v>
+      </c>
       <c r="Q549" s="11"/>
-      <c r="R549" s="11"/>
+      <c r="R549" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S549" s="11"/>
-      <c r="T549" s="11"/>
+      <c r="T549" s="14" t="s">
+        <v>2303</v>
+      </c>
       <c r="U549" s="11"/>
       <c r="V549" s="7"/>
       <c r="W549" s="7"/>
@@ -27373,12 +29069,18 @@
       <c r="Y549" s="11"/>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A550" s="7"/>
+      <c r="A550" s="7" t="s">
+        <v>2304</v>
+      </c>
       <c r="B550" s="11"/>
       <c r="C550" s="11"/>
-      <c r="D550" s="11"/>
+      <c r="D550" s="14" t="s">
+        <v>2305</v>
+      </c>
       <c r="E550" s="11"/>
-      <c r="F550" s="11"/>
+      <c r="F550" s="14" t="s">
+        <v>2306</v>
+      </c>
       <c r="G550" s="11"/>
       <c r="H550" s="7"/>
       <c r="I550" s="11"/>
@@ -27388,11 +29090,17 @@
       <c r="M550" s="11"/>
       <c r="N550" s="11"/>
       <c r="O550" s="7"/>
-      <c r="P550" s="7"/>
+      <c r="P550" s="7" t="s">
+        <v>2307</v>
+      </c>
       <c r="Q550" s="11"/>
-      <c r="R550" s="11"/>
+      <c r="R550" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S550" s="11"/>
-      <c r="T550" s="11"/>
+      <c r="T550" s="14" t="s">
+        <v>2308</v>
+      </c>
       <c r="U550" s="11"/>
       <c r="V550" s="7"/>
       <c r="W550" s="7"/>
@@ -27400,12 +29108,18 @@
       <c r="Y550" s="11"/>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A551" s="7"/>
+      <c r="A551" s="7" t="s">
+        <v>2309</v>
+      </c>
       <c r="B551" s="11"/>
       <c r="C551" s="11"/>
-      <c r="D551" s="11"/>
+      <c r="D551" s="14" t="s">
+        <v>2310</v>
+      </c>
       <c r="E551" s="11"/>
-      <c r="F551" s="11"/>
+      <c r="F551" s="14" t="s">
+        <v>2311</v>
+      </c>
       <c r="G551" s="11"/>
       <c r="H551" s="7"/>
       <c r="I551" s="11"/>
@@ -27415,11 +29129,17 @@
       <c r="M551" s="11"/>
       <c r="N551" s="11"/>
       <c r="O551" s="7"/>
-      <c r="P551" s="7"/>
+      <c r="P551" s="7" t="s">
+        <v>2312</v>
+      </c>
       <c r="Q551" s="11"/>
-      <c r="R551" s="11"/>
+      <c r="R551" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S551" s="11"/>
-      <c r="T551" s="11"/>
+      <c r="T551" s="14" t="s">
+        <v>2313</v>
+      </c>
       <c r="U551" s="11"/>
       <c r="V551" s="7"/>
       <c r="W551" s="7"/>
@@ -27427,12 +29147,18 @@
       <c r="Y551" s="11"/>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="7"/>
+      <c r="A552" s="7" t="s">
+        <v>2314</v>
+      </c>
       <c r="B552" s="11"/>
       <c r="C552" s="11"/>
-      <c r="D552" s="11"/>
+      <c r="D552" s="14" t="s">
+        <v>2315</v>
+      </c>
       <c r="E552" s="11"/>
-      <c r="F552" s="11"/>
+      <c r="F552" s="14" t="s">
+        <v>2316</v>
+      </c>
       <c r="G552" s="11"/>
       <c r="H552" s="7"/>
       <c r="I552" s="11"/>
@@ -27442,11 +29168,17 @@
       <c r="M552" s="11"/>
       <c r="N552" s="11"/>
       <c r="O552" s="7"/>
-      <c r="P552" s="7"/>
+      <c r="P552" s="7" t="s">
+        <v>2317</v>
+      </c>
       <c r="Q552" s="11"/>
-      <c r="R552" s="11"/>
+      <c r="R552" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S552" s="11"/>
-      <c r="T552" s="11"/>
+      <c r="T552" s="14" t="s">
+        <v>2318</v>
+      </c>
       <c r="U552" s="11"/>
       <c r="V552" s="7"/>
       <c r="W552" s="7"/>
@@ -27454,12 +29186,18 @@
       <c r="Y552" s="11"/>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="7"/>
+      <c r="A553" s="7" t="s">
+        <v>2319</v>
+      </c>
       <c r="B553" s="11"/>
       <c r="C553" s="11"/>
-      <c r="D553" s="11"/>
+      <c r="D553" s="14" t="s">
+        <v>2320</v>
+      </c>
       <c r="E553" s="11"/>
-      <c r="F553" s="11"/>
+      <c r="F553" s="14" t="s">
+        <v>2321</v>
+      </c>
       <c r="G553" s="11"/>
       <c r="H553" s="7"/>
       <c r="I553" s="11"/>
@@ -27469,11 +29207,17 @@
       <c r="M553" s="11"/>
       <c r="N553" s="11"/>
       <c r="O553" s="7"/>
-      <c r="P553" s="7"/>
+      <c r="P553" s="7" t="s">
+        <v>2322</v>
+      </c>
       <c r="Q553" s="11"/>
-      <c r="R553" s="11"/>
+      <c r="R553" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S553" s="11"/>
-      <c r="T553" s="11"/>
+      <c r="T553" s="14" t="s">
+        <v>2323</v>
+      </c>
       <c r="U553" s="11"/>
       <c r="V553" s="7"/>
       <c r="W553" s="7"/>
@@ -27481,12 +29225,18 @@
       <c r="Y553" s="11"/>
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="7"/>
+      <c r="A554" s="7" t="s">
+        <v>2324</v>
+      </c>
       <c r="B554" s="11"/>
       <c r="C554" s="11"/>
-      <c r="D554" s="11"/>
+      <c r="D554" s="14" t="s">
+        <v>2325</v>
+      </c>
       <c r="E554" s="11"/>
-      <c r="F554" s="11"/>
+      <c r="F554" s="14" t="s">
+        <v>2283</v>
+      </c>
       <c r="G554" s="11"/>
       <c r="H554" s="7"/>
       <c r="I554" s="11"/>
@@ -27496,11 +29246,17 @@
       <c r="M554" s="11"/>
       <c r="N554" s="11"/>
       <c r="O554" s="7"/>
-      <c r="P554" s="7"/>
+      <c r="P554" s="7" t="s">
+        <v>2326</v>
+      </c>
       <c r="Q554" s="11"/>
-      <c r="R554" s="11"/>
+      <c r="R554" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S554" s="11"/>
-      <c r="T554" s="11"/>
+      <c r="T554" s="14" t="s">
+        <v>2327</v>
+      </c>
       <c r="U554" s="11"/>
       <c r="V554" s="7"/>
       <c r="W554" s="7"/>
@@ -27508,12 +29264,18 @@
       <c r="Y554" s="11"/>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="7"/>
+      <c r="A555" s="7" t="s">
+        <v>2328</v>
+      </c>
       <c r="B555" s="11"/>
       <c r="C555" s="11"/>
-      <c r="D555" s="11"/>
+      <c r="D555" s="14" t="s">
+        <v>2329</v>
+      </c>
       <c r="E555" s="11"/>
-      <c r="F555" s="11"/>
+      <c r="F555" s="14" t="s">
+        <v>2330</v>
+      </c>
       <c r="G555" s="11"/>
       <c r="H555" s="7"/>
       <c r="I555" s="11"/>
@@ -27523,9 +29285,13 @@
       <c r="M555" s="11"/>
       <c r="N555" s="11"/>
       <c r="O555" s="7"/>
-      <c r="P555" s="7"/>
+      <c r="P555" s="7" t="s">
+        <v>2331</v>
+      </c>
       <c r="Q555" s="11"/>
-      <c r="R555" s="11"/>
+      <c r="R555" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S555" s="11"/>
       <c r="T555" s="11"/>
       <c r="U555" s="11"/>
@@ -27535,12 +29301,18 @@
       <c r="Y555" s="11"/>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="7"/>
+      <c r="A556" s="7" t="s">
+        <v>2332</v>
+      </c>
       <c r="B556" s="11"/>
       <c r="C556" s="11"/>
-      <c r="D556" s="11"/>
+      <c r="D556" s="14" t="s">
+        <v>2333</v>
+      </c>
       <c r="E556" s="11"/>
-      <c r="F556" s="11"/>
+      <c r="F556" s="14" t="s">
+        <v>197</v>
+      </c>
       <c r="G556" s="11"/>
       <c r="H556" s="7"/>
       <c r="I556" s="11"/>
@@ -27550,11 +29322,17 @@
       <c r="M556" s="11"/>
       <c r="N556" s="11"/>
       <c r="O556" s="7"/>
-      <c r="P556" s="7"/>
+      <c r="P556" s="7" t="s">
+        <v>2334</v>
+      </c>
       <c r="Q556" s="11"/>
-      <c r="R556" s="11"/>
+      <c r="R556" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S556" s="11"/>
-      <c r="T556" s="11"/>
+      <c r="T556" s="14" t="s">
+        <v>2335</v>
+      </c>
       <c r="U556" s="11"/>
       <c r="V556" s="7"/>
       <c r="W556" s="7"/>
@@ -27562,26 +29340,40 @@
       <c r="Y556" s="11"/>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="7"/>
+      <c r="A557" s="7" t="s">
+        <v>2336</v>
+      </c>
       <c r="B557" s="11"/>
       <c r="C557" s="11"/>
-      <c r="D557" s="11"/>
+      <c r="D557" s="14" t="s">
+        <v>2337</v>
+      </c>
       <c r="E557" s="11"/>
-      <c r="F557" s="11"/>
+      <c r="F557" s="14" t="s">
+        <v>2338</v>
+      </c>
       <c r="G557" s="11"/>
       <c r="H557" s="7"/>
       <c r="I557" s="11"/>
-      <c r="J557" s="10"/>
+      <c r="J557" s="15" t="s">
+        <v>2339</v>
+      </c>
       <c r="K557" s="11"/>
       <c r="L557" s="11"/>
       <c r="M557" s="11"/>
       <c r="N557" s="11"/>
       <c r="O557" s="7"/>
-      <c r="P557" s="7"/>
+      <c r="P557" s="7" t="s">
+        <v>2340</v>
+      </c>
       <c r="Q557" s="11"/>
-      <c r="R557" s="11"/>
+      <c r="R557" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S557" s="11"/>
-      <c r="T557" s="11"/>
+      <c r="T557" s="14" t="s">
+        <v>2341</v>
+      </c>
       <c r="U557" s="11"/>
       <c r="V557" s="7"/>
       <c r="W557" s="7"/>
@@ -27589,12 +29381,18 @@
       <c r="Y557" s="11"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="7"/>
+      <c r="A558" s="7" t="s">
+        <v>2342</v>
+      </c>
       <c r="B558" s="11"/>
       <c r="C558" s="11"/>
-      <c r="D558" s="11"/>
+      <c r="D558" s="14" t="s">
+        <v>2343</v>
+      </c>
       <c r="E558" s="11"/>
-      <c r="F558" s="11"/>
+      <c r="F558" s="14" t="s">
+        <v>2191</v>
+      </c>
       <c r="G558" s="11"/>
       <c r="H558" s="7"/>
       <c r="I558" s="11"/>
@@ -27604,11 +29402,17 @@
       <c r="M558" s="11"/>
       <c r="N558" s="11"/>
       <c r="O558" s="7"/>
-      <c r="P558" s="7"/>
+      <c r="P558" s="7" t="s">
+        <v>2344</v>
+      </c>
       <c r="Q558" s="11"/>
-      <c r="R558" s="11"/>
+      <c r="R558" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S558" s="11"/>
-      <c r="T558" s="11"/>
+      <c r="T558" s="14" t="s">
+        <v>2345</v>
+      </c>
       <c r="U558" s="11"/>
       <c r="V558" s="7"/>
       <c r="W558" s="7"/>
@@ -27616,12 +29420,18 @@
       <c r="Y558" s="11"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="7"/>
+      <c r="A559" s="7" t="s">
+        <v>2346</v>
+      </c>
       <c r="B559" s="11"/>
       <c r="C559" s="11"/>
-      <c r="D559" s="11"/>
+      <c r="D559" s="14" t="s">
+        <v>2347</v>
+      </c>
       <c r="E559" s="11"/>
-      <c r="F559" s="11"/>
+      <c r="F559" s="14" t="s">
+        <v>2348</v>
+      </c>
       <c r="G559" s="11"/>
       <c r="H559" s="7"/>
       <c r="I559" s="11"/>
@@ -27631,11 +29441,17 @@
       <c r="M559" s="11"/>
       <c r="N559" s="11"/>
       <c r="O559" s="7"/>
-      <c r="P559" s="7"/>
+      <c r="P559" s="7" t="s">
+        <v>2349</v>
+      </c>
       <c r="Q559" s="11"/>
-      <c r="R559" s="11"/>
+      <c r="R559" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S559" s="11"/>
-      <c r="T559" s="11"/>
+      <c r="T559" s="14" t="s">
+        <v>2350</v>
+      </c>
       <c r="U559" s="11"/>
       <c r="V559" s="7"/>
       <c r="W559" s="7"/>
@@ -27643,12 +29459,18 @@
       <c r="Y559" s="11"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="7"/>
+      <c r="A560" s="7" t="s">
+        <v>2351</v>
+      </c>
       <c r="B560" s="11"/>
       <c r="C560" s="11"/>
-      <c r="D560" s="11"/>
+      <c r="D560" s="14" t="s">
+        <v>2352</v>
+      </c>
       <c r="E560" s="11"/>
-      <c r="F560" s="11"/>
+      <c r="F560" s="14" t="s">
+        <v>2353</v>
+      </c>
       <c r="G560" s="11"/>
       <c r="H560" s="7"/>
       <c r="I560" s="11"/>
@@ -27658,11 +29480,17 @@
       <c r="M560" s="11"/>
       <c r="N560" s="11"/>
       <c r="O560" s="7"/>
-      <c r="P560" s="7"/>
+      <c r="P560" s="7" t="s">
+        <v>2354</v>
+      </c>
       <c r="Q560" s="11"/>
-      <c r="R560" s="11"/>
+      <c r="R560" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S560" s="11"/>
-      <c r="T560" s="11"/>
+      <c r="T560" s="14" t="s">
+        <v>2355</v>
+      </c>
       <c r="U560" s="11"/>
       <c r="V560" s="7"/>
       <c r="W560" s="7"/>
@@ -27670,12 +29498,18 @@
       <c r="Y560" s="11"/>
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A561" s="7"/>
+      <c r="A561" s="7" t="s">
+        <v>2356</v>
+      </c>
       <c r="B561" s="11"/>
       <c r="C561" s="11"/>
-      <c r="D561" s="11"/>
+      <c r="D561" s="14" t="s">
+        <v>2357</v>
+      </c>
       <c r="E561" s="11"/>
-      <c r="F561" s="11"/>
+      <c r="F561" s="14" t="s">
+        <v>2358</v>
+      </c>
       <c r="G561" s="11"/>
       <c r="H561" s="7"/>
       <c r="I561" s="11"/>
@@ -27685,11 +29519,17 @@
       <c r="M561" s="11"/>
       <c r="N561" s="11"/>
       <c r="O561" s="7"/>
-      <c r="P561" s="7"/>
+      <c r="P561" s="7" t="s">
+        <v>2359</v>
+      </c>
       <c r="Q561" s="11"/>
-      <c r="R561" s="11"/>
+      <c r="R561" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S561" s="11"/>
-      <c r="T561" s="11"/>
+      <c r="T561" s="14" t="s">
+        <v>2360</v>
+      </c>
       <c r="U561" s="11"/>
       <c r="V561" s="7"/>
       <c r="W561" s="7"/>
@@ -27697,12 +29537,18 @@
       <c r="Y561" s="11"/>
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="7"/>
+      <c r="A562" s="7" t="s">
+        <v>2361</v>
+      </c>
       <c r="B562" s="11"/>
       <c r="C562" s="11"/>
-      <c r="D562" s="11"/>
+      <c r="D562" s="14" t="s">
+        <v>2362</v>
+      </c>
       <c r="E562" s="11"/>
-      <c r="F562" s="11"/>
+      <c r="F562" s="14" t="s">
+        <v>2363</v>
+      </c>
       <c r="G562" s="11"/>
       <c r="H562" s="7"/>
       <c r="I562" s="11"/>
@@ -27712,11 +29558,17 @@
       <c r="M562" s="11"/>
       <c r="N562" s="11"/>
       <c r="O562" s="7"/>
-      <c r="P562" s="7"/>
+      <c r="P562" s="7" t="s">
+        <v>2364</v>
+      </c>
       <c r="Q562" s="11"/>
-      <c r="R562" s="11"/>
+      <c r="R562" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S562" s="11"/>
-      <c r="T562" s="11"/>
+      <c r="T562" s="14" t="s">
+        <v>2365</v>
+      </c>
       <c r="U562" s="11"/>
       <c r="V562" s="7"/>
       <c r="W562" s="7"/>
@@ -27724,12 +29576,18 @@
       <c r="Y562" s="11"/>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A563" s="7"/>
+      <c r="A563" s="7" t="s">
+        <v>2366</v>
+      </c>
       <c r="B563" s="11"/>
       <c r="C563" s="11"/>
-      <c r="D563" s="11"/>
+      <c r="D563" s="14" t="s">
+        <v>2367</v>
+      </c>
       <c r="E563" s="11"/>
-      <c r="F563" s="11"/>
+      <c r="F563" s="14" t="s">
+        <v>2115</v>
+      </c>
       <c r="G563" s="11"/>
       <c r="H563" s="7"/>
       <c r="I563" s="11"/>
@@ -27739,11 +29597,17 @@
       <c r="M563" s="11"/>
       <c r="N563" s="11"/>
       <c r="O563" s="7"/>
-      <c r="P563" s="7"/>
+      <c r="P563" s="7" t="s">
+        <v>2368</v>
+      </c>
       <c r="Q563" s="11"/>
-      <c r="R563" s="11"/>
+      <c r="R563" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S563" s="11"/>
-      <c r="T563" s="11"/>
+      <c r="T563" s="14" t="s">
+        <v>2369</v>
+      </c>
       <c r="U563" s="11"/>
       <c r="V563" s="7"/>
       <c r="W563" s="7"/>
@@ -27751,12 +29615,18 @@
       <c r="Y563" s="11"/>
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="7"/>
+      <c r="A564" s="7" t="s">
+        <v>2370</v>
+      </c>
       <c r="B564" s="11"/>
       <c r="C564" s="11"/>
-      <c r="D564" s="11"/>
+      <c r="D564" s="14" t="s">
+        <v>2371</v>
+      </c>
       <c r="E564" s="11"/>
-      <c r="F564" s="11"/>
+      <c r="F564" s="14" t="s">
+        <v>2358</v>
+      </c>
       <c r="G564" s="11"/>
       <c r="H564" s="7"/>
       <c r="I564" s="11"/>
@@ -27766,11 +29636,17 @@
       <c r="M564" s="11"/>
       <c r="N564" s="11"/>
       <c r="O564" s="7"/>
-      <c r="P564" s="7"/>
+      <c r="P564" s="7" t="s">
+        <v>2372</v>
+      </c>
       <c r="Q564" s="11"/>
-      <c r="R564" s="11"/>
+      <c r="R564" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S564" s="11"/>
-      <c r="T564" s="11"/>
+      <c r="T564" s="14" t="s">
+        <v>2373</v>
+      </c>
       <c r="U564" s="11"/>
       <c r="V564" s="7"/>
       <c r="W564" s="7"/>
@@ -27778,12 +29654,18 @@
       <c r="Y564" s="11"/>
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A565" s="7"/>
+      <c r="A565" s="7" t="s">
+        <v>2374</v>
+      </c>
       <c r="B565" s="11"/>
       <c r="C565" s="11"/>
-      <c r="D565" s="11"/>
+      <c r="D565" s="14" t="s">
+        <v>2375</v>
+      </c>
       <c r="E565" s="11"/>
-      <c r="F565" s="11"/>
+      <c r="F565" s="14" t="s">
+        <v>2274</v>
+      </c>
       <c r="G565" s="11"/>
       <c r="H565" s="7"/>
       <c r="I565" s="11"/>
@@ -27793,11 +29675,17 @@
       <c r="M565" s="11"/>
       <c r="N565" s="11"/>
       <c r="O565" s="7"/>
-      <c r="P565" s="7"/>
+      <c r="P565" s="7" t="s">
+        <v>2376</v>
+      </c>
       <c r="Q565" s="11"/>
-      <c r="R565" s="11"/>
+      <c r="R565" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S565" s="11"/>
-      <c r="T565" s="11"/>
+      <c r="T565" s="14" t="s">
+        <v>2377</v>
+      </c>
       <c r="U565" s="11"/>
       <c r="V565" s="7"/>
       <c r="W565" s="7"/>
@@ -27805,12 +29693,18 @@
       <c r="Y565" s="11"/>
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A566" s="7"/>
+      <c r="A566" s="7" t="s">
+        <v>2378</v>
+      </c>
       <c r="B566" s="11"/>
       <c r="C566" s="11"/>
-      <c r="D566" s="11"/>
+      <c r="D566" s="14" t="s">
+        <v>2379</v>
+      </c>
       <c r="E566" s="11"/>
-      <c r="F566" s="11"/>
+      <c r="F566" s="14" t="s">
+        <v>2301</v>
+      </c>
       <c r="G566" s="11"/>
       <c r="H566" s="7"/>
       <c r="I566" s="11"/>
@@ -27820,9 +29714,13 @@
       <c r="M566" s="11"/>
       <c r="N566" s="11"/>
       <c r="O566" s="7"/>
-      <c r="P566" s="7"/>
+      <c r="P566" s="7" t="s">
+        <v>2380</v>
+      </c>
       <c r="Q566" s="11"/>
-      <c r="R566" s="11"/>
+      <c r="R566" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S566" s="11"/>
       <c r="T566" s="11"/>
       <c r="U566" s="11"/>
@@ -27832,12 +29730,18 @@
       <c r="Y566" s="11"/>
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="7"/>
+      <c r="A567" s="7" t="s">
+        <v>2381</v>
+      </c>
       <c r="B567" s="11"/>
       <c r="C567" s="11"/>
-      <c r="D567" s="11"/>
+      <c r="D567" s="14" t="s">
+        <v>2382</v>
+      </c>
       <c r="E567" s="11"/>
-      <c r="F567" s="11"/>
+      <c r="F567" s="14" t="s">
+        <v>2330</v>
+      </c>
       <c r="G567" s="11"/>
       <c r="H567" s="7"/>
       <c r="I567" s="11"/>
@@ -27847,11 +29751,17 @@
       <c r="M567" s="11"/>
       <c r="N567" s="11"/>
       <c r="O567" s="7"/>
-      <c r="P567" s="7"/>
+      <c r="P567" s="7" t="s">
+        <v>2383</v>
+      </c>
       <c r="Q567" s="11"/>
-      <c r="R567" s="11"/>
+      <c r="R567" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S567" s="11"/>
-      <c r="T567" s="11"/>
+      <c r="T567" s="14" t="s">
+        <v>2384</v>
+      </c>
       <c r="U567" s="11"/>
       <c r="V567" s="7"/>
       <c r="W567" s="7"/>
@@ -27859,12 +29769,18 @@
       <c r="Y567" s="11"/>
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A568" s="7"/>
+      <c r="A568" s="7" t="s">
+        <v>2385</v>
+      </c>
       <c r="B568" s="11"/>
       <c r="C568" s="11"/>
-      <c r="D568" s="11"/>
+      <c r="D568" s="14" t="s">
+        <v>2386</v>
+      </c>
       <c r="E568" s="11"/>
-      <c r="F568" s="11"/>
+      <c r="F568" s="14" t="s">
+        <v>2387</v>
+      </c>
       <c r="G568" s="11"/>
       <c r="H568" s="7"/>
       <c r="I568" s="11"/>
@@ -27874,11 +29790,17 @@
       <c r="M568" s="11"/>
       <c r="N568" s="11"/>
       <c r="O568" s="7"/>
-      <c r="P568" s="7"/>
+      <c r="P568" s="7" t="s">
+        <v>2388</v>
+      </c>
       <c r="Q568" s="11"/>
-      <c r="R568" s="11"/>
+      <c r="R568" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S568" s="11"/>
-      <c r="T568" s="11"/>
+      <c r="T568" s="14" t="s">
+        <v>2389</v>
+      </c>
       <c r="U568" s="11"/>
       <c r="V568" s="7"/>
       <c r="W568" s="7"/>
@@ -27886,12 +29808,18 @@
       <c r="Y568" s="11"/>
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A569" s="7"/>
+      <c r="A569" s="7" t="s">
+        <v>2390</v>
+      </c>
       <c r="B569" s="11"/>
       <c r="C569" s="11"/>
-      <c r="D569" s="11"/>
+      <c r="D569" s="14" t="s">
+        <v>2391</v>
+      </c>
       <c r="E569" s="11"/>
-      <c r="F569" s="11"/>
+      <c r="F569" s="14" t="s">
+        <v>2115</v>
+      </c>
       <c r="G569" s="11"/>
       <c r="H569" s="7"/>
       <c r="I569" s="11"/>
@@ -27901,11 +29829,17 @@
       <c r="M569" s="11"/>
       <c r="N569" s="11"/>
       <c r="O569" s="7"/>
-      <c r="P569" s="7"/>
+      <c r="P569" s="7" t="s">
+        <v>2392</v>
+      </c>
       <c r="Q569" s="11"/>
-      <c r="R569" s="11"/>
+      <c r="R569" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S569" s="11"/>
-      <c r="T569" s="11"/>
+      <c r="T569" s="14" t="s">
+        <v>2393</v>
+      </c>
       <c r="U569" s="11"/>
       <c r="V569" s="7"/>
       <c r="W569" s="7"/>
@@ -27913,12 +29847,18 @@
       <c r="Y569" s="11"/>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A570" s="7"/>
+      <c r="A570" s="7" t="s">
+        <v>2394</v>
+      </c>
       <c r="B570" s="11"/>
       <c r="C570" s="11"/>
-      <c r="D570" s="11"/>
+      <c r="D570" s="14" t="s">
+        <v>2395</v>
+      </c>
       <c r="E570" s="11"/>
-      <c r="F570" s="11"/>
+      <c r="F570" s="14" t="s">
+        <v>2210</v>
+      </c>
       <c r="G570" s="11"/>
       <c r="H570" s="7"/>
       <c r="I570" s="11"/>
@@ -27928,11 +29868,17 @@
       <c r="M570" s="11"/>
       <c r="N570" s="11"/>
       <c r="O570" s="7"/>
-      <c r="P570" s="7"/>
+      <c r="P570" s="7" t="s">
+        <v>2396</v>
+      </c>
       <c r="Q570" s="11"/>
-      <c r="R570" s="11"/>
+      <c r="R570" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S570" s="11"/>
-      <c r="T570" s="11"/>
+      <c r="T570" s="14" t="s">
+        <v>2397</v>
+      </c>
       <c r="U570" s="11"/>
       <c r="V570" s="7"/>
       <c r="W570" s="7"/>
@@ -27940,12 +29886,18 @@
       <c r="Y570" s="11"/>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A571" s="7"/>
+      <c r="A571" s="7" t="s">
+        <v>2398</v>
+      </c>
       <c r="B571" s="11"/>
       <c r="C571" s="11"/>
-      <c r="D571" s="11"/>
+      <c r="D571" s="14" t="s">
+        <v>2399</v>
+      </c>
       <c r="E571" s="11"/>
-      <c r="F571" s="11"/>
+      <c r="F571" s="14" t="s">
+        <v>2400</v>
+      </c>
       <c r="G571" s="11"/>
       <c r="H571" s="7"/>
       <c r="I571" s="11"/>
@@ -27955,9 +29907,13 @@
       <c r="M571" s="11"/>
       <c r="N571" s="11"/>
       <c r="O571" s="7"/>
-      <c r="P571" s="7"/>
+      <c r="P571" s="7" t="s">
+        <v>2401</v>
+      </c>
       <c r="Q571" s="11"/>
-      <c r="R571" s="11"/>
+      <c r="R571" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S571" s="11"/>
       <c r="T571" s="11"/>
       <c r="U571" s="11"/>
@@ -27967,12 +29923,18 @@
       <c r="Y571" s="11"/>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A572" s="7"/>
+      <c r="A572" s="7" t="s">
+        <v>2402</v>
+      </c>
       <c r="B572" s="11"/>
       <c r="C572" s="11"/>
-      <c r="D572" s="11"/>
+      <c r="D572" s="14" t="s">
+        <v>2403</v>
+      </c>
       <c r="E572" s="11"/>
-      <c r="F572" s="11"/>
+      <c r="F572" s="14" t="s">
+        <v>2205</v>
+      </c>
       <c r="G572" s="11"/>
       <c r="H572" s="7"/>
       <c r="I572" s="11"/>
@@ -27982,9 +29944,13 @@
       <c r="M572" s="11"/>
       <c r="N572" s="11"/>
       <c r="O572" s="7"/>
-      <c r="P572" s="7"/>
+      <c r="P572" s="7" t="s">
+        <v>2404</v>
+      </c>
       <c r="Q572" s="11"/>
-      <c r="R572" s="11"/>
+      <c r="R572" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S572" s="11"/>
       <c r="T572" s="11"/>
       <c r="U572" s="11"/>
@@ -27994,12 +29960,18 @@
       <c r="Y572" s="11"/>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A573" s="7"/>
+      <c r="A573" s="7" t="s">
+        <v>2405</v>
+      </c>
       <c r="B573" s="11"/>
       <c r="C573" s="11"/>
-      <c r="D573" s="11"/>
+      <c r="D573" s="14" t="s">
+        <v>2406</v>
+      </c>
       <c r="E573" s="11"/>
-      <c r="F573" s="11"/>
+      <c r="F573" s="14" t="s">
+        <v>2407</v>
+      </c>
       <c r="G573" s="11"/>
       <c r="H573" s="7"/>
       <c r="I573" s="11"/>
@@ -28009,11 +29981,17 @@
       <c r="M573" s="11"/>
       <c r="N573" s="11"/>
       <c r="O573" s="7"/>
-      <c r="P573" s="7"/>
+      <c r="P573" s="7" t="s">
+        <v>2408</v>
+      </c>
       <c r="Q573" s="11"/>
-      <c r="R573" s="11"/>
+      <c r="R573" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S573" s="11"/>
-      <c r="T573" s="11"/>
+      <c r="T573" s="14" t="s">
+        <v>2409</v>
+      </c>
       <c r="U573" s="11"/>
       <c r="V573" s="7"/>
       <c r="W573" s="7"/>
@@ -28021,12 +29999,18 @@
       <c r="Y573" s="11"/>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="7"/>
+      <c r="A574" s="7" t="s">
+        <v>2410</v>
+      </c>
       <c r="B574" s="11"/>
       <c r="C574" s="11"/>
-      <c r="D574" s="11"/>
+      <c r="D574" s="14" t="s">
+        <v>2411</v>
+      </c>
       <c r="E574" s="11"/>
-      <c r="F574" s="11"/>
+      <c r="F574" s="14" t="s">
+        <v>2412</v>
+      </c>
       <c r="G574" s="11"/>
       <c r="H574" s="7"/>
       <c r="I574" s="11"/>
@@ -28036,11 +30020,17 @@
       <c r="M574" s="11"/>
       <c r="N574" s="11"/>
       <c r="O574" s="7"/>
-      <c r="P574" s="7"/>
+      <c r="P574" s="7" t="s">
+        <v>2413</v>
+      </c>
       <c r="Q574" s="11"/>
-      <c r="R574" s="11"/>
+      <c r="R574" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S574" s="11"/>
-      <c r="T574" s="11"/>
+      <c r="T574" s="14" t="s">
+        <v>2414</v>
+      </c>
       <c r="U574" s="11"/>
       <c r="V574" s="7"/>
       <c r="W574" s="7"/>
@@ -28048,12 +30038,18 @@
       <c r="Y574" s="11"/>
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A575" s="7"/>
+      <c r="A575" s="7" t="s">
+        <v>2415</v>
+      </c>
       <c r="B575" s="11"/>
       <c r="C575" s="11"/>
-      <c r="D575" s="11"/>
+      <c r="D575" s="14" t="s">
+        <v>2416</v>
+      </c>
       <c r="E575" s="11"/>
-      <c r="F575" s="11"/>
+      <c r="F575" s="14" t="s">
+        <v>2417</v>
+      </c>
       <c r="G575" s="11"/>
       <c r="H575" s="7"/>
       <c r="I575" s="11"/>
@@ -28063,11 +30059,17 @@
       <c r="M575" s="11"/>
       <c r="N575" s="11"/>
       <c r="O575" s="7"/>
-      <c r="P575" s="7"/>
+      <c r="P575" s="7" t="s">
+        <v>2418</v>
+      </c>
       <c r="Q575" s="11"/>
-      <c r="R575" s="11"/>
+      <c r="R575" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S575" s="11"/>
-      <c r="T575" s="11"/>
+      <c r="T575" s="14" t="s">
+        <v>2419</v>
+      </c>
       <c r="U575" s="11"/>
       <c r="V575" s="7"/>
       <c r="W575" s="7"/>
@@ -28075,26 +30077,40 @@
       <c r="Y575" s="11"/>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A576" s="7"/>
+      <c r="A576" s="7" t="s">
+        <v>2420</v>
+      </c>
       <c r="B576" s="11"/>
       <c r="C576" s="11"/>
-      <c r="D576" s="11"/>
+      <c r="D576" s="14" t="s">
+        <v>2421</v>
+      </c>
       <c r="E576" s="11"/>
-      <c r="F576" s="11"/>
+      <c r="F576" s="14" t="s">
+        <v>2422</v>
+      </c>
       <c r="G576" s="11"/>
       <c r="H576" s="7"/>
       <c r="I576" s="11"/>
-      <c r="J576" s="10"/>
+      <c r="J576" s="15" t="s">
+        <v>2423</v>
+      </c>
       <c r="K576" s="11"/>
       <c r="L576" s="11"/>
       <c r="M576" s="11"/>
       <c r="N576" s="11"/>
       <c r="O576" s="7"/>
-      <c r="P576" s="7"/>
+      <c r="P576" s="7" t="s">
+        <v>2424</v>
+      </c>
       <c r="Q576" s="11"/>
-      <c r="R576" s="11"/>
+      <c r="R576" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S576" s="11"/>
-      <c r="T576" s="11"/>
+      <c r="T576" s="14" t="s">
+        <v>2425</v>
+      </c>
       <c r="U576" s="11"/>
       <c r="V576" s="7"/>
       <c r="W576" s="7"/>
@@ -28102,12 +30118,18 @@
       <c r="Y576" s="11"/>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="7"/>
+      <c r="A577" s="7" t="s">
+        <v>2426</v>
+      </c>
       <c r="B577" s="11"/>
       <c r="C577" s="11"/>
-      <c r="D577" s="11"/>
+      <c r="D577" s="14" t="s">
+        <v>2427</v>
+      </c>
       <c r="E577" s="11"/>
-      <c r="F577" s="11"/>
+      <c r="F577" s="14" t="s">
+        <v>2428</v>
+      </c>
       <c r="G577" s="11"/>
       <c r="H577" s="7"/>
       <c r="I577" s="11"/>
@@ -28117,11 +30139,17 @@
       <c r="M577" s="11"/>
       <c r="N577" s="11"/>
       <c r="O577" s="7"/>
-      <c r="P577" s="7"/>
+      <c r="P577" s="7" t="s">
+        <v>2429</v>
+      </c>
       <c r="Q577" s="11"/>
-      <c r="R577" s="11"/>
+      <c r="R577" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S577" s="11"/>
-      <c r="T577" s="11"/>
+      <c r="T577" s="14" t="s">
+        <v>2430</v>
+      </c>
       <c r="U577" s="11"/>
       <c r="V577" s="7"/>
       <c r="W577" s="7"/>
@@ -28129,12 +30157,18 @@
       <c r="Y577" s="11"/>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A578" s="7"/>
+      <c r="A578" s="7" t="s">
+        <v>2431</v>
+      </c>
       <c r="B578" s="11"/>
       <c r="C578" s="11"/>
-      <c r="D578" s="11"/>
+      <c r="D578" s="14" t="s">
+        <v>2320</v>
+      </c>
       <c r="E578" s="11"/>
-      <c r="F578" s="11"/>
+      <c r="F578" s="14" t="s">
+        <v>2432</v>
+      </c>
       <c r="G578" s="11"/>
       <c r="H578" s="7"/>
       <c r="I578" s="11"/>
@@ -28144,9 +30178,13 @@
       <c r="M578" s="11"/>
       <c r="N578" s="11"/>
       <c r="O578" s="7"/>
-      <c r="P578" s="7"/>
+      <c r="P578" s="7" t="s">
+        <v>2433</v>
+      </c>
       <c r="Q578" s="11"/>
-      <c r="R578" s="11"/>
+      <c r="R578" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S578" s="11"/>
       <c r="T578" s="11"/>
       <c r="U578" s="11"/>
@@ -28156,12 +30194,18 @@
       <c r="Y578" s="11"/>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A579" s="7"/>
+      <c r="A579" s="7" t="s">
+        <v>2434</v>
+      </c>
       <c r="B579" s="11"/>
       <c r="C579" s="11"/>
-      <c r="D579" s="11"/>
+      <c r="D579" s="14" t="s">
+        <v>2329</v>
+      </c>
       <c r="E579" s="11"/>
-      <c r="F579" s="11"/>
+      <c r="F579" s="14" t="s">
+        <v>2358</v>
+      </c>
       <c r="G579" s="11"/>
       <c r="H579" s="7"/>
       <c r="I579" s="11"/>
@@ -28171,9 +30215,13 @@
       <c r="M579" s="11"/>
       <c r="N579" s="11"/>
       <c r="O579" s="7"/>
-      <c r="P579" s="7"/>
+      <c r="P579" s="7" t="s">
+        <v>2435</v>
+      </c>
       <c r="Q579" s="11"/>
-      <c r="R579" s="11"/>
+      <c r="R579" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S579" s="11"/>
       <c r="T579" s="11"/>
       <c r="U579" s="11"/>
@@ -28183,12 +30231,18 @@
       <c r="Y579" s="11"/>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="7"/>
+      <c r="A580" s="7" t="s">
+        <v>2436</v>
+      </c>
       <c r="B580" s="11"/>
       <c r="C580" s="11"/>
-      <c r="D580" s="11"/>
+      <c r="D580" s="14" t="s">
+        <v>2437</v>
+      </c>
       <c r="E580" s="11"/>
-      <c r="F580" s="11"/>
+      <c r="F580" s="14" t="s">
+        <v>2438</v>
+      </c>
       <c r="G580" s="11"/>
       <c r="H580" s="7"/>
       <c r="I580" s="11"/>
@@ -28198,9 +30252,13 @@
       <c r="M580" s="11"/>
       <c r="N580" s="11"/>
       <c r="O580" s="7"/>
-      <c r="P580" s="7"/>
+      <c r="P580" s="7" t="s">
+        <v>2439</v>
+      </c>
       <c r="Q580" s="11"/>
-      <c r="R580" s="11"/>
+      <c r="R580" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S580" s="11"/>
       <c r="T580" s="11"/>
       <c r="U580" s="11"/>
@@ -28210,12 +30268,18 @@
       <c r="Y580" s="11"/>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A581" s="7"/>
+      <c r="A581" s="7" t="s">
+        <v>2440</v>
+      </c>
       <c r="B581" s="11"/>
       <c r="C581" s="11"/>
-      <c r="D581" s="11"/>
+      <c r="D581" s="14" t="s">
+        <v>2441</v>
+      </c>
       <c r="E581" s="11"/>
-      <c r="F581" s="11"/>
+      <c r="F581" s="14" t="s">
+        <v>2229</v>
+      </c>
       <c r="G581" s="11"/>
       <c r="H581" s="7"/>
       <c r="I581" s="11"/>
@@ -28225,9 +30289,13 @@
       <c r="M581" s="11"/>
       <c r="N581" s="11"/>
       <c r="O581" s="7"/>
-      <c r="P581" s="7"/>
+      <c r="P581" s="7" t="s">
+        <v>2442</v>
+      </c>
       <c r="Q581" s="11"/>
-      <c r="R581" s="11"/>
+      <c r="R581" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S581" s="11"/>
       <c r="T581" s="11"/>
       <c r="U581" s="11"/>
@@ -28237,12 +30305,18 @@
       <c r="Y581" s="11"/>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A582" s="7"/>
+      <c r="A582" s="7" t="s">
+        <v>2443</v>
+      </c>
       <c r="B582" s="11"/>
       <c r="C582" s="11"/>
-      <c r="D582" s="11"/>
+      <c r="D582" s="14" t="s">
+        <v>2444</v>
+      </c>
       <c r="E582" s="11"/>
-      <c r="F582" s="11"/>
+      <c r="F582" s="14" t="s">
+        <v>2445</v>
+      </c>
       <c r="G582" s="11"/>
       <c r="H582" s="7"/>
       <c r="I582" s="11"/>
@@ -28252,11 +30326,17 @@
       <c r="M582" s="11"/>
       <c r="N582" s="11"/>
       <c r="O582" s="7"/>
-      <c r="P582" s="7"/>
+      <c r="P582" s="7" t="s">
+        <v>2446</v>
+      </c>
       <c r="Q582" s="11"/>
-      <c r="R582" s="11"/>
+      <c r="R582" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S582" s="11"/>
-      <c r="T582" s="11"/>
+      <c r="T582" s="14" t="s">
+        <v>2447</v>
+      </c>
       <c r="U582" s="11"/>
       <c r="V582" s="7"/>
       <c r="W582" s="7"/>
@@ -28264,12 +30344,18 @@
       <c r="Y582" s="11"/>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="7"/>
+      <c r="A583" s="7" t="s">
+        <v>2448</v>
+      </c>
       <c r="B583" s="11"/>
       <c r="C583" s="11"/>
-      <c r="D583" s="11"/>
+      <c r="D583" s="14" t="s">
+        <v>2449</v>
+      </c>
       <c r="E583" s="11"/>
-      <c r="F583" s="11"/>
+      <c r="F583" s="14" t="s">
+        <v>2160</v>
+      </c>
       <c r="G583" s="11"/>
       <c r="H583" s="7"/>
       <c r="I583" s="11"/>
@@ -28279,9 +30365,13 @@
       <c r="M583" s="11"/>
       <c r="N583" s="11"/>
       <c r="O583" s="7"/>
-      <c r="P583" s="7"/>
+      <c r="P583" s="7" t="s">
+        <v>2450</v>
+      </c>
       <c r="Q583" s="11"/>
-      <c r="R583" s="11"/>
+      <c r="R583" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S583" s="11"/>
       <c r="T583" s="11"/>
       <c r="U583" s="11"/>
@@ -28291,12 +30381,18 @@
       <c r="Y583" s="11"/>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A584" s="7"/>
+      <c r="A584" s="7" t="s">
+        <v>2451</v>
+      </c>
       <c r="B584" s="11"/>
       <c r="C584" s="11"/>
-      <c r="D584" s="11"/>
+      <c r="D584" s="14" t="s">
+        <v>2452</v>
+      </c>
       <c r="E584" s="11"/>
-      <c r="F584" s="11"/>
+      <c r="F584" s="14" t="s">
+        <v>2149</v>
+      </c>
       <c r="G584" s="11"/>
       <c r="H584" s="7"/>
       <c r="I584" s="11"/>
@@ -28306,9 +30402,13 @@
       <c r="M584" s="11"/>
       <c r="N584" s="11"/>
       <c r="O584" s="7"/>
-      <c r="P584" s="7"/>
+      <c r="P584" s="7" t="s">
+        <v>2453</v>
+      </c>
       <c r="Q584" s="11"/>
-      <c r="R584" s="11"/>
+      <c r="R584" s="14" t="s">
+        <v>2098</v>
+      </c>
       <c r="S584" s="11"/>
       <c r="T584" s="11"/>
       <c r="U584" s="11"/>
@@ -28318,24 +30418,36 @@
       <c r="Y584" s="11"/>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A585" s="7"/>
+      <c r="A585" s="7" t="s">
+        <v>2454</v>
+      </c>
       <c r="B585" s="11"/>
       <c r="C585" s="11"/>
-      <c r="D585" s="11"/>
+      <c r="D585" s="14" t="s">
+        <v>2455</v>
+      </c>
       <c r="E585" s="11"/>
-      <c r="F585" s="11"/>
+      <c r="F585" s="14" t="s">
+        <v>2456</v>
+      </c>
       <c r="G585" s="11"/>
       <c r="H585" s="7"/>
       <c r="I585" s="11"/>
-      <c r="J585" s="10"/>
+      <c r="J585" s="15" t="s">
+        <v>2457</v>
+      </c>
       <c r="K585" s="11"/>
       <c r="L585" s="11"/>
       <c r="M585" s="11"/>
       <c r="N585" s="11"/>
       <c r="O585" s="7"/>
-      <c r="P585" s="7"/>
+      <c r="P585" s="7" t="s">
+        <v>2458</v>
+      </c>
       <c r="Q585" s="11"/>
-      <c r="R585" s="11"/>
+      <c r="R585" s="14" t="s">
+        <v>2459</v>
+      </c>
       <c r="S585" s="11"/>
       <c r="T585" s="11"/>
       <c r="U585" s="11"/>
@@ -28344,8 +30456,10 @@
       <c r="X585" s="11"/>
       <c r="Y585" s="11"/>
     </row>
-    <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A586" s="7"/>
+    <row r="586" customFormat="false" ht="21.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A586" s="7" t="s">
+        <v>2460</v>
+      </c>
       <c r="B586" s="11"/>
       <c r="C586" s="11"/>
       <c r="D586" s="11"/>
@@ -28356,20 +30470,34 @@
       <c r="I586" s="11"/>
       <c r="J586" s="10"/>
       <c r="K586" s="11"/>
-      <c r="L586" s="11"/>
+      <c r="L586" s="14" t="s">
+        <v>2461</v>
+      </c>
       <c r="M586" s="11"/>
       <c r="N586" s="11"/>
       <c r="O586" s="7"/>
-      <c r="P586" s="7"/>
-      <c r="Q586" s="11"/>
-      <c r="R586" s="11"/>
-      <c r="S586" s="11"/>
+      <c r="P586" s="7" t="s">
+        <v>2462</v>
+      </c>
+      <c r="Q586" s="14" t="s">
+        <v>2463</v>
+      </c>
+      <c r="R586" s="14" t="s">
+        <v>2098</v>
+      </c>
+      <c r="S586" s="14" t="s">
+        <v>2464</v>
+      </c>
       <c r="T586" s="11"/>
       <c r="U586" s="11"/>
-      <c r="V586" s="7"/>
+      <c r="V586" s="7" t="s">
+        <v>569</v>
+      </c>
       <c r="W586" s="7"/>
       <c r="X586" s="11"/>
-      <c r="Y586" s="11"/>
+      <c r="Y586" s="15" t="s">
+        <v>2465</v>
+      </c>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="7"/>
@@ -39525,10 +41653,10 @@
   </sheetData>
   <autoFilter ref="A1:Z483"/>
   <conditionalFormatting sqref="P1:P1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6"/>
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H1001" type="list">
@@ -39550,6 +41678,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="P63" r:id="rId2" display="Gu_Wing-syut.png"/>
+    <hyperlink ref="Y586" r:id="rId3" display="https://www.studio-virtual.cz/about/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -39558,8 +41687,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -39571,240 +41700,240 @@
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>2094</v>
-      </c>
-      <c r="B1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>2096</v>
+      <c r="A2" s="19" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>2468</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>2097</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>2098</v>
+      <c r="A3" s="19" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>2470</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>2099</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>2100</v>
+      <c r="A4" s="19" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>2472</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>2102</v>
+      <c r="A5" s="19" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>2474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>2103</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>2104</v>
+      <c r="A6" s="19" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>2476</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>2105</v>
-      </c>
-      <c r="B8" s="16"/>
+      <c r="A8" s="17" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>2106</v>
+      <c r="B9" s="18" t="s">
+        <v>2478</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>2108</v>
+      <c r="A10" s="19" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>2480</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>2110</v>
+      <c r="A11" s="19" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>2482</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>2111</v>
+      <c r="B12" s="18" t="s">
+        <v>2483</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>2112</v>
+      <c r="B13" s="18" t="s">
+        <v>2484</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>2113</v>
+      <c r="B14" s="18" t="s">
+        <v>2485</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>2114</v>
+      <c r="B15" s="18" t="s">
+        <v>2486</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>2115</v>
+      <c r="B16" s="18" t="s">
+        <v>2487</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>2116</v>
+      <c r="B17" s="18" t="s">
+        <v>2488</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>2117</v>
+      <c r="B18" s="18" t="s">
+        <v>2489</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>2118</v>
+      <c r="B19" s="18" t="s">
+        <v>2490</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>2119</v>
+      <c r="B20" s="18" t="s">
+        <v>2491</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>2120</v>
+      <c r="B21" s="18" t="s">
+        <v>2492</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>2122</v>
+      <c r="A22" s="19" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>2494</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>2123</v>
+      <c r="B23" s="18" t="s">
+        <v>2495</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>2124</v>
+      <c r="B24" s="18" t="s">
+        <v>2496</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>2125</v>
+      <c r="B25" s="18" t="s">
+        <v>2497</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>2126</v>
+      <c r="B26" s="18" t="s">
+        <v>2498</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>2127</v>
+      <c r="B27" s="18" t="s">
+        <v>2499</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>2128</v>
+      <c r="B28" s="18" t="s">
+        <v>2500</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>2129</v>
+      <c r="B29" s="18" t="s">
+        <v>2501</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>2130</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>2131</v>
+      <c r="A30" s="20" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>2503</v>
       </c>
     </row>
   </sheetData>
